--- a/TestCase_Chaldal.xlsx
+++ b/TestCase_Chaldal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Full Stack Sqa Course\ChalDal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Full Stack Sqa Course\ChalDal\Chaldal-Manual-Testing-TestCases--Writing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB052390-51D3-4F97-8464-9BBF544F6C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BEFBB6-86DF-4EE1-945E-1EF469E3EA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="666">
   <si>
     <t>Product Name</t>
   </si>
@@ -979,9 +979,6 @@
   </si>
   <si>
     <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>Sign Up and Login</t>
   </si>
   <si>
     <t>Should not display a validation error message when the name field is empty</t>
@@ -3040,6 +3037,12 @@
       </rPr>
       <t>Blank Input</t>
     </r>
+  </si>
+  <si>
+    <t>Sign Up, Login</t>
+  </si>
+  <si>
+    <t>MD. Nasif Sadnan Chwodhury</t>
   </si>
 </sst>
 </file>
@@ -3705,7 +3708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="89">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -4466,19 +4469,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -4726,7 +4716,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="519">
+  <cellXfs count="516">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5482,39 +5472,39 @@
     <xf numFmtId="0" fontId="47" fillId="21" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="33" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="33" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5593,7 +5583,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="42" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="42" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
@@ -5640,12 +5630,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5657,21 +5647,21 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5707,7 +5697,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="60" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5717,7 +5707,7 @@
     <xf numFmtId="0" fontId="57" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5756,16 +5746,229 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="43" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="43" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5773,35 +5976,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5815,298 +6000,94 @@
     <xf numFmtId="0" fontId="30" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="20" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="43" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="43" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6780,48 +6761,48 @@
   <sheetData>
     <row r="5" spans="10:25" ht="13.8" customHeight="1"/>
     <row r="6" spans="10:25">
-      <c r="J6" s="408" t="s">
-        <v>404</v>
-      </c>
-      <c r="K6" s="408"/>
-      <c r="L6" s="408"/>
-      <c r="M6" s="408"/>
-      <c r="N6" s="408"/>
-      <c r="O6" s="408"/>
-      <c r="P6" s="408"/>
-      <c r="Q6" s="408"/>
-      <c r="R6" s="408"/>
-      <c r="S6" s="408"/>
-      <c r="T6" s="408"/>
-      <c r="U6" s="408"/>
+      <c r="J6" s="384" t="s">
+        <v>403</v>
+      </c>
+      <c r="K6" s="384"/>
+      <c r="L6" s="384"/>
+      <c r="M6" s="384"/>
+      <c r="N6" s="384"/>
+      <c r="O6" s="384"/>
+      <c r="P6" s="384"/>
+      <c r="Q6" s="384"/>
+      <c r="R6" s="384"/>
+      <c r="S6" s="384"/>
+      <c r="T6" s="384"/>
+      <c r="U6" s="384"/>
     </row>
     <row r="7" spans="10:25">
-      <c r="J7" s="408"/>
-      <c r="K7" s="408"/>
-      <c r="L7" s="408"/>
-      <c r="M7" s="408"/>
-      <c r="N7" s="408"/>
-      <c r="O7" s="408"/>
-      <c r="P7" s="408"/>
-      <c r="Q7" s="408"/>
-      <c r="R7" s="408"/>
-      <c r="S7" s="408"/>
-      <c r="T7" s="408"/>
-      <c r="U7" s="408"/>
+      <c r="J7" s="384"/>
+      <c r="K7" s="384"/>
+      <c r="L7" s="384"/>
+      <c r="M7" s="384"/>
+      <c r="N7" s="384"/>
+      <c r="O7" s="384"/>
+      <c r="P7" s="384"/>
+      <c r="Q7" s="384"/>
+      <c r="R7" s="384"/>
+      <c r="S7" s="384"/>
+      <c r="T7" s="384"/>
+      <c r="U7" s="384"/>
     </row>
     <row r="8" spans="10:25">
-      <c r="J8" s="408"/>
-      <c r="K8" s="408"/>
-      <c r="L8" s="408"/>
-      <c r="M8" s="408"/>
-      <c r="N8" s="408"/>
-      <c r="O8" s="408"/>
-      <c r="P8" s="408"/>
-      <c r="Q8" s="408"/>
-      <c r="R8" s="408"/>
-      <c r="S8" s="408"/>
-      <c r="T8" s="408"/>
-      <c r="U8" s="408"/>
+      <c r="J8" s="384"/>
+      <c r="K8" s="384"/>
+      <c r="L8" s="384"/>
+      <c r="M8" s="384"/>
+      <c r="N8" s="384"/>
+      <c r="O8" s="384"/>
+      <c r="P8" s="384"/>
+      <c r="Q8" s="384"/>
+      <c r="R8" s="384"/>
+      <c r="S8" s="384"/>
+      <c r="T8" s="384"/>
+      <c r="U8" s="384"/>
       <c r="V8" s="283"/>
       <c r="W8" s="283"/>
       <c r="X8" s="283"/>
@@ -6872,74 +6853,74 @@
     <row r="7" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="8" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="9" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q9" s="409" t="s">
-        <v>405</v>
-      </c>
-      <c r="R9" s="409"/>
-      <c r="S9" s="409"/>
-      <c r="T9" s="409"/>
-      <c r="U9" s="409"/>
-      <c r="V9" s="409"/>
-      <c r="W9" s="409"/>
-      <c r="X9" s="409"/>
-      <c r="Y9" s="409"/>
-      <c r="Z9" s="409"/>
-      <c r="AA9" s="409"/>
-      <c r="AB9" s="409"/>
-      <c r="AC9" s="409"/>
-      <c r="AD9" s="409"/>
-      <c r="AE9" s="409"/>
+      <c r="Q9" s="383" t="s">
+        <v>404</v>
+      </c>
+      <c r="R9" s="383"/>
+      <c r="S9" s="383"/>
+      <c r="T9" s="383"/>
+      <c r="U9" s="383"/>
+      <c r="V9" s="383"/>
+      <c r="W9" s="383"/>
+      <c r="X9" s="383"/>
+      <c r="Y9" s="383"/>
+      <c r="Z9" s="383"/>
+      <c r="AA9" s="383"/>
+      <c r="AB9" s="383"/>
+      <c r="AC9" s="383"/>
+      <c r="AD9" s="383"/>
+      <c r="AE9" s="383"/>
     </row>
     <row r="10" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q10" s="409"/>
-      <c r="R10" s="409"/>
-      <c r="S10" s="409"/>
-      <c r="T10" s="409"/>
-      <c r="U10" s="409"/>
-      <c r="V10" s="409"/>
-      <c r="W10" s="409"/>
-      <c r="X10" s="409"/>
-      <c r="Y10" s="409"/>
-      <c r="Z10" s="409"/>
-      <c r="AA10" s="409"/>
-      <c r="AB10" s="409"/>
-      <c r="AC10" s="409"/>
-      <c r="AD10" s="409"/>
-      <c r="AE10" s="409"/>
+      <c r="Q10" s="383"/>
+      <c r="R10" s="383"/>
+      <c r="S10" s="383"/>
+      <c r="T10" s="383"/>
+      <c r="U10" s="383"/>
+      <c r="V10" s="383"/>
+      <c r="W10" s="383"/>
+      <c r="X10" s="383"/>
+      <c r="Y10" s="383"/>
+      <c r="Z10" s="383"/>
+      <c r="AA10" s="383"/>
+      <c r="AB10" s="383"/>
+      <c r="AC10" s="383"/>
+      <c r="AD10" s="383"/>
+      <c r="AE10" s="383"/>
     </row>
     <row r="11" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q11" s="409"/>
-      <c r="R11" s="409"/>
-      <c r="S11" s="409"/>
-      <c r="T11" s="409"/>
-      <c r="U11" s="409"/>
-      <c r="V11" s="409"/>
-      <c r="W11" s="409"/>
-      <c r="X11" s="409"/>
-      <c r="Y11" s="409"/>
-      <c r="Z11" s="409"/>
-      <c r="AA11" s="409"/>
-      <c r="AB11" s="409"/>
-      <c r="AC11" s="409"/>
-      <c r="AD11" s="409"/>
-      <c r="AE11" s="409"/>
+      <c r="Q11" s="383"/>
+      <c r="R11" s="383"/>
+      <c r="S11" s="383"/>
+      <c r="T11" s="383"/>
+      <c r="U11" s="383"/>
+      <c r="V11" s="383"/>
+      <c r="W11" s="383"/>
+      <c r="X11" s="383"/>
+      <c r="Y11" s="383"/>
+      <c r="Z11" s="383"/>
+      <c r="AA11" s="383"/>
+      <c r="AB11" s="383"/>
+      <c r="AC11" s="383"/>
+      <c r="AD11" s="383"/>
+      <c r="AE11" s="383"/>
     </row>
     <row r="12" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q12" s="409"/>
-      <c r="R12" s="409"/>
-      <c r="S12" s="409"/>
-      <c r="T12" s="409"/>
-      <c r="U12" s="409"/>
-      <c r="V12" s="409"/>
-      <c r="W12" s="409"/>
-      <c r="X12" s="409"/>
-      <c r="Y12" s="409"/>
-      <c r="Z12" s="409"/>
-      <c r="AA12" s="409"/>
-      <c r="AB12" s="409"/>
-      <c r="AC12" s="409"/>
-      <c r="AD12" s="409"/>
-      <c r="AE12" s="409"/>
+      <c r="Q12" s="383"/>
+      <c r="R12" s="383"/>
+      <c r="S12" s="383"/>
+      <c r="T12" s="383"/>
+      <c r="U12" s="383"/>
+      <c r="V12" s="383"/>
+      <c r="W12" s="383"/>
+      <c r="X12" s="383"/>
+      <c r="Y12" s="383"/>
+      <c r="Z12" s="383"/>
+      <c r="AA12" s="383"/>
+      <c r="AB12" s="383"/>
+      <c r="AC12" s="383"/>
+      <c r="AD12" s="383"/>
+      <c r="AE12" s="383"/>
     </row>
     <row r="13" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="14" spans="17:31" ht="13.5" customHeight="1"/>
@@ -7953,54 +7934,54 @@
   <sheetData>
     <row r="4" spans="1:5" ht="14.4">
       <c r="A4" s="312" t="s">
-        <v>406</v>
-      </c>
-      <c r="B4" s="415" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="385" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="416"/>
+      <c r="C4" s="386"/>
       <c r="D4" s="289"/>
       <c r="E4" s="289"/>
     </row>
     <row r="5" spans="1:5" ht="14.4">
       <c r="A5" s="312" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" s="387" t="s">
         <v>407</v>
       </c>
-      <c r="B5" s="417" t="s">
-        <v>408</v>
-      </c>
-      <c r="C5" s="418"/>
+      <c r="C5" s="388"/>
       <c r="D5" s="289"/>
       <c r="E5" s="289"/>
     </row>
     <row r="6" spans="1:5" ht="14.4">
       <c r="A6" s="312" t="s">
-        <v>409</v>
-      </c>
-      <c r="B6" s="419" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" s="420"/>
+        <v>408</v>
+      </c>
+      <c r="B6" s="389" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="390"/>
       <c r="D6" s="289"/>
       <c r="E6" s="289"/>
     </row>
     <row r="7" spans="1:5" ht="14.4">
       <c r="A7" s="312" t="s">
-        <v>410</v>
-      </c>
-      <c r="B7" s="421">
+        <v>409</v>
+      </c>
+      <c r="B7" s="391">
         <v>46145</v>
       </c>
-      <c r="C7" s="422"/>
+      <c r="C7" s="392"/>
       <c r="D7" s="289"/>
       <c r="E7" s="289"/>
     </row>
     <row r="8" spans="1:5" ht="14.4">
       <c r="A8" s="312" t="s">
-        <v>411</v>
-      </c>
-      <c r="B8" s="419"/>
-      <c r="C8" s="420"/>
+        <v>410</v>
+      </c>
+      <c r="B8" s="389"/>
+      <c r="C8" s="390"/>
       <c r="D8" s="289"/>
       <c r="E8" s="289"/>
     </row>
@@ -8026,39 +8007,39 @@
       <c r="E11" s="289"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="410" t="s">
+      <c r="A12" s="393" t="s">
+        <v>411</v>
+      </c>
+      <c r="B12" s="395" t="s">
         <v>412</v>
       </c>
-      <c r="B12" s="412" t="s">
+      <c r="C12" s="397" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="414" t="s">
+      <c r="D12" s="395" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="412" t="s">
+      <c r="E12" s="395" t="s">
         <v>415</v>
       </c>
-      <c r="E12" s="412" t="s">
-        <v>416</v>
-      </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="411"/>
-      <c r="B13" s="413"/>
-      <c r="C13" s="413"/>
-      <c r="D13" s="413"/>
-      <c r="E13" s="413"/>
+      <c r="A13" s="394"/>
+      <c r="B13" s="396"/>
+      <c r="C13" s="396"/>
+      <c r="D13" s="396"/>
+      <c r="E13" s="396"/>
     </row>
     <row r="14" spans="1:5" ht="14.4">
       <c r="A14" s="295" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B14" s="296"/>
       <c r="C14" s="311" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D14" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E14" s="296">
         <v>1</v>
@@ -8073,14 +8054,14 @@
     </row>
     <row r="16" spans="1:5" ht="14.4">
       <c r="A16" s="295" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B16" s="296"/>
       <c r="C16" s="297" t="s">
+        <v>417</v>
+      </c>
+      <c r="D16" s="298" t="s">
         <v>418</v>
-      </c>
-      <c r="D16" s="298" t="s">
-        <v>419</v>
       </c>
       <c r="E16" s="296">
         <v>35</v>
@@ -8088,14 +8069,14 @@
     </row>
     <row r="17" spans="1:5" ht="14.4">
       <c r="A17" s="299" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B17" s="300"/>
       <c r="C17" s="301" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D17" s="302" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E17" s="300">
         <v>3</v>
@@ -8103,14 +8084,14 @@
     </row>
     <row r="18" spans="1:5" ht="14.4">
       <c r="A18" s="295" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B18" s="296"/>
       <c r="C18" s="297" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D18" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E18" s="296">
         <v>17</v>
@@ -8118,14 +8099,14 @@
     </row>
     <row r="19" spans="1:5" ht="14.4">
       <c r="A19" s="299" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B19" s="296"/>
       <c r="C19" s="297" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D19" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E19" s="296">
         <v>12</v>
@@ -8140,14 +8121,14 @@
     </row>
     <row r="21" spans="1:5" ht="14.4">
       <c r="A21" s="295" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B21" s="296"/>
       <c r="C21" s="297" t="s">
+        <v>427</v>
+      </c>
+      <c r="D21" s="298" t="s">
         <v>428</v>
-      </c>
-      <c r="D21" s="298" t="s">
-        <v>429</v>
       </c>
       <c r="E21" s="296">
         <v>7</v>
@@ -8162,14 +8143,14 @@
     </row>
     <row r="23" spans="1:5" ht="14.4">
       <c r="A23" s="295" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B23" s="296"/>
       <c r="C23" s="297" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D23" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E23" s="296">
         <v>11</v>
@@ -8177,14 +8158,14 @@
     </row>
     <row r="24" spans="1:5" ht="14.4">
       <c r="A24" s="295" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B24" s="296"/>
       <c r="C24" s="297" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D24" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E24" s="296">
         <v>5</v>
@@ -8192,14 +8173,14 @@
     </row>
     <row r="25" spans="1:5" ht="14.4">
       <c r="A25" s="295" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B25" s="296"/>
       <c r="C25" s="297" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D25" s="298" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E25" s="296">
         <v>7</v>
@@ -8207,16 +8188,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
   </mergeCells>
   <phoneticPr fontId="62" type="noConversion"/>
   <hyperlinks>
@@ -8253,10 +8234,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="29.25" customHeight="1">
-      <c r="A1" s="441" t="s">
+      <c r="A1" s="429" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="442"/>
+      <c r="B1" s="430"/>
       <c r="C1" s="234" t="s">
         <v>117</v>
       </c>
@@ -8276,10 +8257,10 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="443" t="s">
+      <c r="L1" s="431" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="444"/>
+      <c r="M1" s="432"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -8298,10 +8279,10 @@
       <c r="AC1" s="3"/>
     </row>
     <row r="2" spans="1:29" ht="32.25" customHeight="1">
-      <c r="A2" s="441" t="s">
+      <c r="A2" s="429" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="442"/>
+      <c r="B2" s="430"/>
       <c r="C2" s="235" t="s">
         <v>118</v>
       </c>
@@ -8346,16 +8327,16 @@
       <c r="AC2" s="3"/>
     </row>
     <row r="3" spans="1:29" ht="33" customHeight="1">
-      <c r="A3" s="441" t="s">
+      <c r="A3" s="429" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="442"/>
+      <c r="B3" s="430"/>
       <c r="C3" s="4"/>
       <c r="D3" s="231" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>10</v>
@@ -8392,16 +8373,16 @@
       <c r="AC3" s="3"/>
     </row>
     <row r="4" spans="1:29" ht="34.5" customHeight="1">
-      <c r="A4" s="441" t="s">
+      <c r="A4" s="429" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="442"/>
+      <c r="B4" s="430"/>
       <c r="C4" s="4"/>
       <c r="D4" s="231" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>15</v>
@@ -8438,15 +8419,15 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" ht="31.5" customHeight="1">
-      <c r="A5" s="450" t="s">
+      <c r="A5" s="411" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="398"/>
-      <c r="C5" s="445"/>
-      <c r="D5" s="397"/>
-      <c r="E5" s="397"/>
-      <c r="F5" s="397"/>
-      <c r="G5" s="398"/>
+      <c r="B5" s="400"/>
+      <c r="C5" s="398"/>
+      <c r="D5" s="399"/>
+      <c r="E5" s="399"/>
+      <c r="F5" s="399"/>
+      <c r="G5" s="400"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -8650,13 +8631,13 @@
       <c r="A10" s="32">
         <v>2</v>
       </c>
-      <c r="B10" s="446" t="s">
+      <c r="B10" s="401" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="430" t="s">
+      <c r="C10" s="426" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="451" t="s">
+      <c r="D10" s="415" t="s">
         <v>119</v>
       </c>
       <c r="E10" s="244" t="s">
@@ -8701,9 +8682,9 @@
       <c r="A11" s="32">
         <v>3</v>
       </c>
-      <c r="B11" s="447"/>
-      <c r="C11" s="431"/>
-      <c r="D11" s="452"/>
+      <c r="B11" s="402"/>
+      <c r="C11" s="427"/>
+      <c r="D11" s="416"/>
       <c r="E11" s="244" t="s">
         <v>124</v>
       </c>
@@ -8746,9 +8727,9 @@
       <c r="A12" s="32">
         <v>4</v>
       </c>
-      <c r="B12" s="447"/>
-      <c r="C12" s="431"/>
-      <c r="D12" s="452"/>
+      <c r="B12" s="402"/>
+      <c r="C12" s="427"/>
+      <c r="D12" s="416"/>
       <c r="E12" s="244" t="s">
         <v>127</v>
       </c>
@@ -8791,9 +8772,9 @@
       <c r="A13" s="32">
         <v>5</v>
       </c>
-      <c r="B13" s="447"/>
-      <c r="C13" s="431"/>
-      <c r="D13" s="452"/>
+      <c r="B13" s="402"/>
+      <c r="C13" s="427"/>
+      <c r="D13" s="416"/>
       <c r="E13" s="244" t="s">
         <v>131</v>
       </c>
@@ -8836,9 +8817,9 @@
       <c r="A14" s="32">
         <v>6</v>
       </c>
-      <c r="B14" s="447"/>
-      <c r="C14" s="431"/>
-      <c r="D14" s="452"/>
+      <c r="B14" s="402"/>
+      <c r="C14" s="427"/>
+      <c r="D14" s="416"/>
       <c r="E14" s="244" t="s">
         <v>136</v>
       </c>
@@ -8881,9 +8862,9 @@
       <c r="A15" s="32">
         <v>7</v>
       </c>
-      <c r="B15" s="447"/>
-      <c r="C15" s="431"/>
-      <c r="D15" s="452"/>
+      <c r="B15" s="402"/>
+      <c r="C15" s="427"/>
+      <c r="D15" s="416"/>
       <c r="E15" s="244" t="s">
         <v>142</v>
       </c>
@@ -8900,7 +8881,7 @@
         <v>145</v>
       </c>
       <c r="J15" s="266" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K15" s="37"/>
       <c r="L15" s="34" t="s">
@@ -8928,9 +8909,9 @@
       <c r="A16" s="32">
         <v>8</v>
       </c>
-      <c r="B16" s="447"/>
-      <c r="C16" s="431"/>
-      <c r="D16" s="452"/>
+      <c r="B16" s="402"/>
+      <c r="C16" s="427"/>
+      <c r="D16" s="416"/>
       <c r="E16" s="244" t="s">
         <v>147</v>
       </c>
@@ -8973,9 +8954,9 @@
       <c r="A17" s="32">
         <v>9</v>
       </c>
-      <c r="B17" s="447"/>
-      <c r="C17" s="431"/>
-      <c r="D17" s="452"/>
+      <c r="B17" s="402"/>
+      <c r="C17" s="427"/>
+      <c r="D17" s="416"/>
       <c r="E17" s="244" t="s">
         <v>155</v>
       </c>
@@ -9018,9 +8999,9 @@
       <c r="A18" s="32">
         <v>10</v>
       </c>
-      <c r="B18" s="447"/>
-      <c r="C18" s="431"/>
-      <c r="D18" s="452"/>
+      <c r="B18" s="402"/>
+      <c r="C18" s="427"/>
+      <c r="D18" s="416"/>
       <c r="E18" s="244" t="s">
         <v>159</v>
       </c>
@@ -9063,9 +9044,9 @@
       <c r="A19" s="32">
         <v>11</v>
       </c>
-      <c r="B19" s="447"/>
-      <c r="C19" s="431"/>
-      <c r="D19" s="452"/>
+      <c r="B19" s="402"/>
+      <c r="C19" s="427"/>
+      <c r="D19" s="416"/>
       <c r="E19" s="244" t="s">
         <v>193</v>
       </c>
@@ -9108,9 +9089,9 @@
       <c r="A20" s="32">
         <v>12</v>
       </c>
-      <c r="B20" s="447"/>
-      <c r="C20" s="431"/>
-      <c r="D20" s="452"/>
+      <c r="B20" s="402"/>
+      <c r="C20" s="427"/>
+      <c r="D20" s="416"/>
       <c r="E20" s="244" t="s">
         <v>195</v>
       </c>
@@ -9153,9 +9134,9 @@
       <c r="A21" s="32">
         <v>13</v>
       </c>
-      <c r="B21" s="447"/>
-      <c r="C21" s="431"/>
-      <c r="D21" s="452"/>
+      <c r="B21" s="402"/>
+      <c r="C21" s="427"/>
+      <c r="D21" s="416"/>
       <c r="E21" s="244" t="s">
         <v>200</v>
       </c>
@@ -9198,9 +9179,9 @@
       <c r="A22" s="32">
         <v>14</v>
       </c>
-      <c r="B22" s="447"/>
-      <c r="C22" s="431"/>
-      <c r="D22" s="452"/>
+      <c r="B22" s="402"/>
+      <c r="C22" s="427"/>
+      <c r="D22" s="416"/>
       <c r="E22" s="244" t="s">
         <v>204</v>
       </c>
@@ -9243,9 +9224,9 @@
       <c r="A23" s="32">
         <v>15</v>
       </c>
-      <c r="B23" s="447"/>
-      <c r="C23" s="431"/>
-      <c r="D23" s="452"/>
+      <c r="B23" s="402"/>
+      <c r="C23" s="427"/>
+      <c r="D23" s="416"/>
       <c r="E23" s="238" t="s">
         <v>190</v>
       </c>
@@ -9288,9 +9269,9 @@
       <c r="A24" s="32">
         <v>16</v>
       </c>
-      <c r="B24" s="447"/>
-      <c r="C24" s="431"/>
-      <c r="D24" s="452"/>
+      <c r="B24" s="402"/>
+      <c r="C24" s="427"/>
+      <c r="D24" s="416"/>
       <c r="E24" s="242" t="s">
         <v>167</v>
       </c>
@@ -9333,9 +9314,9 @@
       <c r="A25" s="32">
         <v>17</v>
       </c>
-      <c r="B25" s="447"/>
-      <c r="C25" s="431"/>
-      <c r="D25" s="452"/>
+      <c r="B25" s="402"/>
+      <c r="C25" s="427"/>
+      <c r="D25" s="416"/>
       <c r="E25" s="242" t="s">
         <v>172</v>
       </c>
@@ -9378,9 +9359,9 @@
       <c r="A26" s="32">
         <v>18</v>
       </c>
-      <c r="B26" s="447"/>
-      <c r="C26" s="431"/>
-      <c r="D26" s="452"/>
+      <c r="B26" s="402"/>
+      <c r="C26" s="427"/>
+      <c r="D26" s="416"/>
       <c r="E26" s="242" t="s">
         <v>177</v>
       </c>
@@ -9423,9 +9404,9 @@
       <c r="A27" s="32">
         <v>19</v>
       </c>
-      <c r="B27" s="447"/>
-      <c r="C27" s="431"/>
-      <c r="D27" s="452"/>
+      <c r="B27" s="402"/>
+      <c r="C27" s="427"/>
+      <c r="D27" s="416"/>
       <c r="E27" s="242" t="s">
         <v>182</v>
       </c>
@@ -9468,9 +9449,9 @@
       <c r="A28" s="32">
         <v>20</v>
       </c>
-      <c r="B28" s="447"/>
-      <c r="C28" s="431"/>
-      <c r="D28" s="452"/>
+      <c r="B28" s="402"/>
+      <c r="C28" s="427"/>
+      <c r="D28" s="416"/>
       <c r="E28" s="242" t="s">
         <v>183</v>
       </c>
@@ -9513,9 +9494,9 @@
       <c r="A29" s="32">
         <v>21</v>
       </c>
-      <c r="B29" s="447"/>
-      <c r="C29" s="431"/>
-      <c r="D29" s="452"/>
+      <c r="B29" s="402"/>
+      <c r="C29" s="427"/>
+      <c r="D29" s="416"/>
       <c r="E29" s="242" t="s">
         <v>211</v>
       </c>
@@ -9558,9 +9539,9 @@
       <c r="A30" s="32">
         <v>22</v>
       </c>
-      <c r="B30" s="447"/>
-      <c r="C30" s="431"/>
-      <c r="D30" s="452"/>
+      <c r="B30" s="402"/>
+      <c r="C30" s="427"/>
+      <c r="D30" s="416"/>
       <c r="E30" s="242" t="s">
         <v>212</v>
       </c>
@@ -9603,9 +9584,9 @@
       <c r="A31" s="32">
         <v>23</v>
       </c>
-      <c r="B31" s="447"/>
-      <c r="C31" s="431"/>
-      <c r="D31" s="452"/>
+      <c r="B31" s="402"/>
+      <c r="C31" s="427"/>
+      <c r="D31" s="416"/>
       <c r="E31" s="242" t="s">
         <v>215</v>
       </c>
@@ -9648,9 +9629,9 @@
       <c r="A32" s="32">
         <v>24</v>
       </c>
-      <c r="B32" s="447"/>
-      <c r="C32" s="431"/>
-      <c r="D32" s="452"/>
+      <c r="B32" s="402"/>
+      <c r="C32" s="427"/>
+      <c r="D32" s="416"/>
       <c r="E32" s="242" t="s">
         <v>220</v>
       </c>
@@ -9664,7 +9645,7 @@
         <v>223</v>
       </c>
       <c r="I32" s="240" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J32" s="39"/>
       <c r="K32" s="37"/>
@@ -9693,9 +9674,9 @@
       <c r="A33" s="32">
         <v>25</v>
       </c>
-      <c r="B33" s="447"/>
-      <c r="C33" s="431"/>
-      <c r="D33" s="452"/>
+      <c r="B33" s="402"/>
+      <c r="C33" s="427"/>
+      <c r="D33" s="416"/>
       <c r="E33" s="242" t="s">
         <v>225</v>
       </c>
@@ -9709,7 +9690,7 @@
         <v>228</v>
       </c>
       <c r="I33" s="240" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J33" s="39"/>
       <c r="K33" s="37"/>
@@ -9738,9 +9719,9 @@
       <c r="A34" s="32">
         <v>26</v>
       </c>
-      <c r="B34" s="447"/>
-      <c r="C34" s="431"/>
-      <c r="D34" s="452"/>
+      <c r="B34" s="402"/>
+      <c r="C34" s="427"/>
+      <c r="D34" s="416"/>
       <c r="E34" s="242" t="s">
         <v>229</v>
       </c>
@@ -9783,9 +9764,9 @@
       <c r="A35" s="32">
         <v>27</v>
       </c>
-      <c r="B35" s="447"/>
-      <c r="C35" s="431"/>
-      <c r="D35" s="452"/>
+      <c r="B35" s="402"/>
+      <c r="C35" s="427"/>
+      <c r="D35" s="416"/>
       <c r="E35" s="242" t="s">
         <v>233</v>
       </c>
@@ -9828,9 +9809,9 @@
       <c r="A36" s="32">
         <v>28</v>
       </c>
-      <c r="B36" s="447"/>
-      <c r="C36" s="431"/>
-      <c r="D36" s="452"/>
+      <c r="B36" s="402"/>
+      <c r="C36" s="427"/>
+      <c r="D36" s="416"/>
       <c r="E36" s="242" t="s">
         <v>237</v>
       </c>
@@ -9844,7 +9825,7 @@
         <v>240</v>
       </c>
       <c r="I36" s="240" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J36" s="39"/>
       <c r="K36" s="37"/>
@@ -9873,9 +9854,9 @@
       <c r="A37" s="32">
         <v>29</v>
       </c>
-      <c r="B37" s="447"/>
-      <c r="C37" s="431"/>
-      <c r="D37" s="452"/>
+      <c r="B37" s="402"/>
+      <c r="C37" s="427"/>
+      <c r="D37" s="416"/>
       <c r="E37" s="242" t="s">
         <v>241</v>
       </c>
@@ -9918,9 +9899,9 @@
       <c r="A38" s="32">
         <v>30</v>
       </c>
-      <c r="B38" s="447"/>
-      <c r="C38" s="431"/>
-      <c r="D38" s="452"/>
+      <c r="B38" s="402"/>
+      <c r="C38" s="427"/>
+      <c r="D38" s="416"/>
       <c r="E38" s="242" t="s">
         <v>246</v>
       </c>
@@ -9965,9 +9946,9 @@
       <c r="A39" s="32">
         <v>31</v>
       </c>
-      <c r="B39" s="447"/>
-      <c r="C39" s="431"/>
-      <c r="D39" s="452"/>
+      <c r="B39" s="402"/>
+      <c r="C39" s="427"/>
+      <c r="D39" s="416"/>
       <c r="E39" s="242" t="s">
         <v>249</v>
       </c>
@@ -9984,7 +9965,7 @@
         <v>232</v>
       </c>
       <c r="J39" s="266" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K39" s="37"/>
       <c r="L39" s="247" t="s">
@@ -10012,9 +9993,9 @@
       <c r="A40" s="32">
         <v>32</v>
       </c>
-      <c r="B40" s="447"/>
-      <c r="C40" s="431"/>
-      <c r="D40" s="452"/>
+      <c r="B40" s="402"/>
+      <c r="C40" s="427"/>
+      <c r="D40" s="416"/>
       <c r="E40" s="242" t="s">
         <v>252</v>
       </c>
@@ -10057,9 +10038,9 @@
       <c r="A41" s="32">
         <v>33</v>
       </c>
-      <c r="B41" s="447"/>
-      <c r="C41" s="431"/>
-      <c r="D41" s="452"/>
+      <c r="B41" s="402"/>
+      <c r="C41" s="427"/>
+      <c r="D41" s="416"/>
       <c r="E41" s="242" t="s">
         <v>254</v>
       </c>
@@ -10073,7 +10054,7 @@
         <v>261</v>
       </c>
       <c r="I41" s="240" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J41" s="39"/>
       <c r="K41" s="37"/>
@@ -10102,9 +10083,9 @@
       <c r="A42" s="32">
         <v>34</v>
       </c>
-      <c r="B42" s="447"/>
-      <c r="C42" s="431"/>
-      <c r="D42" s="452"/>
+      <c r="B42" s="402"/>
+      <c r="C42" s="427"/>
+      <c r="D42" s="416"/>
       <c r="E42" s="242" t="s">
         <v>262</v>
       </c>
@@ -10118,7 +10099,7 @@
         <v>265</v>
       </c>
       <c r="I42" s="240" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J42" s="39"/>
       <c r="K42" s="37"/>
@@ -10147,9 +10128,9 @@
       <c r="A43" s="32">
         <v>35</v>
       </c>
-      <c r="B43" s="447"/>
-      <c r="C43" s="431"/>
-      <c r="D43" s="452"/>
+      <c r="B43" s="402"/>
+      <c r="C43" s="427"/>
+      <c r="D43" s="416"/>
       <c r="E43" s="242" t="s">
         <v>266</v>
       </c>
@@ -10163,7 +10144,7 @@
         <v>269</v>
       </c>
       <c r="I43" s="240" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J43" s="39"/>
       <c r="K43" s="37"/>
@@ -10192,9 +10173,9 @@
       <c r="A44" s="32">
         <v>36</v>
       </c>
-      <c r="B44" s="447"/>
-      <c r="C44" s="431"/>
-      <c r="D44" s="453"/>
+      <c r="B44" s="402"/>
+      <c r="C44" s="427"/>
+      <c r="D44" s="417"/>
       <c r="E44" s="242" t="s">
         <v>270</v>
       </c>
@@ -10208,10 +10189,10 @@
         <v>265</v>
       </c>
       <c r="I44" s="240" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J44" s="267" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K44" s="37"/>
       <c r="L44" s="23" t="s">
@@ -10237,8 +10218,8 @@
     </row>
     <row r="45" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A45" s="348"/>
-      <c r="B45" s="447"/>
-      <c r="C45" s="431"/>
+      <c r="B45" s="402"/>
+      <c r="C45" s="427"/>
       <c r="D45" s="356"/>
       <c r="E45" s="314"/>
       <c r="F45" s="316"/>
@@ -10270,25 +10251,25 @@
       <c r="A46" s="370">
         <v>37</v>
       </c>
-      <c r="B46" s="394"/>
-      <c r="C46" s="431"/>
-      <c r="D46" s="492" t="s">
+      <c r="B46" s="403"/>
+      <c r="C46" s="427"/>
+      <c r="D46" s="443" t="s">
+        <v>430</v>
+      </c>
+      <c r="E46" s="342" t="s">
         <v>431</v>
       </c>
-      <c r="E46" s="342" t="s">
+      <c r="F46" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="G46" s="342" t="s">
         <v>432</v>
       </c>
-      <c r="F46" s="342" t="s">
+      <c r="H46" s="342" t="s">
+        <v>436</v>
+      </c>
+      <c r="I46" s="240" t="s">
         <v>434</v>
-      </c>
-      <c r="G46" s="342" t="s">
-        <v>433</v>
-      </c>
-      <c r="H46" s="342" t="s">
-        <v>437</v>
-      </c>
-      <c r="I46" s="240" t="s">
-        <v>435</v>
       </c>
       <c r="J46" s="342"/>
       <c r="K46" s="342"/>
@@ -10317,23 +10298,23 @@
       <c r="A47" s="370">
         <v>38</v>
       </c>
-      <c r="B47" s="394"/>
-      <c r="C47" s="431"/>
-      <c r="D47" s="493"/>
+      <c r="B47" s="403"/>
+      <c r="C47" s="427"/>
+      <c r="D47" s="444"/>
       <c r="E47" s="343" t="s">
+        <v>437</v>
+      </c>
+      <c r="F47" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="G47" s="347" t="s">
+        <v>435</v>
+      </c>
+      <c r="H47" s="342" t="s">
         <v>438</v>
       </c>
-      <c r="F47" s="344" t="s">
-        <v>442</v>
-      </c>
-      <c r="G47" s="347" t="s">
-        <v>436</v>
-      </c>
-      <c r="H47" s="342" t="s">
-        <v>439</v>
-      </c>
       <c r="I47" s="240" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J47" s="342"/>
       <c r="K47" s="342"/>
@@ -10362,23 +10343,23 @@
       <c r="A48" s="370">
         <v>39</v>
       </c>
-      <c r="B48" s="394"/>
-      <c r="C48" s="431"/>
-      <c r="D48" s="494"/>
+      <c r="B48" s="403"/>
+      <c r="C48" s="427"/>
+      <c r="D48" s="445"/>
       <c r="E48" s="345" t="s">
+        <v>439</v>
+      </c>
+      <c r="F48" s="345" t="s">
         <v>440</v>
       </c>
-      <c r="F48" s="345" t="s">
-        <v>441</v>
-      </c>
       <c r="G48" s="345" t="s">
+        <v>442</v>
+      </c>
+      <c r="H48" s="345" t="s">
         <v>443</v>
       </c>
-      <c r="H48" s="345" t="s">
-        <v>444</v>
-      </c>
       <c r="I48" s="362" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J48" s="346"/>
       <c r="K48" s="345"/>
@@ -10405,8 +10386,8 @@
     </row>
     <row r="49" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A49" s="348"/>
-      <c r="B49" s="394"/>
-      <c r="C49" s="431"/>
+      <c r="B49" s="403"/>
+      <c r="C49" s="427"/>
       <c r="D49" s="356"/>
       <c r="E49" s="361"/>
       <c r="F49" s="361"/>
@@ -10438,28 +10419,28 @@
       <c r="A50" s="371">
         <v>40</v>
       </c>
-      <c r="B50" s="447"/>
-      <c r="C50" s="431"/>
-      <c r="D50" s="428" t="s">
+      <c r="B50" s="402"/>
+      <c r="C50" s="427"/>
+      <c r="D50" s="446" t="s">
         <v>273</v>
       </c>
       <c r="E50" s="315" t="s">
+        <v>276</v>
+      </c>
+      <c r="F50" s="317" t="s">
+        <v>275</v>
+      </c>
+      <c r="G50" s="317" t="s">
         <v>277</v>
-      </c>
-      <c r="F50" s="317" t="s">
-        <v>276</v>
-      </c>
-      <c r="G50" s="317" t="s">
-        <v>278</v>
       </c>
       <c r="H50" s="318" t="s">
         <v>41</v>
       </c>
       <c r="I50" s="320" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J50" s="268" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K50" s="322"/>
       <c r="L50" s="324" t="s">
@@ -10487,26 +10468,26 @@
       <c r="A51" s="23">
         <v>41</v>
       </c>
-      <c r="B51" s="447"/>
-      <c r="C51" s="431"/>
-      <c r="D51" s="429"/>
+      <c r="B51" s="402"/>
+      <c r="C51" s="427"/>
+      <c r="D51" s="447"/>
       <c r="E51" s="253" t="s">
+        <v>279</v>
+      </c>
+      <c r="F51" s="255" t="s">
         <v>280</v>
       </c>
-      <c r="F51" s="255" t="s">
+      <c r="G51" s="252" t="s">
         <v>281</v>
-      </c>
-      <c r="G51" s="252" t="s">
-        <v>282</v>
       </c>
       <c r="H51" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I51" s="240" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J51" s="268" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K51" s="46"/>
       <c r="L51" s="247" t="s">
@@ -10534,23 +10515,23 @@
       <c r="A52" s="371">
         <v>42</v>
       </c>
-      <c r="B52" s="447"/>
-      <c r="C52" s="431"/>
-      <c r="D52" s="429"/>
+      <c r="B52" s="402"/>
+      <c r="C52" s="427"/>
+      <c r="D52" s="447"/>
       <c r="E52" s="253" t="s">
+        <v>316</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="G52" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="F52" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="G52" s="20" t="s">
+      <c r="H52" s="260" t="s">
+        <v>319</v>
+      </c>
+      <c r="I52" s="240" t="s">
         <v>318</v>
-      </c>
-      <c r="H52" s="260" t="s">
-        <v>320</v>
-      </c>
-      <c r="I52" s="240" t="s">
-        <v>319</v>
       </c>
       <c r="J52" s="44"/>
       <c r="K52" s="46"/>
@@ -10579,26 +10560,26 @@
       <c r="A53" s="23">
         <v>43</v>
       </c>
-      <c r="B53" s="447"/>
-      <c r="C53" s="431"/>
-      <c r="D53" s="429"/>
+      <c r="B53" s="402"/>
+      <c r="C53" s="427"/>
+      <c r="D53" s="447"/>
       <c r="E53" s="253" t="s">
+        <v>282</v>
+      </c>
+      <c r="F53" s="255" t="s">
         <v>283</v>
       </c>
-      <c r="F53" s="255" t="s">
+      <c r="G53" s="252" t="s">
         <v>284</v>
-      </c>
-      <c r="G53" s="252" t="s">
-        <v>285</v>
       </c>
       <c r="H53" s="258">
         <v>12345</v>
       </c>
       <c r="I53" s="240" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J53" s="268" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K53" s="46"/>
       <c r="L53" s="23" t="s">
@@ -10626,26 +10607,26 @@
       <c r="A54" s="371">
         <v>44</v>
       </c>
-      <c r="B54" s="447"/>
-      <c r="C54" s="431"/>
-      <c r="D54" s="429"/>
+      <c r="B54" s="402"/>
+      <c r="C54" s="427"/>
+      <c r="D54" s="447"/>
       <c r="E54" s="253" t="s">
+        <v>286</v>
+      </c>
+      <c r="F54" s="255" t="s">
         <v>287</v>
       </c>
-      <c r="F54" s="255" t="s">
+      <c r="G54" s="257" t="s">
+        <v>303</v>
+      </c>
+      <c r="H54" s="259" t="s">
         <v>288</v>
       </c>
-      <c r="G54" s="257" t="s">
-        <v>304</v>
-      </c>
-      <c r="H54" s="259" t="s">
+      <c r="I54" s="242" t="s">
         <v>289</v>
       </c>
-      <c r="I54" s="242" t="s">
-        <v>290</v>
-      </c>
       <c r="J54" s="268" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K54" s="52"/>
       <c r="L54" s="23" t="s">
@@ -10673,26 +10654,26 @@
       <c r="A55" s="23">
         <v>45</v>
       </c>
-      <c r="B55" s="447"/>
-      <c r="C55" s="431"/>
-      <c r="D55" s="429"/>
+      <c r="B55" s="402"/>
+      <c r="C55" s="427"/>
+      <c r="D55" s="447"/>
       <c r="E55" s="253" t="s">
+        <v>290</v>
+      </c>
+      <c r="F55" s="255" t="s">
         <v>291</v>
       </c>
-      <c r="F55" s="255" t="s">
+      <c r="G55" s="252" t="s">
+        <v>302</v>
+      </c>
+      <c r="H55" s="256" t="s">
         <v>292</v>
       </c>
-      <c r="G55" s="252" t="s">
-        <v>303</v>
-      </c>
-      <c r="H55" s="256" t="s">
+      <c r="I55" s="240" t="s">
         <v>293</v>
       </c>
-      <c r="I55" s="240" t="s">
-        <v>294</v>
-      </c>
       <c r="J55" s="268" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K55" s="46"/>
       <c r="L55" s="23" t="s">
@@ -10720,26 +10701,26 @@
       <c r="A56" s="371">
         <v>46</v>
       </c>
-      <c r="B56" s="447"/>
-      <c r="C56" s="431"/>
-      <c r="D56" s="429"/>
+      <c r="B56" s="402"/>
+      <c r="C56" s="427"/>
+      <c r="D56" s="447"/>
       <c r="E56" s="253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F56" s="255" t="s">
+        <v>294</v>
+      </c>
+      <c r="G56" s="252" t="s">
+        <v>296</v>
+      </c>
+      <c r="H56" s="252" t="s">
         <v>295</v>
       </c>
-      <c r="G56" s="252" t="s">
+      <c r="I56" s="240" t="s">
         <v>297</v>
       </c>
-      <c r="H56" s="252" t="s">
-        <v>296</v>
-      </c>
-      <c r="I56" s="240" t="s">
-        <v>298</v>
-      </c>
       <c r="J56" s="269" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K56" s="46"/>
       <c r="L56" s="23" t="s">
@@ -10767,26 +10748,26 @@
       <c r="A57" s="23">
         <v>47</v>
       </c>
-      <c r="B57" s="447"/>
-      <c r="C57" s="431"/>
-      <c r="D57" s="429"/>
+      <c r="B57" s="402"/>
+      <c r="C57" s="427"/>
+      <c r="D57" s="447"/>
       <c r="E57" s="253" t="s">
+        <v>299</v>
+      </c>
+      <c r="F57" s="255" t="s">
         <v>300</v>
       </c>
-      <c r="F57" s="255" t="s">
+      <c r="G57" s="252" t="s">
         <v>301</v>
       </c>
-      <c r="G57" s="252" t="s">
-        <v>302</v>
-      </c>
       <c r="H57" s="252" t="s">
+        <v>304</v>
+      </c>
+      <c r="I57" s="240" t="s">
         <v>305</v>
       </c>
-      <c r="I57" s="240" t="s">
-        <v>306</v>
-      </c>
       <c r="J57" s="268" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K57" s="46"/>
       <c r="L57" s="23" t="s">
@@ -10814,23 +10795,23 @@
       <c r="A58" s="371">
         <v>48</v>
       </c>
-      <c r="B58" s="447"/>
-      <c r="C58" s="431"/>
-      <c r="D58" s="429"/>
+      <c r="B58" s="402"/>
+      <c r="C58" s="427"/>
+      <c r="D58" s="447"/>
       <c r="E58" s="253" t="s">
+        <v>306</v>
+      </c>
+      <c r="F58" s="255" t="s">
         <v>307</v>
       </c>
-      <c r="F58" s="255" t="s">
+      <c r="G58" s="252" t="s">
         <v>308</v>
       </c>
-      <c r="G58" s="252" t="s">
+      <c r="H58" s="252" t="s">
         <v>309</v>
       </c>
-      <c r="H58" s="252" t="s">
+      <c r="I58" s="240" t="s">
         <v>310</v>
-      </c>
-      <c r="I58" s="240" t="s">
-        <v>311</v>
       </c>
       <c r="J58" s="51"/>
       <c r="K58" s="46"/>
@@ -10859,23 +10840,23 @@
       <c r="A59" s="23">
         <v>49</v>
       </c>
-      <c r="B59" s="447"/>
-      <c r="C59" s="431"/>
-      <c r="D59" s="429"/>
+      <c r="B59" s="402"/>
+      <c r="C59" s="427"/>
+      <c r="D59" s="447"/>
       <c r="E59" s="253" t="s">
+        <v>311</v>
+      </c>
+      <c r="F59" s="255" t="s">
         <v>312</v>
       </c>
-      <c r="F59" s="255" t="s">
+      <c r="G59" s="44" t="s">
         <v>313</v>
-      </c>
-      <c r="G59" s="44" t="s">
-        <v>314</v>
       </c>
       <c r="H59" s="262" t="s">
         <v>170</v>
       </c>
       <c r="I59" s="240" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J59" s="44"/>
       <c r="K59" s="46"/>
@@ -10904,9 +10885,9 @@
       <c r="A60" s="371">
         <v>50</v>
       </c>
-      <c r="B60" s="447"/>
-      <c r="C60" s="431"/>
-      <c r="D60" s="429"/>
+      <c r="B60" s="402"/>
+      <c r="C60" s="427"/>
+      <c r="D60" s="447"/>
       <c r="E60" s="43" t="s">
         <v>195</v>
       </c>
@@ -10920,7 +10901,7 @@
         <v>198</v>
       </c>
       <c r="I60" s="242" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J60" s="44"/>
       <c r="K60" s="46"/>
@@ -10949,9 +10930,9 @@
       <c r="A61" s="23">
         <v>51</v>
       </c>
-      <c r="B61" s="447"/>
-      <c r="C61" s="431"/>
-      <c r="D61" s="429"/>
+      <c r="B61" s="402"/>
+      <c r="C61" s="427"/>
+      <c r="D61" s="447"/>
       <c r="E61" s="50" t="s">
         <v>200</v>
       </c>
@@ -10959,13 +10940,13 @@
         <v>201</v>
       </c>
       <c r="G61" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H61" s="245" t="s">
         <v>203</v>
       </c>
       <c r="I61" s="240" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J61" s="51"/>
       <c r="K61" s="46"/>
@@ -10994,23 +10975,23 @@
       <c r="A62" s="371">
         <v>52</v>
       </c>
-      <c r="B62" s="447"/>
-      <c r="C62" s="431"/>
-      <c r="D62" s="429"/>
+      <c r="B62" s="402"/>
+      <c r="C62" s="427"/>
+      <c r="D62" s="447"/>
       <c r="E62" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="F62" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="F62" s="49" t="s">
+      <c r="G62" s="44" t="s">
         <v>325</v>
-      </c>
-      <c r="G62" s="44" t="s">
-        <v>326</v>
       </c>
       <c r="H62" s="44" t="s">
         <v>41</v>
       </c>
       <c r="I62" s="240" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J62" s="44"/>
       <c r="K62" s="46"/>
@@ -11039,23 +11020,23 @@
       <c r="A63" s="23">
         <v>53</v>
       </c>
-      <c r="B63" s="447"/>
-      <c r="C63" s="431"/>
-      <c r="D63" s="429"/>
+      <c r="B63" s="402"/>
+      <c r="C63" s="427"/>
+      <c r="D63" s="447"/>
       <c r="E63" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="F63" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="F63" s="49" t="s">
+      <c r="G63" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="G63" s="44" t="s">
+      <c r="H63" s="44" t="s">
         <v>330</v>
       </c>
-      <c r="H63" s="44" t="s">
-        <v>331</v>
-      </c>
       <c r="I63" s="240" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J63" s="44"/>
       <c r="K63" s="46"/>
@@ -11084,23 +11065,23 @@
       <c r="A64" s="371">
         <v>54</v>
       </c>
-      <c r="B64" s="447"/>
-      <c r="C64" s="431"/>
-      <c r="D64" s="429"/>
+      <c r="B64" s="402"/>
+      <c r="C64" s="427"/>
+      <c r="D64" s="447"/>
       <c r="E64" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="F64" s="53" t="s">
         <v>332</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="G64" s="254" t="s">
         <v>333</v>
       </c>
-      <c r="G64" s="254" t="s">
+      <c r="H64" s="264" t="s">
         <v>334</v>
       </c>
-      <c r="H64" s="264" t="s">
+      <c r="I64" s="240" t="s">
         <v>335</v>
-      </c>
-      <c r="I64" s="240" t="s">
-        <v>336</v>
       </c>
       <c r="J64" s="44"/>
       <c r="K64" s="44"/>
@@ -11129,23 +11110,23 @@
       <c r="A65" s="23">
         <v>55</v>
       </c>
-      <c r="B65" s="447"/>
-      <c r="C65" s="431"/>
-      <c r="D65" s="429"/>
+      <c r="B65" s="402"/>
+      <c r="C65" s="427"/>
+      <c r="D65" s="447"/>
       <c r="E65" s="253" t="s">
+        <v>337</v>
+      </c>
+      <c r="F65" s="254" t="s">
+        <v>336</v>
+      </c>
+      <c r="G65" s="254" t="s">
         <v>338</v>
       </c>
-      <c r="F65" s="254" t="s">
-        <v>337</v>
-      </c>
-      <c r="G65" s="254" t="s">
+      <c r="H65" s="265" t="s">
         <v>339</v>
       </c>
-      <c r="H65" s="265" t="s">
-        <v>340</v>
-      </c>
       <c r="I65" s="240" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J65" s="44"/>
       <c r="K65" s="44"/>
@@ -11174,23 +11155,23 @@
       <c r="A66" s="371">
         <v>56</v>
       </c>
-      <c r="B66" s="447"/>
-      <c r="C66" s="431"/>
-      <c r="D66" s="429"/>
+      <c r="B66" s="402"/>
+      <c r="C66" s="427"/>
+      <c r="D66" s="447"/>
       <c r="E66" s="253" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F66" s="254" t="s">
+        <v>340</v>
+      </c>
+      <c r="G66" s="254" t="s">
         <v>341</v>
       </c>
-      <c r="G66" s="254" t="s">
+      <c r="H66" s="264" t="s">
+        <v>330</v>
+      </c>
+      <c r="I66" s="240" t="s">
         <v>342</v>
-      </c>
-      <c r="H66" s="264" t="s">
-        <v>331</v>
-      </c>
-      <c r="I66" s="240" t="s">
-        <v>343</v>
       </c>
       <c r="J66" s="44"/>
       <c r="K66" s="44"/>
@@ -11217,8 +11198,8 @@
     </row>
     <row r="67" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A67" s="348"/>
-      <c r="B67" s="447"/>
-      <c r="C67" s="431"/>
+      <c r="B67" s="402"/>
+      <c r="C67" s="427"/>
       <c r="D67" s="356"/>
       <c r="E67" s="314"/>
       <c r="F67" s="316"/>
@@ -11250,25 +11231,25 @@
       <c r="A68" s="23">
         <v>57</v>
       </c>
-      <c r="B68" s="447"/>
-      <c r="C68" s="431"/>
-      <c r="D68" s="502" t="s">
-        <v>491</v>
+      <c r="B68" s="402"/>
+      <c r="C68" s="427"/>
+      <c r="D68" s="448" t="s">
+        <v>490</v>
       </c>
       <c r="E68" s="357" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F68" s="255" t="s">
+        <v>453</v>
+      </c>
+      <c r="G68" s="252" t="s">
         <v>454</v>
-      </c>
-      <c r="G68" s="252" t="s">
-        <v>455</v>
       </c>
       <c r="H68" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I68" s="254" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J68" s="44"/>
       <c r="K68" s="44"/>
@@ -11297,23 +11278,23 @@
       <c r="A69" s="23">
         <v>58</v>
       </c>
-      <c r="B69" s="447"/>
-      <c r="C69" s="431"/>
-      <c r="D69" s="503"/>
+      <c r="B69" s="402"/>
+      <c r="C69" s="427"/>
+      <c r="D69" s="449"/>
       <c r="E69" s="357" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F69" s="349" t="s">
+        <v>457</v>
+      </c>
+      <c r="G69" s="254" t="s">
         <v>458</v>
-      </c>
-      <c r="G69" s="254" t="s">
-        <v>459</v>
       </c>
       <c r="H69" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I69" s="254" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J69" s="44"/>
       <c r="K69" s="44"/>
@@ -11342,23 +11323,23 @@
       <c r="A70" s="23">
         <v>59</v>
       </c>
-      <c r="B70" s="447"/>
-      <c r="C70" s="431"/>
-      <c r="D70" s="503"/>
+      <c r="B70" s="402"/>
+      <c r="C70" s="427"/>
+      <c r="D70" s="449"/>
       <c r="E70" s="357" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F70" s="255" t="s">
+        <v>459</v>
+      </c>
+      <c r="G70" s="252" t="s">
         <v>460</v>
-      </c>
-      <c r="G70" s="252" t="s">
-        <v>461</v>
       </c>
       <c r="H70" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I70" s="254" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J70" s="44"/>
       <c r="K70" s="44"/>
@@ -11387,23 +11368,23 @@
       <c r="A71" s="23">
         <v>60</v>
       </c>
-      <c r="B71" s="447"/>
-      <c r="C71" s="431"/>
-      <c r="D71" s="503"/>
+      <c r="B71" s="402"/>
+      <c r="C71" s="427"/>
+      <c r="D71" s="449"/>
       <c r="E71" s="357" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F71" s="255" t="s">
+        <v>461</v>
+      </c>
+      <c r="G71" s="252" t="s">
         <v>462</v>
-      </c>
-      <c r="G71" s="252" t="s">
-        <v>463</v>
       </c>
       <c r="H71" s="264" t="s">
         <v>41</v>
       </c>
       <c r="I71" s="355" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J71" s="44"/>
       <c r="K71" s="44"/>
@@ -11432,23 +11413,23 @@
       <c r="A72" s="23">
         <v>61</v>
       </c>
-      <c r="B72" s="447"/>
-      <c r="C72" s="431"/>
-      <c r="D72" s="503"/>
+      <c r="B72" s="402"/>
+      <c r="C72" s="427"/>
+      <c r="D72" s="449"/>
       <c r="E72" s="358" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F72" s="255" t="s">
+        <v>463</v>
+      </c>
+      <c r="G72" s="252" t="s">
         <v>464</v>
-      </c>
-      <c r="G72" s="252" t="s">
-        <v>465</v>
       </c>
       <c r="H72" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I72" s="254" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J72" s="44"/>
       <c r="K72" s="44"/>
@@ -11477,23 +11458,23 @@
       <c r="A73" s="23">
         <v>62</v>
       </c>
-      <c r="B73" s="447"/>
-      <c r="C73" s="431"/>
-      <c r="D73" s="503"/>
+      <c r="B73" s="402"/>
+      <c r="C73" s="427"/>
+      <c r="D73" s="449"/>
       <c r="E73" s="357" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F73" s="255" t="s">
+        <v>465</v>
+      </c>
+      <c r="G73" s="252" t="s">
         <v>466</v>
-      </c>
-      <c r="G73" s="252" t="s">
-        <v>467</v>
       </c>
       <c r="H73" s="354" t="s">
         <v>41</v>
       </c>
       <c r="I73" s="254" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J73" s="44"/>
       <c r="K73" s="44"/>
@@ -11522,23 +11503,23 @@
       <c r="A74" s="23">
         <v>63</v>
       </c>
-      <c r="B74" s="447"/>
-      <c r="C74" s="431"/>
-      <c r="D74" s="503"/>
+      <c r="B74" s="402"/>
+      <c r="C74" s="427"/>
+      <c r="D74" s="449"/>
       <c r="E74" s="357" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F74" s="349" t="s">
+        <v>467</v>
+      </c>
+      <c r="G74" s="257" t="s">
         <v>468</v>
       </c>
-      <c r="G74" s="257" t="s">
+      <c r="H74" s="350" t="s">
         <v>469</v>
       </c>
-      <c r="H74" s="350" t="s">
-        <v>470</v>
-      </c>
       <c r="I74" s="254" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J74" s="44"/>
       <c r="K74" s="44"/>
@@ -11567,23 +11548,23 @@
       <c r="A75" s="23">
         <v>64</v>
       </c>
-      <c r="B75" s="447"/>
-      <c r="C75" s="431"/>
-      <c r="D75" s="503"/>
+      <c r="B75" s="402"/>
+      <c r="C75" s="427"/>
+      <c r="D75" s="449"/>
       <c r="E75" s="357" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F75" s="349" t="s">
+        <v>470</v>
+      </c>
+      <c r="G75" s="351" t="s">
         <v>471</v>
       </c>
-      <c r="G75" s="351" t="s">
-        <v>472</v>
-      </c>
       <c r="H75" s="350" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I75" s="254" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J75" s="44"/>
       <c r="K75" s="44"/>
@@ -11612,23 +11593,23 @@
       <c r="A76" s="23">
         <v>65</v>
       </c>
-      <c r="B76" s="447"/>
-      <c r="C76" s="431"/>
-      <c r="D76" s="503"/>
+      <c r="B76" s="402"/>
+      <c r="C76" s="427"/>
+      <c r="D76" s="449"/>
       <c r="E76" s="357" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F76" s="349" t="s">
+        <v>472</v>
+      </c>
+      <c r="G76" s="351" t="s">
         <v>473</v>
       </c>
-      <c r="G76" s="351" t="s">
+      <c r="H76" s="353" t="s">
         <v>474</v>
       </c>
-      <c r="H76" s="353" t="s">
-        <v>475</v>
-      </c>
       <c r="I76" s="254" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J76" s="44"/>
       <c r="K76" s="44"/>
@@ -11657,23 +11638,23 @@
       <c r="A77" s="23">
         <v>66</v>
       </c>
-      <c r="B77" s="447"/>
-      <c r="C77" s="431"/>
-      <c r="D77" s="503"/>
+      <c r="B77" s="402"/>
+      <c r="C77" s="427"/>
+      <c r="D77" s="449"/>
       <c r="E77" s="357" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F77" s="255" t="s">
+        <v>475</v>
+      </c>
+      <c r="G77" s="351" t="s">
         <v>476</v>
       </c>
-      <c r="G77" s="351" t="s">
-        <v>477</v>
-      </c>
       <c r="H77" s="353" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I77" s="254" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J77" s="44"/>
       <c r="K77" s="44"/>
@@ -11702,23 +11683,23 @@
       <c r="A78" s="23">
         <v>67</v>
       </c>
-      <c r="B78" s="447"/>
-      <c r="C78" s="431"/>
-      <c r="D78" s="503"/>
+      <c r="B78" s="402"/>
+      <c r="C78" s="427"/>
+      <c r="D78" s="449"/>
       <c r="E78" s="357" t="s">
+        <v>477</v>
+      </c>
+      <c r="F78" s="349" t="s">
         <v>478</v>
       </c>
-      <c r="F78" s="349" t="s">
+      <c r="G78" s="254" t="s">
         <v>479</v>
       </c>
-      <c r="G78" s="254" t="s">
-        <v>480</v>
-      </c>
       <c r="H78" s="352" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I78" s="254" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J78" s="44"/>
       <c r="K78" s="44"/>
@@ -11747,23 +11728,23 @@
       <c r="A79" s="23">
         <v>68</v>
       </c>
-      <c r="B79" s="447"/>
-      <c r="C79" s="431"/>
-      <c r="D79" s="504"/>
+      <c r="B79" s="402"/>
+      <c r="C79" s="427"/>
+      <c r="D79" s="450"/>
       <c r="E79" s="359" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F79" s="349" t="s">
+        <v>480</v>
+      </c>
+      <c r="G79" s="254" t="s">
         <v>481</v>
-      </c>
-      <c r="G79" s="254" t="s">
-        <v>482</v>
       </c>
       <c r="H79" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I79" s="254" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J79" s="44"/>
       <c r="K79" s="44"/>
@@ -11790,8 +11771,8 @@
     </row>
     <row r="80" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A80" s="348"/>
-      <c r="B80" s="447"/>
-      <c r="C80" s="431"/>
+      <c r="B80" s="402"/>
+      <c r="C80" s="427"/>
       <c r="D80" s="356"/>
       <c r="E80" s="314"/>
       <c r="F80" s="316"/>
@@ -11823,25 +11804,25 @@
       <c r="A81" s="23">
         <v>69</v>
       </c>
-      <c r="B81" s="447"/>
-      <c r="C81" s="431"/>
-      <c r="D81" s="495" t="s">
+      <c r="B81" s="402"/>
+      <c r="C81" s="427"/>
+      <c r="D81" s="451" t="s">
+        <v>503</v>
+      </c>
+      <c r="E81" s="374" t="s">
+        <v>523</v>
+      </c>
+      <c r="F81" s="349" t="s">
         <v>504</v>
       </c>
-      <c r="E81" s="505" t="s">
-        <v>524</v>
-      </c>
-      <c r="F81" s="349" t="s">
+      <c r="G81" s="252" t="s">
         <v>505</v>
-      </c>
-      <c r="G81" s="252" t="s">
-        <v>506</v>
       </c>
       <c r="H81" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I81" s="254" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J81" s="44"/>
       <c r="K81" s="44"/>
@@ -11870,23 +11851,23 @@
       <c r="A82" s="23">
         <v>70</v>
       </c>
-      <c r="B82" s="447"/>
-      <c r="C82" s="431"/>
-      <c r="D82" s="496"/>
-      <c r="E82" s="506" t="s">
-        <v>523</v>
+      <c r="B82" s="402"/>
+      <c r="C82" s="427"/>
+      <c r="D82" s="452"/>
+      <c r="E82" s="375" t="s">
+        <v>522</v>
       </c>
       <c r="F82" s="349" t="s">
+        <v>507</v>
+      </c>
+      <c r="G82" s="252" t="s">
         <v>508</v>
       </c>
-      <c r="G82" s="252" t="s">
+      <c r="H82" s="252" t="s">
         <v>509</v>
       </c>
-      <c r="H82" s="252" t="s">
+      <c r="I82" s="254" t="s">
         <v>510</v>
-      </c>
-      <c r="I82" s="254" t="s">
-        <v>511</v>
       </c>
       <c r="J82" s="44"/>
       <c r="K82" s="44"/>
@@ -11915,26 +11896,26 @@
       <c r="A83" s="23">
         <v>71</v>
       </c>
-      <c r="B83" s="447"/>
-      <c r="C83" s="431"/>
-      <c r="D83" s="496"/>
-      <c r="E83" s="507" t="s">
-        <v>522</v>
+      <c r="B83" s="402"/>
+      <c r="C83" s="427"/>
+      <c r="D83" s="452"/>
+      <c r="E83" s="376" t="s">
+        <v>521</v>
       </c>
       <c r="F83" s="255" t="s">
+        <v>511</v>
+      </c>
+      <c r="G83" s="252" t="s">
         <v>512</v>
       </c>
-      <c r="G83" s="252" t="s">
+      <c r="H83" s="252" t="s">
         <v>513</v>
       </c>
-      <c r="H83" s="252" t="s">
+      <c r="I83" s="254" t="s">
         <v>514</v>
       </c>
-      <c r="I83" s="254" t="s">
-        <v>515</v>
-      </c>
       <c r="J83" s="268" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K83" s="44"/>
       <c r="L83" s="23" t="s">
@@ -11962,23 +11943,23 @@
       <c r="A84" s="23">
         <v>72</v>
       </c>
-      <c r="B84" s="447"/>
-      <c r="C84" s="431"/>
-      <c r="D84" s="496"/>
-      <c r="E84" s="507" t="s">
-        <v>521</v>
+      <c r="B84" s="402"/>
+      <c r="C84" s="427"/>
+      <c r="D84" s="452"/>
+      <c r="E84" s="376" t="s">
+        <v>520</v>
       </c>
       <c r="F84" s="255" t="s">
+        <v>515</v>
+      </c>
+      <c r="G84" s="252" t="s">
         <v>516</v>
       </c>
-      <c r="G84" s="252" t="s">
+      <c r="H84" s="252" t="s">
         <v>517</v>
       </c>
-      <c r="H84" s="252" t="s">
+      <c r="I84" s="254" t="s">
         <v>518</v>
-      </c>
-      <c r="I84" s="254" t="s">
-        <v>519</v>
       </c>
       <c r="J84" s="44"/>
       <c r="K84" s="44"/>
@@ -12007,23 +11988,23 @@
       <c r="A85" s="23">
         <v>73</v>
       </c>
-      <c r="B85" s="447"/>
-      <c r="C85" s="431"/>
-      <c r="D85" s="496"/>
-      <c r="E85" s="507" t="s">
-        <v>520</v>
+      <c r="B85" s="402"/>
+      <c r="C85" s="427"/>
+      <c r="D85" s="452"/>
+      <c r="E85" s="376" t="s">
+        <v>519</v>
       </c>
       <c r="F85" s="255" t="s">
+        <v>524</v>
+      </c>
+      <c r="G85" s="252" t="s">
         <v>525</v>
       </c>
-      <c r="G85" s="252" t="s">
+      <c r="H85" s="252" t="s">
         <v>526</v>
       </c>
-      <c r="H85" s="252" t="s">
+      <c r="I85" s="254" t="s">
         <v>527</v>
-      </c>
-      <c r="I85" s="254" t="s">
-        <v>528</v>
       </c>
       <c r="J85" s="44"/>
       <c r="K85" s="44"/>
@@ -12052,25 +12033,25 @@
       <c r="A86" s="23">
         <v>74</v>
       </c>
-      <c r="B86" s="447"/>
-      <c r="C86" s="431"/>
-      <c r="D86" s="496"/>
-      <c r="E86" s="507" t="s">
+      <c r="B86" s="402"/>
+      <c r="C86" s="427"/>
+      <c r="D86" s="452"/>
+      <c r="E86" s="376" t="s">
+        <v>528</v>
+      </c>
+      <c r="F86" s="255" t="s">
         <v>529</v>
       </c>
-      <c r="F86" s="255" t="s">
+      <c r="G86" s="252" t="s">
         <v>530</v>
       </c>
-      <c r="G86" s="252" t="s">
+      <c r="H86" s="254" t="s">
         <v>531</v>
       </c>
-      <c r="H86" s="254" t="s">
+      <c r="I86" s="254" t="s">
         <v>532</v>
       </c>
-      <c r="I86" s="254" t="s">
-        <v>533</v>
-      </c>
-      <c r="J86" s="508"/>
+      <c r="J86" s="377"/>
       <c r="K86" s="44"/>
       <c r="L86" s="23" t="s">
         <v>39</v>
@@ -12097,23 +12078,23 @@
       <c r="A87" s="23">
         <v>75</v>
       </c>
-      <c r="B87" s="447"/>
-      <c r="C87" s="431"/>
-      <c r="D87" s="496"/>
-      <c r="E87" s="507" t="s">
+      <c r="B87" s="402"/>
+      <c r="C87" s="427"/>
+      <c r="D87" s="452"/>
+      <c r="E87" s="376" t="s">
+        <v>533</v>
+      </c>
+      <c r="F87" s="254" t="s">
         <v>534</v>
       </c>
-      <c r="F87" s="254" t="s">
+      <c r="G87" s="254" t="s">
         <v>535</v>
       </c>
-      <c r="G87" s="254" t="s">
-        <v>536</v>
-      </c>
       <c r="H87" s="254" t="s">
+        <v>531</v>
+      </c>
+      <c r="I87" s="254" t="s">
         <v>532</v>
-      </c>
-      <c r="I87" s="254" t="s">
-        <v>533</v>
       </c>
       <c r="J87" s="44"/>
       <c r="K87" s="44"/>
@@ -12140,10 +12121,10 @@
     </row>
     <row r="88" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A88" s="55"/>
-      <c r="B88" s="447"/>
-      <c r="C88" s="431"/>
-      <c r="D88" s="510"/>
-      <c r="E88" s="509"/>
+      <c r="B88" s="402"/>
+      <c r="C88" s="427"/>
+      <c r="D88" s="379"/>
+      <c r="E88" s="378"/>
       <c r="F88" s="56"/>
       <c r="G88" s="56"/>
       <c r="H88" s="56"/>
@@ -12173,25 +12154,25 @@
       <c r="A89" s="23">
         <v>76</v>
       </c>
-      <c r="B89" s="447"/>
-      <c r="C89" s="431"/>
-      <c r="D89" s="511" t="s">
+      <c r="B89" s="402"/>
+      <c r="C89" s="427"/>
+      <c r="D89" s="453" t="s">
+        <v>538</v>
+      </c>
+      <c r="E89" s="252" t="s">
         <v>539</v>
       </c>
-      <c r="E89" s="252" t="s">
+      <c r="F89" s="254" t="s">
         <v>540</v>
       </c>
-      <c r="F89" s="254" t="s">
+      <c r="G89" s="252" t="s">
         <v>541</v>
       </c>
-      <c r="G89" s="252" t="s">
+      <c r="H89" s="254" t="s">
         <v>542</v>
       </c>
-      <c r="H89" s="254" t="s">
-        <v>543</v>
-      </c>
       <c r="I89" s="240" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J89" s="44"/>
       <c r="K89" s="44"/>
@@ -12220,23 +12201,23 @@
       <c r="A90" s="23">
         <v>77</v>
       </c>
-      <c r="B90" s="447"/>
-      <c r="C90" s="431"/>
-      <c r="D90" s="512"/>
+      <c r="B90" s="402"/>
+      <c r="C90" s="427"/>
+      <c r="D90" s="454"/>
       <c r="E90" s="253" t="s">
+        <v>543</v>
+      </c>
+      <c r="F90" s="252" t="s">
         <v>544</v>
       </c>
-      <c r="F90" s="252" t="s">
+      <c r="G90" s="252" t="s">
         <v>545</v>
       </c>
-      <c r="G90" s="252" t="s">
+      <c r="H90" s="252" t="s">
         <v>546</v>
       </c>
-      <c r="H90" s="252" t="s">
+      <c r="I90" s="240" t="s">
         <v>547</v>
-      </c>
-      <c r="I90" s="240" t="s">
-        <v>548</v>
       </c>
       <c r="J90" s="44"/>
       <c r="K90" s="44"/>
@@ -12265,23 +12246,23 @@
       <c r="A91" s="23">
         <v>78</v>
       </c>
-      <c r="B91" s="447"/>
-      <c r="C91" s="431"/>
-      <c r="D91" s="512"/>
+      <c r="B91" s="402"/>
+      <c r="C91" s="427"/>
+      <c r="D91" s="454"/>
       <c r="E91" s="253" t="s">
+        <v>549</v>
+      </c>
+      <c r="F91" s="252" t="s">
         <v>550</v>
       </c>
-      <c r="F91" s="252" t="s">
+      <c r="G91" s="252" t="s">
         <v>551</v>
       </c>
-      <c r="G91" s="252" t="s">
+      <c r="H91" s="252" t="s">
         <v>552</v>
       </c>
-      <c r="H91" s="252" t="s">
+      <c r="I91" s="240" t="s">
         <v>553</v>
-      </c>
-      <c r="I91" s="240" t="s">
-        <v>554</v>
       </c>
       <c r="J91" s="44"/>
       <c r="K91" s="44"/>
@@ -12310,23 +12291,23 @@
       <c r="A92" s="23">
         <v>79</v>
       </c>
-      <c r="B92" s="447"/>
-      <c r="C92" s="431"/>
-      <c r="D92" s="512"/>
+      <c r="B92" s="402"/>
+      <c r="C92" s="427"/>
+      <c r="D92" s="454"/>
       <c r="E92" s="253" t="s">
+        <v>554</v>
+      </c>
+      <c r="F92" s="252" t="s">
         <v>555</v>
       </c>
-      <c r="F92" s="252" t="s">
+      <c r="G92" s="252" t="s">
         <v>556</v>
       </c>
-      <c r="G92" s="252" t="s">
+      <c r="H92" s="264" t="s">
         <v>557</v>
       </c>
-      <c r="H92" s="264" t="s">
+      <c r="I92" s="240" t="s">
         <v>558</v>
-      </c>
-      <c r="I92" s="240" t="s">
-        <v>559</v>
       </c>
       <c r="J92" s="44"/>
       <c r="K92" s="44"/>
@@ -12355,23 +12336,23 @@
       <c r="A93" s="23">
         <v>80</v>
       </c>
-      <c r="B93" s="447"/>
-      <c r="C93" s="431"/>
-      <c r="D93" s="512"/>
-      <c r="E93" s="514" t="s">
+      <c r="B93" s="402"/>
+      <c r="C93" s="427"/>
+      <c r="D93" s="454"/>
+      <c r="E93" s="380" t="s">
+        <v>559</v>
+      </c>
+      <c r="F93" s="252" t="s">
         <v>560</v>
       </c>
-      <c r="F93" s="252" t="s">
+      <c r="G93" s="252" t="s">
         <v>561</v>
       </c>
-      <c r="G93" s="252" t="s">
+      <c r="H93" s="252" t="s">
         <v>562</v>
       </c>
-      <c r="H93" s="252" t="s">
+      <c r="I93" s="240" t="s">
         <v>563</v>
-      </c>
-      <c r="I93" s="240" t="s">
-        <v>564</v>
       </c>
       <c r="J93" s="44"/>
       <c r="K93" s="44"/>
@@ -12400,23 +12381,23 @@
       <c r="A94" s="23">
         <v>81</v>
       </c>
-      <c r="B94" s="447"/>
-      <c r="C94" s="431"/>
-      <c r="D94" s="512"/>
-      <c r="E94" s="514" t="s">
+      <c r="B94" s="402"/>
+      <c r="C94" s="427"/>
+      <c r="D94" s="454"/>
+      <c r="E94" s="380" t="s">
+        <v>564</v>
+      </c>
+      <c r="F94" s="252" t="s">
         <v>565</v>
       </c>
-      <c r="F94" s="252" t="s">
+      <c r="G94" s="252" t="s">
         <v>566</v>
       </c>
-      <c r="G94" s="252" t="s">
+      <c r="H94" s="252" t="s">
         <v>567</v>
       </c>
-      <c r="H94" s="252" t="s">
-        <v>568</v>
-      </c>
       <c r="I94" s="240" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J94" s="44"/>
       <c r="K94" s="44"/>
@@ -12445,23 +12426,23 @@
       <c r="A95" s="23">
         <v>82</v>
       </c>
-      <c r="B95" s="447"/>
-      <c r="C95" s="431"/>
-      <c r="D95" s="512"/>
-      <c r="E95" s="514" t="s">
+      <c r="B95" s="402"/>
+      <c r="C95" s="427"/>
+      <c r="D95" s="454"/>
+      <c r="E95" s="380" t="s">
+        <v>568</v>
+      </c>
+      <c r="F95" s="252" t="s">
         <v>569</v>
       </c>
-      <c r="F95" s="252" t="s">
+      <c r="G95" s="252" t="s">
         <v>570</v>
       </c>
-      <c r="G95" s="252" t="s">
+      <c r="H95" s="252" t="s">
+        <v>567</v>
+      </c>
+      <c r="I95" s="240" t="s">
         <v>571</v>
-      </c>
-      <c r="H95" s="252" t="s">
-        <v>568</v>
-      </c>
-      <c r="I95" s="240" t="s">
-        <v>572</v>
       </c>
       <c r="J95" s="44"/>
       <c r="K95" s="44"/>
@@ -12490,23 +12471,23 @@
       <c r="A96" s="23">
         <v>83</v>
       </c>
-      <c r="B96" s="447"/>
-      <c r="C96" s="431"/>
-      <c r="D96" s="512"/>
-      <c r="E96" s="514" t="s">
+      <c r="B96" s="402"/>
+      <c r="C96" s="427"/>
+      <c r="D96" s="454"/>
+      <c r="E96" s="380" t="s">
+        <v>573</v>
+      </c>
+      <c r="F96" s="252" t="s">
         <v>574</v>
       </c>
-      <c r="F96" s="252" t="s">
+      <c r="G96" s="252" t="s">
         <v>575</v>
       </c>
-      <c r="G96" s="252" t="s">
+      <c r="H96" s="252" t="s">
         <v>576</v>
       </c>
-      <c r="H96" s="252" t="s">
+      <c r="I96" s="240" t="s">
         <v>577</v>
-      </c>
-      <c r="I96" s="240" t="s">
-        <v>578</v>
       </c>
       <c r="J96" s="44"/>
       <c r="K96" s="44"/>
@@ -12535,23 +12516,23 @@
       <c r="A97" s="23">
         <v>84</v>
       </c>
-      <c r="B97" s="447"/>
-      <c r="C97" s="431"/>
-      <c r="D97" s="512"/>
-      <c r="E97" s="514" t="s">
+      <c r="B97" s="402"/>
+      <c r="C97" s="427"/>
+      <c r="D97" s="454"/>
+      <c r="E97" s="380" t="s">
+        <v>578</v>
+      </c>
+      <c r="F97" s="252" t="s">
         <v>579</v>
       </c>
-      <c r="F97" s="252" t="s">
+      <c r="G97" s="252" t="s">
         <v>580</v>
       </c>
-      <c r="G97" s="252" t="s">
+      <c r="H97" s="252" t="s">
         <v>581</v>
       </c>
-      <c r="H97" s="252" t="s">
+      <c r="I97" s="240" t="s">
         <v>582</v>
-      </c>
-      <c r="I97" s="240" t="s">
-        <v>583</v>
       </c>
       <c r="J97" s="44"/>
       <c r="K97" s="44"/>
@@ -12580,23 +12561,23 @@
       <c r="A98" s="23">
         <v>85</v>
       </c>
-      <c r="B98" s="447"/>
-      <c r="C98" s="431"/>
-      <c r="D98" s="512"/>
-      <c r="E98" s="514" t="s">
+      <c r="B98" s="402"/>
+      <c r="C98" s="427"/>
+      <c r="D98" s="454"/>
+      <c r="E98" s="380" t="s">
+        <v>583</v>
+      </c>
+      <c r="F98" s="252" t="s">
         <v>584</v>
       </c>
-      <c r="F98" s="252" t="s">
+      <c r="G98" s="252" t="s">
         <v>585</v>
-      </c>
-      <c r="G98" s="252" t="s">
-        <v>586</v>
       </c>
       <c r="H98" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I98" s="240" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J98" s="44"/>
       <c r="K98" s="44"/>
@@ -12625,23 +12606,23 @@
       <c r="A99" s="23">
         <v>86</v>
       </c>
-      <c r="B99" s="447"/>
-      <c r="C99" s="431"/>
-      <c r="D99" s="513"/>
+      <c r="B99" s="402"/>
+      <c r="C99" s="427"/>
+      <c r="D99" s="455"/>
       <c r="E99" s="265" t="s">
+        <v>587</v>
+      </c>
+      <c r="F99" s="265" t="s">
         <v>588</v>
       </c>
-      <c r="F99" s="265" t="s">
+      <c r="G99" s="265" t="s">
         <v>589</v>
-      </c>
-      <c r="G99" s="265" t="s">
-        <v>590</v>
       </c>
       <c r="H99" s="252" t="s">
         <v>41</v>
       </c>
       <c r="I99" s="240" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L99" s="23" t="s">
         <v>39</v>
@@ -12649,10 +12630,10 @@
     </row>
     <row r="100" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A100" s="55"/>
-      <c r="B100" s="447"/>
-      <c r="C100" s="431"/>
-      <c r="D100" s="510"/>
-      <c r="E100" s="509"/>
+      <c r="B100" s="402"/>
+      <c r="C100" s="427"/>
+      <c r="D100" s="379"/>
+      <c r="E100" s="378"/>
       <c r="F100" s="56"/>
       <c r="G100" s="56"/>
       <c r="H100" s="56"/>
@@ -12682,25 +12663,25 @@
       <c r="A101" s="23">
         <v>87</v>
       </c>
-      <c r="B101" s="447"/>
-      <c r="C101" s="431"/>
-      <c r="D101" s="515" t="s">
+      <c r="B101" s="402"/>
+      <c r="C101" s="427"/>
+      <c r="D101" s="456" t="s">
+        <v>593</v>
+      </c>
+      <c r="E101" s="265" t="s">
         <v>594</v>
       </c>
-      <c r="E101" s="265" t="s">
+      <c r="F101" s="265" t="s">
         <v>595</v>
       </c>
-      <c r="F101" s="265" t="s">
+      <c r="G101" s="265" t="s">
         <v>596</v>
       </c>
-      <c r="G101" s="265" t="s">
+      <c r="H101" s="252" t="s">
         <v>597</v>
       </c>
-      <c r="H101" s="252" t="s">
-        <v>598</v>
-      </c>
       <c r="I101" s="240" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="L101" s="23" t="s">
         <v>39</v>
@@ -12710,23 +12691,23 @@
       <c r="A102" s="23">
         <v>88</v>
       </c>
-      <c r="B102" s="447"/>
-      <c r="C102" s="431"/>
-      <c r="D102" s="516"/>
+      <c r="B102" s="402"/>
+      <c r="C102" s="427"/>
+      <c r="D102" s="457"/>
       <c r="E102" s="265" t="s">
+        <v>598</v>
+      </c>
+      <c r="F102" s="265" t="s">
         <v>599</v>
       </c>
-      <c r="F102" s="265" t="s">
+      <c r="G102" s="265" t="s">
         <v>600</v>
       </c>
-      <c r="G102" s="265" t="s">
+      <c r="H102" s="252" t="s">
         <v>601</v>
       </c>
-      <c r="H102" s="252" t="s">
-        <v>602</v>
-      </c>
       <c r="I102" s="240" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L102" s="23" t="s">
         <v>39</v>
@@ -12736,23 +12717,23 @@
       <c r="A103" s="23">
         <v>89</v>
       </c>
-      <c r="B103" s="447"/>
-      <c r="C103" s="431"/>
-      <c r="D103" s="516"/>
+      <c r="B103" s="402"/>
+      <c r="C103" s="427"/>
+      <c r="D103" s="457"/>
       <c r="E103" s="265" t="s">
+        <v>602</v>
+      </c>
+      <c r="F103" s="265" t="s">
         <v>603</v>
       </c>
-      <c r="F103" s="265" t="s">
+      <c r="G103" s="265" t="s">
         <v>604</v>
       </c>
-      <c r="G103" s="265" t="s">
+      <c r="H103" s="252" t="s">
         <v>605</v>
       </c>
-      <c r="H103" s="252" t="s">
+      <c r="I103" s="240" t="s">
         <v>606</v>
-      </c>
-      <c r="I103" s="240" t="s">
-        <v>607</v>
       </c>
       <c r="L103" s="23" t="s">
         <v>39</v>
@@ -12762,23 +12743,23 @@
       <c r="A104" s="23">
         <v>90</v>
       </c>
-      <c r="B104" s="447"/>
-      <c r="C104" s="431"/>
-      <c r="D104" s="516"/>
+      <c r="B104" s="402"/>
+      <c r="C104" s="427"/>
+      <c r="D104" s="457"/>
       <c r="E104" s="265" t="s">
+        <v>609</v>
+      </c>
+      <c r="F104" s="265" t="s">
         <v>610</v>
       </c>
-      <c r="F104" s="265" t="s">
+      <c r="G104" s="265" t="s">
         <v>611</v>
       </c>
-      <c r="G104" s="265" t="s">
+      <c r="H104" s="252" t="s">
         <v>612</v>
       </c>
-      <c r="H104" s="252" t="s">
+      <c r="I104" s="240" t="s">
         <v>613</v>
-      </c>
-      <c r="I104" s="240" t="s">
-        <v>614</v>
       </c>
       <c r="L104" s="23" t="s">
         <v>39</v>
@@ -12788,23 +12769,23 @@
       <c r="A105" s="23">
         <v>91</v>
       </c>
-      <c r="B105" s="447"/>
-      <c r="C105" s="431"/>
-      <c r="D105" s="516"/>
+      <c r="B105" s="402"/>
+      <c r="C105" s="427"/>
+      <c r="D105" s="457"/>
       <c r="E105" s="265" t="s">
+        <v>614</v>
+      </c>
+      <c r="F105" s="265" t="s">
         <v>615</v>
       </c>
-      <c r="F105" s="265" t="s">
+      <c r="G105" s="265" t="s">
         <v>616</v>
       </c>
-      <c r="G105" s="265" t="s">
+      <c r="H105" s="252" t="s">
         <v>617</v>
       </c>
-      <c r="H105" s="252" t="s">
+      <c r="I105" s="240" t="s">
         <v>618</v>
-      </c>
-      <c r="I105" s="240" t="s">
-        <v>619</v>
       </c>
       <c r="L105" s="23" t="s">
         <v>39</v>
@@ -12812,10 +12793,10 @@
     </row>
     <row r="106" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A106" s="55"/>
-      <c r="B106" s="447"/>
-      <c r="C106" s="431"/>
-      <c r="D106" s="510"/>
-      <c r="E106" s="509"/>
+      <c r="B106" s="402"/>
+      <c r="C106" s="427"/>
+      <c r="D106" s="379"/>
+      <c r="E106" s="378"/>
       <c r="F106" s="56"/>
       <c r="G106" s="56"/>
       <c r="H106" s="56"/>
@@ -12845,23 +12826,23 @@
       <c r="A107" s="42">
         <v>92</v>
       </c>
-      <c r="B107" s="447"/>
-      <c r="C107" s="431"/>
-      <c r="D107" s="497"/>
+      <c r="B107" s="402"/>
+      <c r="C107" s="427"/>
+      <c r="D107" s="412"/>
       <c r="E107" s="252" t="s">
+        <v>621</v>
+      </c>
+      <c r="F107" s="252" t="s">
         <v>622</v>
       </c>
-      <c r="F107" s="252" t="s">
+      <c r="G107" s="252" t="s">
         <v>623</v>
       </c>
-      <c r="G107" s="252" t="s">
+      <c r="H107" s="252" t="s">
         <v>624</v>
       </c>
-      <c r="H107" s="252" t="s">
+      <c r="I107" s="240" t="s">
         <v>625</v>
-      </c>
-      <c r="I107" s="240" t="s">
-        <v>626</v>
       </c>
       <c r="J107" s="44"/>
       <c r="K107" s="44"/>
@@ -12890,23 +12871,23 @@
       <c r="A108" s="42">
         <v>93</v>
       </c>
-      <c r="B108" s="447"/>
-      <c r="C108" s="431"/>
-      <c r="D108" s="498"/>
+      <c r="B108" s="402"/>
+      <c r="C108" s="427"/>
+      <c r="D108" s="413"/>
       <c r="E108" s="253" t="s">
+        <v>626</v>
+      </c>
+      <c r="F108" s="254" t="s">
         <v>627</v>
       </c>
-      <c r="F108" s="254" t="s">
+      <c r="G108" s="252" t="s">
         <v>628</v>
       </c>
-      <c r="G108" s="252" t="s">
+      <c r="H108" s="264" t="s">
         <v>629</v>
       </c>
-      <c r="H108" s="264" t="s">
+      <c r="I108" s="240" t="s">
         <v>630</v>
-      </c>
-      <c r="I108" s="240" t="s">
-        <v>631</v>
       </c>
       <c r="J108" s="44"/>
       <c r="K108" s="46"/>
@@ -12935,23 +12916,23 @@
       <c r="A109" s="42">
         <v>94</v>
       </c>
-      <c r="B109" s="447"/>
-      <c r="C109" s="431"/>
-      <c r="D109" s="498"/>
+      <c r="B109" s="402"/>
+      <c r="C109" s="427"/>
+      <c r="D109" s="413"/>
       <c r="E109" s="253" t="s">
+        <v>631</v>
+      </c>
+      <c r="F109" s="254" t="s">
         <v>632</v>
       </c>
-      <c r="F109" s="254" t="s">
+      <c r="G109" s="254" t="s">
         <v>633</v>
       </c>
-      <c r="G109" s="254" t="s">
+      <c r="H109" s="264" t="s">
         <v>634</v>
       </c>
-      <c r="H109" s="264" t="s">
+      <c r="I109" s="240" t="s">
         <v>635</v>
-      </c>
-      <c r="I109" s="240" t="s">
-        <v>636</v>
       </c>
       <c r="J109" s="44"/>
       <c r="K109" s="44"/>
@@ -12980,23 +12961,23 @@
       <c r="A110" s="42">
         <v>95</v>
       </c>
-      <c r="B110" s="447"/>
-      <c r="C110" s="431"/>
-      <c r="D110" s="498"/>
+      <c r="B110" s="402"/>
+      <c r="C110" s="427"/>
+      <c r="D110" s="413"/>
       <c r="E110" s="253" t="s">
+        <v>636</v>
+      </c>
+      <c r="F110" s="254" t="s">
         <v>637</v>
       </c>
-      <c r="F110" s="254" t="s">
+      <c r="G110" s="254" t="s">
         <v>638</v>
       </c>
-      <c r="G110" s="254" t="s">
+      <c r="H110" s="264" t="s">
         <v>639</v>
       </c>
-      <c r="H110" s="264" t="s">
-        <v>640</v>
-      </c>
       <c r="I110" s="240" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J110" s="44"/>
       <c r="K110" s="44"/>
@@ -13025,23 +13006,23 @@
       <c r="A111" s="42">
         <v>96</v>
       </c>
-      <c r="B111" s="447"/>
-      <c r="C111" s="431"/>
-      <c r="D111" s="498"/>
+      <c r="B111" s="402"/>
+      <c r="C111" s="427"/>
+      <c r="D111" s="413"/>
       <c r="E111" s="253" t="s">
+        <v>641</v>
+      </c>
+      <c r="F111" s="254" t="s">
         <v>642</v>
       </c>
-      <c r="F111" s="254" t="s">
+      <c r="G111" s="254" t="s">
         <v>643</v>
       </c>
-      <c r="G111" s="254" t="s">
+      <c r="H111" s="264" t="s">
         <v>644</v>
       </c>
-      <c r="H111" s="264" t="s">
-        <v>645</v>
-      </c>
       <c r="I111" s="240" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J111" s="44"/>
       <c r="K111" s="44"/>
@@ -13070,23 +13051,23 @@
       <c r="A112" s="42">
         <v>97</v>
       </c>
-      <c r="B112" s="447"/>
-      <c r="C112" s="431"/>
-      <c r="D112" s="498"/>
-      <c r="E112" s="517" t="s">
+      <c r="B112" s="402"/>
+      <c r="C112" s="427"/>
+      <c r="D112" s="413"/>
+      <c r="E112" s="381" t="s">
+        <v>646</v>
+      </c>
+      <c r="F112" s="254" t="s">
         <v>647</v>
       </c>
-      <c r="F112" s="254" t="s">
+      <c r="G112" s="254" t="s">
         <v>648</v>
       </c>
-      <c r="G112" s="254" t="s">
+      <c r="H112" s="264" t="s">
         <v>649</v>
       </c>
-      <c r="H112" s="264" t="s">
+      <c r="I112" s="320" t="s">
         <v>650</v>
-      </c>
-      <c r="I112" s="320" t="s">
-        <v>651</v>
       </c>
       <c r="J112" s="60"/>
       <c r="K112" s="60"/>
@@ -13115,23 +13096,23 @@
       <c r="A113" s="42">
         <v>98</v>
       </c>
-      <c r="B113" s="447"/>
-      <c r="C113" s="431"/>
-      <c r="D113" s="498"/>
-      <c r="E113" s="518" t="s">
+      <c r="B113" s="402"/>
+      <c r="C113" s="427"/>
+      <c r="D113" s="413"/>
+      <c r="E113" s="382" t="s">
+        <v>651</v>
+      </c>
+      <c r="F113" s="254" t="s">
         <v>652</v>
       </c>
-      <c r="F113" s="254" t="s">
+      <c r="G113" s="254" t="s">
         <v>653</v>
       </c>
-      <c r="G113" s="254" t="s">
+      <c r="H113" s="264" t="s">
         <v>654</v>
       </c>
-      <c r="H113" s="264" t="s">
+      <c r="I113" s="320" t="s">
         <v>655</v>
-      </c>
-      <c r="I113" s="320" t="s">
-        <v>656</v>
       </c>
       <c r="J113" s="44"/>
       <c r="K113" s="44"/>
@@ -13158,10 +13139,10 @@
     </row>
     <row r="114" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A114" s="55"/>
-      <c r="B114" s="447"/>
-      <c r="C114" s="431"/>
-      <c r="D114" s="498"/>
-      <c r="E114" s="509"/>
+      <c r="B114" s="402"/>
+      <c r="C114" s="427"/>
+      <c r="D114" s="413"/>
+      <c r="E114" s="378"/>
       <c r="F114" s="56"/>
       <c r="G114" s="56"/>
       <c r="H114" s="56"/>
@@ -13189,9 +13170,9 @@
     </row>
     <row r="115" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A115" s="42"/>
-      <c r="B115" s="447"/>
-      <c r="C115" s="431"/>
-      <c r="D115" s="498"/>
+      <c r="B115" s="402"/>
+      <c r="C115" s="427"/>
+      <c r="D115" s="413"/>
       <c r="E115" s="62"/>
       <c r="F115" s="54"/>
       <c r="G115" s="54"/>
@@ -13220,9 +13201,9 @@
     </row>
     <row r="116" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A116" s="42"/>
-      <c r="B116" s="447"/>
-      <c r="C116" s="431"/>
-      <c r="D116" s="498"/>
+      <c r="B116" s="402"/>
+      <c r="C116" s="427"/>
+      <c r="D116" s="413"/>
       <c r="E116" s="62"/>
       <c r="F116" s="54"/>
       <c r="G116" s="44"/>
@@ -13251,9 +13232,9 @@
     </row>
     <row r="117" spans="1:29" ht="30.75" customHeight="1" thickBot="1">
       <c r="A117" s="42"/>
-      <c r="B117" s="447"/>
-      <c r="C117" s="431"/>
-      <c r="D117" s="498"/>
+      <c r="B117" s="402"/>
+      <c r="C117" s="427"/>
+      <c r="D117" s="413"/>
       <c r="E117" s="34"/>
       <c r="F117" s="54"/>
       <c r="G117" s="44"/>
@@ -13282,9 +13263,9 @@
     </row>
     <row r="118" spans="1:29" ht="30.75" customHeight="1" thickBot="1">
       <c r="A118" s="42"/>
-      <c r="B118" s="447"/>
-      <c r="C118" s="431"/>
-      <c r="D118" s="499"/>
+      <c r="B118" s="402"/>
+      <c r="C118" s="427"/>
+      <c r="D118" s="414"/>
       <c r="E118" s="50"/>
       <c r="F118" s="54"/>
       <c r="G118" s="44"/>
@@ -13313,9 +13294,9 @@
     </row>
     <row r="119" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A119" s="55"/>
-      <c r="B119" s="447"/>
-      <c r="C119" s="432"/>
-      <c r="D119" s="500"/>
+      <c r="B119" s="402"/>
+      <c r="C119" s="428"/>
+      <c r="D119" s="373"/>
       <c r="E119" s="63"/>
       <c r="F119" s="56"/>
       <c r="G119" s="56"/>
@@ -13344,9 +13325,9 @@
     </row>
     <row r="120" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A120" s="42"/>
-      <c r="B120" s="374"/>
-      <c r="C120" s="501"/>
-      <c r="D120" s="457"/>
+      <c r="B120" s="404"/>
+      <c r="C120" s="422"/>
+      <c r="D120" s="423"/>
       <c r="E120" s="64"/>
       <c r="F120" s="44"/>
       <c r="G120" s="44"/>
@@ -13375,9 +13356,9 @@
     </row>
     <row r="121" spans="1:29" ht="28.5" customHeight="1" thickBot="1">
       <c r="A121" s="42"/>
-      <c r="B121" s="374"/>
-      <c r="C121" s="374"/>
-      <c r="D121" s="374"/>
+      <c r="B121" s="404"/>
+      <c r="C121" s="404"/>
+      <c r="D121" s="404"/>
       <c r="E121" s="64"/>
       <c r="F121" s="44"/>
       <c r="G121" s="44"/>
@@ -13406,9 +13387,9 @@
     </row>
     <row r="122" spans="1:29" ht="26.25" customHeight="1">
       <c r="A122" s="42"/>
-      <c r="B122" s="374"/>
-      <c r="C122" s="374"/>
-      <c r="D122" s="374"/>
+      <c r="B122" s="404"/>
+      <c r="C122" s="404"/>
+      <c r="D122" s="404"/>
       <c r="E122" s="44"/>
       <c r="F122" s="65"/>
       <c r="G122" s="44"/>
@@ -13437,9 +13418,9 @@
     </row>
     <row r="123" spans="1:29" ht="30" customHeight="1">
       <c r="A123" s="42"/>
-      <c r="B123" s="374"/>
-      <c r="C123" s="374"/>
-      <c r="D123" s="375"/>
+      <c r="B123" s="404"/>
+      <c r="C123" s="404"/>
+      <c r="D123" s="405"/>
       <c r="E123" s="44"/>
       <c r="F123" s="44"/>
       <c r="G123" s="44"/>
@@ -13468,8 +13449,8 @@
     </row>
     <row r="124" spans="1:29" ht="15.75" customHeight="1">
       <c r="A124" s="42"/>
-      <c r="B124" s="374"/>
-      <c r="C124" s="375"/>
+      <c r="B124" s="404"/>
+      <c r="C124" s="405"/>
       <c r="D124" s="66"/>
       <c r="E124" s="67"/>
       <c r="F124" s="44"/>
@@ -13499,7 +13480,7 @@
     </row>
     <row r="125" spans="1:29" ht="15.75" customHeight="1">
       <c r="A125" s="68"/>
-      <c r="B125" s="374"/>
+      <c r="B125" s="404"/>
       <c r="C125" s="69"/>
       <c r="D125" s="66"/>
       <c r="E125" s="67"/>
@@ -13530,7 +13511,7 @@
     </row>
     <row r="126" spans="1:29" ht="15.75" customHeight="1">
       <c r="A126" s="68"/>
-      <c r="B126" s="374"/>
+      <c r="B126" s="404"/>
       <c r="C126" s="69"/>
       <c r="D126" s="66"/>
       <c r="E126" s="70"/>
@@ -13561,7 +13542,7 @@
     </row>
     <row r="127" spans="1:29" ht="15.75" customHeight="1">
       <c r="A127" s="68"/>
-      <c r="B127" s="374"/>
+      <c r="B127" s="404"/>
       <c r="C127" s="69"/>
       <c r="D127" s="66"/>
       <c r="E127" s="70"/>
@@ -13592,7 +13573,7 @@
     </row>
     <row r="128" spans="1:29" ht="15.75" customHeight="1">
       <c r="A128" s="68"/>
-      <c r="B128" s="374"/>
+      <c r="B128" s="404"/>
       <c r="C128" s="69"/>
       <c r="D128" s="66"/>
       <c r="E128" s="70"/>
@@ -13623,7 +13604,7 @@
     </row>
     <row r="129" spans="1:29" ht="15.75" customHeight="1">
       <c r="A129" s="68"/>
-      <c r="B129" s="374"/>
+      <c r="B129" s="404"/>
       <c r="C129" s="69"/>
       <c r="D129" s="66"/>
       <c r="E129" s="70"/>
@@ -13654,7 +13635,7 @@
     </row>
     <row r="130" spans="1:29" ht="15.75" customHeight="1">
       <c r="A130" s="68"/>
-      <c r="B130" s="374"/>
+      <c r="B130" s="404"/>
       <c r="C130" s="69"/>
       <c r="D130" s="71"/>
       <c r="E130" s="70"/>
@@ -13685,9 +13666,9 @@
     </row>
     <row r="131" spans="1:29" ht="15.75" customHeight="1">
       <c r="A131" s="68"/>
-      <c r="B131" s="374"/>
+      <c r="B131" s="404"/>
       <c r="C131" s="69"/>
-      <c r="D131" s="458"/>
+      <c r="D131" s="424"/>
       <c r="E131" s="70"/>
       <c r="F131" s="65"/>
       <c r="G131" s="44"/>
@@ -13716,9 +13697,9 @@
     </row>
     <row r="132" spans="1:29" ht="15.75" customHeight="1">
       <c r="A132" s="68"/>
-      <c r="B132" s="374"/>
+      <c r="B132" s="404"/>
       <c r="C132" s="69"/>
-      <c r="D132" s="374"/>
+      <c r="D132" s="404"/>
       <c r="E132" s="70"/>
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
@@ -13747,9 +13728,9 @@
     </row>
     <row r="133" spans="1:29" ht="15.75" customHeight="1">
       <c r="A133" s="68"/>
-      <c r="B133" s="374"/>
+      <c r="B133" s="404"/>
       <c r="C133" s="69"/>
-      <c r="D133" s="374"/>
+      <c r="D133" s="404"/>
       <c r="E133" s="72"/>
       <c r="F133" s="49"/>
       <c r="G133" s="44"/>
@@ -13778,9 +13759,9 @@
     </row>
     <row r="134" spans="1:29" ht="15.75" customHeight="1">
       <c r="A134" s="68"/>
-      <c r="B134" s="374"/>
+      <c r="B134" s="404"/>
       <c r="C134" s="69"/>
-      <c r="D134" s="374"/>
+      <c r="D134" s="404"/>
       <c r="E134" s="72"/>
       <c r="F134" s="49"/>
       <c r="G134" s="44"/>
@@ -13809,9 +13790,9 @@
     </row>
     <row r="135" spans="1:29" ht="15.75" customHeight="1">
       <c r="A135" s="68"/>
-      <c r="B135" s="374"/>
+      <c r="B135" s="404"/>
       <c r="C135" s="69"/>
-      <c r="D135" s="375"/>
+      <c r="D135" s="405"/>
       <c r="E135" s="72"/>
       <c r="F135" s="49"/>
       <c r="G135" s="44"/>
@@ -13840,7 +13821,7 @@
     </row>
     <row r="136" spans="1:29" ht="15.75" customHeight="1">
       <c r="A136" s="68"/>
-      <c r="B136" s="374"/>
+      <c r="B136" s="404"/>
       <c r="C136" s="69"/>
       <c r="D136" s="73"/>
       <c r="E136" s="74"/>
@@ -13871,9 +13852,9 @@
     </row>
     <row r="137" spans="1:29" ht="15.75" customHeight="1">
       <c r="A137" s="68"/>
-      <c r="B137" s="374"/>
+      <c r="B137" s="404"/>
       <c r="C137" s="69"/>
-      <c r="D137" s="458"/>
+      <c r="D137" s="424"/>
       <c r="E137" s="67"/>
       <c r="F137" s="44"/>
       <c r="G137" s="44"/>
@@ -13902,9 +13883,9 @@
     </row>
     <row r="138" spans="1:29" ht="15.75" customHeight="1">
       <c r="A138" s="68"/>
-      <c r="B138" s="374"/>
+      <c r="B138" s="404"/>
       <c r="C138" s="69"/>
-      <c r="D138" s="375"/>
+      <c r="D138" s="405"/>
       <c r="E138" s="67"/>
       <c r="F138" s="44"/>
       <c r="G138" s="44"/>
@@ -13933,7 +13914,7 @@
     </row>
     <row r="139" spans="1:29" ht="15.75" customHeight="1">
       <c r="A139" s="68"/>
-      <c r="B139" s="374"/>
+      <c r="B139" s="404"/>
       <c r="C139" s="69"/>
       <c r="D139" s="75"/>
       <c r="E139" s="70"/>
@@ -13964,9 +13945,9 @@
     </row>
     <row r="140" spans="1:29" ht="15.75" customHeight="1">
       <c r="A140" s="68"/>
-      <c r="B140" s="374"/>
+      <c r="B140" s="404"/>
       <c r="C140" s="69"/>
-      <c r="D140" s="459"/>
+      <c r="D140" s="425"/>
       <c r="E140" s="70"/>
       <c r="F140" s="44"/>
       <c r="G140" s="44"/>
@@ -13995,9 +13976,9 @@
     </row>
     <row r="141" spans="1:29" ht="15.75" customHeight="1">
       <c r="A141" s="68"/>
-      <c r="B141" s="374"/>
+      <c r="B141" s="404"/>
       <c r="C141" s="69"/>
-      <c r="D141" s="374"/>
+      <c r="D141" s="404"/>
       <c r="E141" s="70"/>
       <c r="F141" s="44"/>
       <c r="G141" s="44"/>
@@ -14026,9 +14007,9 @@
     </row>
     <row r="142" spans="1:29" ht="15.75" customHeight="1">
       <c r="A142" s="68"/>
-      <c r="B142" s="374"/>
+      <c r="B142" s="404"/>
       <c r="C142" s="69"/>
-      <c r="D142" s="374"/>
+      <c r="D142" s="404"/>
       <c r="E142" s="72"/>
       <c r="F142" s="49"/>
       <c r="G142" s="44"/>
@@ -14057,9 +14038,9 @@
     </row>
     <row r="143" spans="1:29" ht="15.75" customHeight="1">
       <c r="A143" s="68"/>
-      <c r="B143" s="374"/>
+      <c r="B143" s="404"/>
       <c r="C143" s="69"/>
-      <c r="D143" s="374"/>
+      <c r="D143" s="404"/>
       <c r="E143" s="67"/>
       <c r="F143" s="44"/>
       <c r="G143" s="44"/>
@@ -14088,9 +14069,9 @@
     </row>
     <row r="144" spans="1:29" ht="15.75" customHeight="1">
       <c r="A144" s="68"/>
-      <c r="B144" s="374"/>
+      <c r="B144" s="404"/>
       <c r="C144" s="69"/>
-      <c r="D144" s="374"/>
+      <c r="D144" s="404"/>
       <c r="E144" s="67"/>
       <c r="F144" s="44"/>
       <c r="G144" s="44"/>
@@ -14119,9 +14100,9 @@
     </row>
     <row r="145" spans="1:29" ht="15.75" customHeight="1">
       <c r="A145" s="68"/>
-      <c r="B145" s="374"/>
+      <c r="B145" s="404"/>
       <c r="C145" s="69"/>
-      <c r="D145" s="374"/>
+      <c r="D145" s="404"/>
       <c r="E145" s="70"/>
       <c r="F145" s="44"/>
       <c r="G145" s="44"/>
@@ -14150,9 +14131,9 @@
     </row>
     <row r="146" spans="1:29" ht="15.75" customHeight="1">
       <c r="A146" s="68"/>
-      <c r="B146" s="374"/>
+      <c r="B146" s="404"/>
       <c r="C146" s="69"/>
-      <c r="D146" s="374"/>
+      <c r="D146" s="404"/>
       <c r="E146" s="70"/>
       <c r="F146" s="44"/>
       <c r="G146" s="44"/>
@@ -14181,9 +14162,9 @@
     </row>
     <row r="147" spans="1:29" ht="15.75" customHeight="1">
       <c r="A147" s="68"/>
-      <c r="B147" s="374"/>
+      <c r="B147" s="404"/>
       <c r="C147" s="69"/>
-      <c r="D147" s="374"/>
+      <c r="D147" s="404"/>
       <c r="E147" s="70"/>
       <c r="F147" s="44"/>
       <c r="G147" s="44"/>
@@ -14212,9 +14193,9 @@
     </row>
     <row r="148" spans="1:29" ht="15.75" customHeight="1">
       <c r="A148" s="68"/>
-      <c r="B148" s="374"/>
+      <c r="B148" s="404"/>
       <c r="C148" s="69"/>
-      <c r="D148" s="374"/>
+      <c r="D148" s="404"/>
       <c r="E148" s="72"/>
       <c r="F148" s="49"/>
       <c r="G148" s="44"/>
@@ -14243,9 +14224,9 @@
     </row>
     <row r="149" spans="1:29" ht="15.75" customHeight="1">
       <c r="A149" s="68"/>
-      <c r="B149" s="374"/>
+      <c r="B149" s="404"/>
       <c r="C149" s="69"/>
-      <c r="D149" s="374"/>
+      <c r="D149" s="404"/>
       <c r="E149" s="74"/>
       <c r="F149" s="45"/>
       <c r="G149" s="45"/>
@@ -14274,9 +14255,9 @@
     </row>
     <row r="150" spans="1:29" ht="15.75" customHeight="1">
       <c r="A150" s="68"/>
-      <c r="B150" s="374"/>
+      <c r="B150" s="404"/>
       <c r="C150" s="69"/>
-      <c r="D150" s="375"/>
+      <c r="D150" s="405"/>
       <c r="E150" s="67"/>
       <c r="F150" s="44"/>
       <c r="G150" s="44"/>
@@ -14305,7 +14286,7 @@
     </row>
     <row r="151" spans="1:29" ht="15.75" customHeight="1">
       <c r="A151" s="68"/>
-      <c r="B151" s="374"/>
+      <c r="B151" s="404"/>
       <c r="C151" s="69"/>
       <c r="D151" s="75"/>
       <c r="E151" s="67"/>
@@ -14336,9 +14317,9 @@
     </row>
     <row r="152" spans="1:29" ht="15.75" customHeight="1">
       <c r="A152" s="68"/>
-      <c r="B152" s="374"/>
+      <c r="B152" s="404"/>
       <c r="C152" s="69"/>
-      <c r="D152" s="423"/>
+      <c r="D152" s="441"/>
       <c r="E152" s="70"/>
       <c r="F152" s="44"/>
       <c r="G152" s="44"/>
@@ -14367,9 +14348,9 @@
     </row>
     <row r="153" spans="1:29" ht="15.75" customHeight="1">
       <c r="A153" s="68"/>
-      <c r="B153" s="374"/>
+      <c r="B153" s="404"/>
       <c r="C153" s="69"/>
-      <c r="D153" s="382"/>
+      <c r="D153" s="419"/>
       <c r="E153" s="70"/>
       <c r="F153" s="44"/>
       <c r="G153" s="44"/>
@@ -14398,9 +14379,9 @@
     </row>
     <row r="154" spans="1:29" ht="15.75" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="374"/>
+      <c r="B154" s="404"/>
       <c r="C154" s="69"/>
-      <c r="D154" s="382"/>
+      <c r="D154" s="419"/>
       <c r="E154" s="70"/>
       <c r="F154" s="44"/>
       <c r="G154" s="44"/>
@@ -14429,9 +14410,9 @@
     </row>
     <row r="155" spans="1:29" ht="15.75" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="374"/>
+      <c r="B155" s="404"/>
       <c r="C155" s="69"/>
-      <c r="D155" s="382"/>
+      <c r="D155" s="419"/>
       <c r="E155" s="72"/>
       <c r="F155" s="49"/>
       <c r="G155" s="44"/>
@@ -14460,9 +14441,9 @@
     </row>
     <row r="156" spans="1:29" ht="15.75" customHeight="1">
       <c r="A156" s="77"/>
-      <c r="B156" s="374"/>
+      <c r="B156" s="404"/>
       <c r="C156" s="78"/>
-      <c r="D156" s="382"/>
+      <c r="D156" s="419"/>
       <c r="E156" s="79"/>
       <c r="F156" s="80"/>
       <c r="G156" s="80"/>
@@ -14491,9 +14472,9 @@
     </row>
     <row r="157" spans="1:29" ht="15.75" customHeight="1">
       <c r="A157" s="83"/>
-      <c r="B157" s="374"/>
+      <c r="B157" s="404"/>
       <c r="C157" s="78"/>
-      <c r="D157" s="382"/>
+      <c r="D157" s="419"/>
       <c r="E157" s="84"/>
       <c r="F157" s="85"/>
       <c r="G157" s="86"/>
@@ -14522,9 +14503,9 @@
     </row>
     <row r="158" spans="1:29" ht="15.75" customHeight="1">
       <c r="A158" s="83"/>
-      <c r="B158" s="374"/>
+      <c r="B158" s="404"/>
       <c r="C158" s="78"/>
-      <c r="D158" s="382"/>
+      <c r="D158" s="419"/>
       <c r="E158" s="90"/>
       <c r="F158" s="91"/>
       <c r="G158" s="91"/>
@@ -14553,9 +14534,9 @@
     </row>
     <row r="159" spans="1:29" ht="15.75" customHeight="1">
       <c r="A159" s="83"/>
-      <c r="B159" s="374"/>
+      <c r="B159" s="404"/>
       <c r="C159" s="78"/>
-      <c r="D159" s="382"/>
+      <c r="D159" s="419"/>
       <c r="E159" s="90"/>
       <c r="F159" s="91"/>
       <c r="G159" s="91"/>
@@ -14584,9 +14565,9 @@
     </row>
     <row r="160" spans="1:29" ht="15.75" customHeight="1">
       <c r="A160" s="83"/>
-      <c r="B160" s="374"/>
+      <c r="B160" s="404"/>
       <c r="C160" s="78"/>
-      <c r="D160" s="382"/>
+      <c r="D160" s="419"/>
       <c r="E160" s="94"/>
       <c r="F160" s="91"/>
       <c r="G160" s="91"/>
@@ -14615,9 +14596,9 @@
     </row>
     <row r="161" spans="1:29" ht="15.75" customHeight="1">
       <c r="A161" s="83"/>
-      <c r="B161" s="374"/>
+      <c r="B161" s="404"/>
       <c r="C161" s="78"/>
-      <c r="D161" s="382"/>
+      <c r="D161" s="419"/>
       <c r="E161" s="95"/>
       <c r="F161" s="85"/>
       <c r="G161" s="86"/>
@@ -14646,7 +14627,7 @@
     </row>
     <row r="162" spans="1:29" ht="15.75" customHeight="1">
       <c r="A162" s="83"/>
-      <c r="B162" s="374"/>
+      <c r="B162" s="404"/>
       <c r="C162" s="78"/>
       <c r="D162" s="96"/>
       <c r="E162" s="84"/>
@@ -14677,9 +14658,9 @@
     </row>
     <row r="163" spans="1:29" ht="15.75" customHeight="1">
       <c r="A163" s="83"/>
-      <c r="B163" s="374"/>
+      <c r="B163" s="404"/>
       <c r="C163" s="78"/>
-      <c r="D163" s="424"/>
+      <c r="D163" s="436"/>
       <c r="E163" s="97"/>
       <c r="F163" s="85"/>
       <c r="G163" s="86"/>
@@ -14708,9 +14689,9 @@
     </row>
     <row r="164" spans="1:29" ht="15.75" customHeight="1">
       <c r="A164" s="83"/>
-      <c r="B164" s="374"/>
+      <c r="B164" s="404"/>
       <c r="C164" s="78"/>
-      <c r="D164" s="425"/>
+      <c r="D164" s="407"/>
       <c r="E164" s="99"/>
       <c r="F164" s="91"/>
       <c r="G164" s="91"/>
@@ -14739,7 +14720,7 @@
     </row>
     <row r="165" spans="1:29" ht="15.75" customHeight="1">
       <c r="A165" s="83"/>
-      <c r="B165" s="374"/>
+      <c r="B165" s="404"/>
       <c r="C165" s="78"/>
       <c r="D165" s="100"/>
       <c r="E165" s="101"/>
@@ -14770,9 +14751,9 @@
     </row>
     <row r="166" spans="1:29" ht="15.75" customHeight="1">
       <c r="A166" s="83"/>
-      <c r="B166" s="374"/>
+      <c r="B166" s="404"/>
       <c r="C166" s="78"/>
-      <c r="D166" s="426"/>
+      <c r="D166" s="442"/>
       <c r="E166" s="99"/>
       <c r="F166" s="91"/>
       <c r="G166" s="91"/>
@@ -14801,9 +14782,9 @@
     </row>
     <row r="167" spans="1:29" ht="15.75" customHeight="1">
       <c r="A167" s="83"/>
-      <c r="B167" s="374"/>
+      <c r="B167" s="404"/>
       <c r="C167" s="78"/>
-      <c r="D167" s="425"/>
+      <c r="D167" s="407"/>
       <c r="E167" s="97"/>
       <c r="F167" s="91"/>
       <c r="G167" s="91"/>
@@ -14832,9 +14813,9 @@
     </row>
     <row r="168" spans="1:29" ht="15.75" customHeight="1">
       <c r="A168" s="83"/>
-      <c r="B168" s="374"/>
+      <c r="B168" s="404"/>
       <c r="C168" s="78"/>
-      <c r="D168" s="425"/>
+      <c r="D168" s="407"/>
       <c r="E168" s="99"/>
       <c r="F168" s="91"/>
       <c r="G168" s="91"/>
@@ -14863,9 +14844,9 @@
     </row>
     <row r="169" spans="1:29" ht="15.75" customHeight="1">
       <c r="A169" s="83"/>
-      <c r="B169" s="374"/>
+      <c r="B169" s="404"/>
       <c r="C169" s="78"/>
-      <c r="D169" s="425"/>
+      <c r="D169" s="407"/>
       <c r="E169" s="97"/>
       <c r="F169" s="85"/>
       <c r="G169" s="86"/>
@@ -14894,9 +14875,9 @@
     </row>
     <row r="170" spans="1:29" ht="15.75" customHeight="1">
       <c r="A170" s="83"/>
-      <c r="B170" s="374"/>
+      <c r="B170" s="404"/>
       <c r="C170" s="78"/>
-      <c r="D170" s="425"/>
+      <c r="D170" s="407"/>
       <c r="E170" s="102"/>
       <c r="F170" s="103"/>
       <c r="G170" s="93"/>
@@ -14925,9 +14906,9 @@
     </row>
     <row r="171" spans="1:29" ht="15.75" customHeight="1">
       <c r="A171" s="83"/>
-      <c r="B171" s="374"/>
+      <c r="B171" s="404"/>
       <c r="C171" s="78"/>
-      <c r="D171" s="425"/>
+      <c r="D171" s="407"/>
       <c r="E171" s="97"/>
       <c r="F171" s="104"/>
       <c r="G171" s="86"/>
@@ -14956,9 +14937,9 @@
     </row>
     <row r="172" spans="1:29" ht="15.75" customHeight="1">
       <c r="A172" s="83"/>
-      <c r="B172" s="374"/>
+      <c r="B172" s="404"/>
       <c r="C172" s="78"/>
-      <c r="D172" s="427"/>
+      <c r="D172" s="410"/>
       <c r="E172" s="102"/>
       <c r="F172" s="105"/>
       <c r="G172" s="93"/>
@@ -14987,7 +14968,7 @@
     </row>
     <row r="173" spans="1:29" ht="15.75" customHeight="1">
       <c r="A173" s="83"/>
-      <c r="B173" s="374"/>
+      <c r="B173" s="404"/>
       <c r="C173" s="78"/>
       <c r="D173" s="106"/>
       <c r="E173" s="102"/>
@@ -15018,9 +14999,9 @@
     </row>
     <row r="174" spans="1:29" ht="15.75" customHeight="1">
       <c r="A174" s="83"/>
-      <c r="B174" s="374"/>
+      <c r="B174" s="404"/>
       <c r="C174" s="78"/>
-      <c r="D174" s="454"/>
+      <c r="D174" s="418"/>
       <c r="E174" s="107"/>
       <c r="F174" s="108"/>
       <c r="G174" s="93"/>
@@ -15049,9 +15030,9 @@
     </row>
     <row r="175" spans="1:29" ht="15.75" customHeight="1">
       <c r="A175" s="83"/>
-      <c r="B175" s="374"/>
+      <c r="B175" s="404"/>
       <c r="C175" s="78"/>
-      <c r="D175" s="382"/>
+      <c r="D175" s="419"/>
       <c r="E175" s="102"/>
       <c r="F175" s="108"/>
       <c r="G175" s="93"/>
@@ -15080,9 +15061,9 @@
     </row>
     <row r="176" spans="1:29" ht="15.75" customHeight="1">
       <c r="A176" s="83"/>
-      <c r="B176" s="374"/>
+      <c r="B176" s="404"/>
       <c r="C176" s="78"/>
-      <c r="D176" s="382"/>
+      <c r="D176" s="419"/>
       <c r="E176" s="109"/>
       <c r="F176" s="98"/>
       <c r="G176" s="98"/>
@@ -15111,9 +15092,9 @@
     </row>
     <row r="177" spans="1:29" ht="15.75" customHeight="1">
       <c r="A177" s="83"/>
-      <c r="B177" s="374"/>
+      <c r="B177" s="404"/>
       <c r="C177" s="78"/>
-      <c r="D177" s="382"/>
+      <c r="D177" s="419"/>
       <c r="E177" s="109"/>
       <c r="F177" s="98"/>
       <c r="G177" s="98"/>
@@ -15142,9 +15123,9 @@
     </row>
     <row r="178" spans="1:29" ht="15.75" customHeight="1">
       <c r="A178" s="83"/>
-      <c r="B178" s="374"/>
+      <c r="B178" s="404"/>
       <c r="C178" s="78"/>
-      <c r="D178" s="382"/>
+      <c r="D178" s="419"/>
       <c r="E178" s="109"/>
       <c r="F178" s="98"/>
       <c r="G178" s="98"/>
@@ -15173,9 +15154,9 @@
     </row>
     <row r="179" spans="1:29" ht="15.75" customHeight="1">
       <c r="A179" s="83"/>
-      <c r="B179" s="374"/>
+      <c r="B179" s="404"/>
       <c r="C179" s="78"/>
-      <c r="D179" s="382"/>
+      <c r="D179" s="419"/>
       <c r="E179" s="109"/>
       <c r="F179" s="98"/>
       <c r="G179" s="98"/>
@@ -15204,9 +15185,9 @@
     </row>
     <row r="180" spans="1:29" ht="15.75" customHeight="1">
       <c r="A180" s="83"/>
-      <c r="B180" s="374"/>
+      <c r="B180" s="404"/>
       <c r="C180" s="78"/>
-      <c r="D180" s="382"/>
+      <c r="D180" s="419"/>
       <c r="E180" s="109"/>
       <c r="F180" s="98"/>
       <c r="G180" s="98"/>
@@ -15235,9 +15216,9 @@
     </row>
     <row r="181" spans="1:29" ht="15.75" customHeight="1">
       <c r="A181" s="83"/>
-      <c r="B181" s="374"/>
+      <c r="B181" s="404"/>
       <c r="C181" s="78"/>
-      <c r="D181" s="382"/>
+      <c r="D181" s="419"/>
       <c r="E181" s="109"/>
       <c r="F181" s="98"/>
       <c r="G181" s="98"/>
@@ -15266,9 +15247,9 @@
     </row>
     <row r="182" spans="1:29" ht="15.75" customHeight="1">
       <c r="A182" s="83"/>
-      <c r="B182" s="374"/>
+      <c r="B182" s="404"/>
       <c r="C182" s="78"/>
-      <c r="D182" s="455"/>
+      <c r="D182" s="420"/>
       <c r="E182" s="109"/>
       <c r="F182" s="98"/>
       <c r="G182" s="98"/>
@@ -15297,7 +15278,7 @@
     </row>
     <row r="183" spans="1:29" ht="15.75" customHeight="1">
       <c r="A183" s="83"/>
-      <c r="B183" s="374"/>
+      <c r="B183" s="404"/>
       <c r="C183" s="110"/>
       <c r="D183" s="111"/>
       <c r="E183" s="109"/>
@@ -15328,7 +15309,7 @@
     </row>
     <row r="184" spans="1:29" ht="15.75" customHeight="1">
       <c r="A184" s="83"/>
-      <c r="B184" s="374"/>
+      <c r="B184" s="404"/>
       <c r="C184" s="112"/>
       <c r="D184" s="111"/>
       <c r="E184" s="109"/>
@@ -15359,7 +15340,7 @@
     </row>
     <row r="185" spans="1:29" ht="15.75" customHeight="1">
       <c r="A185" s="83"/>
-      <c r="B185" s="374"/>
+      <c r="B185" s="404"/>
       <c r="C185" s="112"/>
       <c r="D185" s="113"/>
       <c r="E185" s="109"/>
@@ -15390,9 +15371,9 @@
     </row>
     <row r="186" spans="1:29" ht="15.75" customHeight="1">
       <c r="A186" s="83"/>
-      <c r="B186" s="374"/>
+      <c r="B186" s="404"/>
       <c r="C186" s="112"/>
-      <c r="D186" s="456"/>
+      <c r="D186" s="421"/>
       <c r="E186" s="115"/>
       <c r="F186" s="98"/>
       <c r="G186" s="98"/>
@@ -15421,9 +15402,9 @@
     </row>
     <row r="187" spans="1:29" ht="15.75" customHeight="1">
       <c r="A187" s="83"/>
-      <c r="B187" s="374"/>
+      <c r="B187" s="404"/>
       <c r="C187" s="112"/>
-      <c r="D187" s="427"/>
+      <c r="D187" s="410"/>
       <c r="E187" s="115"/>
       <c r="F187" s="98"/>
       <c r="G187" s="98"/>
@@ -15452,7 +15433,7 @@
     </row>
     <row r="188" spans="1:29" ht="15.75" customHeight="1">
       <c r="A188" s="83"/>
-      <c r="B188" s="374"/>
+      <c r="B188" s="404"/>
       <c r="C188" s="112"/>
       <c r="D188" s="116"/>
       <c r="E188" s="109"/>
@@ -15483,7 +15464,7 @@
     </row>
     <row r="189" spans="1:29" ht="15.75" customHeight="1">
       <c r="A189" s="83"/>
-      <c r="B189" s="374"/>
+      <c r="B189" s="404"/>
       <c r="C189" s="112"/>
       <c r="D189" s="117"/>
       <c r="E189" s="109"/>
@@ -15514,7 +15495,7 @@
     </row>
     <row r="190" spans="1:29" ht="15.75" customHeight="1">
       <c r="A190" s="83"/>
-      <c r="B190" s="374"/>
+      <c r="B190" s="404"/>
       <c r="C190" s="112"/>
       <c r="D190" s="117"/>
       <c r="E190" s="118"/>
@@ -15545,7 +15526,7 @@
     </row>
     <row r="191" spans="1:29" ht="15.75" customHeight="1">
       <c r="A191" s="83"/>
-      <c r="B191" s="374"/>
+      <c r="B191" s="404"/>
       <c r="C191" s="112"/>
       <c r="D191" s="117"/>
       <c r="E191" s="109"/>
@@ -15576,7 +15557,7 @@
     </row>
     <row r="192" spans="1:29" ht="15.75" customHeight="1">
       <c r="A192" s="83"/>
-      <c r="B192" s="374"/>
+      <c r="B192" s="404"/>
       <c r="C192" s="112"/>
       <c r="D192" s="117"/>
       <c r="E192" s="109"/>
@@ -15607,7 +15588,7 @@
     </row>
     <row r="193" spans="1:29" ht="15.75" customHeight="1">
       <c r="A193" s="83"/>
-      <c r="B193" s="374"/>
+      <c r="B193" s="404"/>
       <c r="C193" s="112"/>
       <c r="D193" s="117"/>
       <c r="E193" s="109"/>
@@ -15638,7 +15619,7 @@
     </row>
     <row r="194" spans="1:29" ht="15.75" customHeight="1">
       <c r="A194" s="83"/>
-      <c r="B194" s="374"/>
+      <c r="B194" s="404"/>
       <c r="C194" s="112"/>
       <c r="D194" s="117"/>
       <c r="E194" s="109"/>
@@ -15669,7 +15650,7 @@
     </row>
     <row r="195" spans="1:29" ht="15.75" customHeight="1">
       <c r="A195" s="83"/>
-      <c r="B195" s="374"/>
+      <c r="B195" s="404"/>
       <c r="C195" s="112"/>
       <c r="D195" s="117"/>
       <c r="E195" s="118"/>
@@ -15700,7 +15681,7 @@
     </row>
     <row r="196" spans="1:29" ht="15.75" customHeight="1">
       <c r="A196" s="83"/>
-      <c r="B196" s="374"/>
+      <c r="B196" s="404"/>
       <c r="C196" s="112"/>
       <c r="D196" s="117"/>
       <c r="E196" s="118"/>
@@ -15731,7 +15712,7 @@
     </row>
     <row r="197" spans="1:29" ht="15.75" customHeight="1">
       <c r="A197" s="83"/>
-      <c r="B197" s="374"/>
+      <c r="B197" s="404"/>
       <c r="C197" s="112"/>
       <c r="D197" s="117"/>
       <c r="E197" s="118"/>
@@ -15762,7 +15743,7 @@
     </row>
     <row r="198" spans="1:29" ht="15.75" customHeight="1">
       <c r="A198" s="83"/>
-      <c r="B198" s="374"/>
+      <c r="B198" s="404"/>
       <c r="C198" s="112"/>
       <c r="D198" s="117"/>
       <c r="E198" s="109"/>
@@ -15793,7 +15774,7 @@
     </row>
     <row r="199" spans="1:29" ht="15.75" customHeight="1">
       <c r="A199" s="83"/>
-      <c r="B199" s="374"/>
+      <c r="B199" s="404"/>
       <c r="C199" s="112"/>
       <c r="D199" s="117"/>
       <c r="E199" s="109"/>
@@ -15824,7 +15805,7 @@
     </row>
     <row r="200" spans="1:29" ht="15.75" customHeight="1">
       <c r="A200" s="83"/>
-      <c r="B200" s="374"/>
+      <c r="B200" s="404"/>
       <c r="C200" s="112"/>
       <c r="D200" s="117"/>
       <c r="E200" s="109"/>
@@ -15855,7 +15836,7 @@
     </row>
     <row r="201" spans="1:29" ht="15.75" customHeight="1">
       <c r="A201" s="83"/>
-      <c r="B201" s="374"/>
+      <c r="B201" s="404"/>
       <c r="C201" s="112"/>
       <c r="D201" s="117"/>
       <c r="E201" s="109"/>
@@ -15886,7 +15867,7 @@
     </row>
     <row r="202" spans="1:29" ht="15.75" customHeight="1">
       <c r="A202" s="83"/>
-      <c r="B202" s="374"/>
+      <c r="B202" s="404"/>
       <c r="C202" s="112"/>
       <c r="D202" s="117"/>
       <c r="E202" s="109"/>
@@ -15917,7 +15898,7 @@
     </row>
     <row r="203" spans="1:29" ht="15.75" customHeight="1">
       <c r="A203" s="83"/>
-      <c r="B203" s="374"/>
+      <c r="B203" s="404"/>
       <c r="C203" s="112"/>
       <c r="D203" s="117"/>
       <c r="E203" s="109"/>
@@ -15948,7 +15929,7 @@
     </row>
     <row r="204" spans="1:29" ht="15.75" customHeight="1">
       <c r="A204" s="123"/>
-      <c r="B204" s="374"/>
+      <c r="B204" s="404"/>
       <c r="C204" s="112"/>
       <c r="D204" s="124"/>
       <c r="E204" s="125"/>
@@ -15979,7 +15960,7 @@
     </row>
     <row r="205" spans="1:29" ht="15.75" customHeight="1">
       <c r="A205" s="123"/>
-      <c r="B205" s="374"/>
+      <c r="B205" s="404"/>
       <c r="C205" s="112"/>
       <c r="D205" s="126"/>
       <c r="E205" s="109"/>
@@ -16010,7 +15991,7 @@
     </row>
     <row r="206" spans="1:29" ht="15.75" customHeight="1">
       <c r="A206" s="123"/>
-      <c r="B206" s="374"/>
+      <c r="B206" s="404"/>
       <c r="C206" s="112"/>
       <c r="D206" s="126"/>
       <c r="E206" s="109"/>
@@ -16041,7 +16022,7 @@
     </row>
     <row r="207" spans="1:29" ht="15.75" customHeight="1">
       <c r="A207" s="123"/>
-      <c r="B207" s="374"/>
+      <c r="B207" s="404"/>
       <c r="C207" s="112"/>
       <c r="D207" s="126"/>
       <c r="E207" s="127"/>
@@ -16072,7 +16053,7 @@
     </row>
     <row r="208" spans="1:29" ht="15.75" customHeight="1">
       <c r="A208" s="123"/>
-      <c r="B208" s="374"/>
+      <c r="B208" s="404"/>
       <c r="C208" s="112"/>
       <c r="D208" s="126"/>
       <c r="E208" s="128"/>
@@ -16103,7 +16084,7 @@
     </row>
     <row r="209" spans="1:29" ht="15.75" customHeight="1">
       <c r="A209" s="123"/>
-      <c r="B209" s="374"/>
+      <c r="B209" s="404"/>
       <c r="C209" s="112"/>
       <c r="D209" s="126"/>
       <c r="E209" s="128"/>
@@ -16134,7 +16115,7 @@
     </row>
     <row r="210" spans="1:29" ht="15.75" customHeight="1">
       <c r="A210" s="123"/>
-      <c r="B210" s="374"/>
+      <c r="B210" s="404"/>
       <c r="C210" s="112"/>
       <c r="D210" s="126"/>
       <c r="E210" s="128"/>
@@ -16165,7 +16146,7 @@
     </row>
     <row r="211" spans="1:29" ht="15.75" customHeight="1">
       <c r="A211" s="123"/>
-      <c r="B211" s="374"/>
+      <c r="B211" s="404"/>
       <c r="C211" s="112"/>
       <c r="D211" s="126"/>
       <c r="E211" s="128"/>
@@ -16196,7 +16177,7 @@
     </row>
     <row r="212" spans="1:29" ht="15.75" customHeight="1">
       <c r="A212" s="123"/>
-      <c r="B212" s="374"/>
+      <c r="B212" s="404"/>
       <c r="C212" s="112"/>
       <c r="D212" s="126"/>
       <c r="E212" s="109"/>
@@ -16227,7 +16208,7 @@
     </row>
     <row r="213" spans="1:29" ht="15.75" customHeight="1">
       <c r="A213" s="123"/>
-      <c r="B213" s="374"/>
+      <c r="B213" s="404"/>
       <c r="C213" s="112"/>
       <c r="D213" s="126"/>
       <c r="E213" s="109"/>
@@ -16258,7 +16239,7 @@
     </row>
     <row r="214" spans="1:29" ht="15.75" customHeight="1">
       <c r="A214" s="123"/>
-      <c r="B214" s="374"/>
+      <c r="B214" s="404"/>
       <c r="C214" s="112"/>
       <c r="D214" s="126"/>
       <c r="E214" s="109"/>
@@ -16289,7 +16270,7 @@
     </row>
     <row r="215" spans="1:29" ht="15.75" customHeight="1">
       <c r="A215" s="123"/>
-      <c r="B215" s="374"/>
+      <c r="B215" s="404"/>
       <c r="C215" s="112"/>
       <c r="D215" s="126"/>
       <c r="E215" s="109"/>
@@ -16320,7 +16301,7 @@
     </row>
     <row r="216" spans="1:29" ht="15.75" customHeight="1">
       <c r="A216" s="123"/>
-      <c r="B216" s="374"/>
+      <c r="B216" s="404"/>
       <c r="C216" s="112"/>
       <c r="D216" s="126"/>
       <c r="E216" s="125"/>
@@ -16351,7 +16332,7 @@
     </row>
     <row r="217" spans="1:29" ht="15.75" customHeight="1">
       <c r="A217" s="123"/>
-      <c r="B217" s="374"/>
+      <c r="B217" s="404"/>
       <c r="C217" s="112"/>
       <c r="D217" s="129"/>
       <c r="E217" s="130"/>
@@ -16382,7 +16363,7 @@
     </row>
     <row r="218" spans="1:29" ht="15.75" customHeight="1">
       <c r="A218" s="123"/>
-      <c r="B218" s="374"/>
+      <c r="B218" s="404"/>
       <c r="C218" s="112"/>
       <c r="D218" s="131"/>
       <c r="E218" s="125"/>
@@ -16413,9 +16394,9 @@
     </row>
     <row r="219" spans="1:29" ht="15.75" customHeight="1">
       <c r="A219" s="123"/>
-      <c r="B219" s="374"/>
+      <c r="B219" s="404"/>
       <c r="C219" s="112"/>
-      <c r="D219" s="448"/>
+      <c r="D219" s="406"/>
       <c r="E219" s="109"/>
       <c r="F219" s="98"/>
       <c r="G219" s="98"/>
@@ -16424,7 +16405,7 @@
       <c r="J219" s="98"/>
       <c r="K219" s="98"/>
       <c r="L219" s="89"/>
-      <c r="M219" s="440"/>
+      <c r="M219" s="409"/>
       <c r="N219" s="82"/>
       <c r="O219" s="82"/>
       <c r="P219" s="82"/>
@@ -16444,9 +16425,9 @@
     </row>
     <row r="220" spans="1:29" ht="15.75" customHeight="1">
       <c r="A220" s="83"/>
-      <c r="B220" s="374"/>
+      <c r="B220" s="404"/>
       <c r="C220" s="112"/>
-      <c r="D220" s="425"/>
+      <c r="D220" s="407"/>
       <c r="E220" s="109"/>
       <c r="F220" s="98"/>
       <c r="G220" s="98"/>
@@ -16455,7 +16436,7 @@
       <c r="J220" s="98"/>
       <c r="K220" s="98"/>
       <c r="L220" s="89"/>
-      <c r="M220" s="425"/>
+      <c r="M220" s="407"/>
       <c r="N220" s="82"/>
       <c r="O220" s="82"/>
       <c r="P220" s="82"/>
@@ -16475,9 +16456,9 @@
     </row>
     <row r="221" spans="1:29" ht="15.75" customHeight="1">
       <c r="A221" s="83"/>
-      <c r="B221" s="374"/>
+      <c r="B221" s="404"/>
       <c r="C221" s="112"/>
-      <c r="D221" s="425"/>
+      <c r="D221" s="407"/>
       <c r="E221" s="127"/>
       <c r="F221" s="98"/>
       <c r="G221" s="98"/>
@@ -16486,7 +16467,7 @@
       <c r="J221" s="98"/>
       <c r="K221" s="98"/>
       <c r="L221" s="89"/>
-      <c r="M221" s="425"/>
+      <c r="M221" s="407"/>
       <c r="N221" s="82"/>
       <c r="O221" s="82"/>
       <c r="P221" s="82"/>
@@ -16506,9 +16487,9 @@
     </row>
     <row r="222" spans="1:29" ht="15.75" customHeight="1">
       <c r="A222" s="83"/>
-      <c r="B222" s="374"/>
+      <c r="B222" s="404"/>
       <c r="C222" s="112"/>
-      <c r="D222" s="425"/>
+      <c r="D222" s="407"/>
       <c r="E222" s="128"/>
       <c r="F222" s="98"/>
       <c r="G222" s="98"/>
@@ -16517,7 +16498,7 @@
       <c r="J222" s="98"/>
       <c r="K222" s="98"/>
       <c r="L222" s="89"/>
-      <c r="M222" s="425"/>
+      <c r="M222" s="407"/>
       <c r="N222" s="82"/>
       <c r="O222" s="82"/>
       <c r="P222" s="82"/>
@@ -16537,9 +16518,9 @@
     </row>
     <row r="223" spans="1:29" ht="15.75" customHeight="1">
       <c r="A223" s="83"/>
-      <c r="B223" s="374"/>
+      <c r="B223" s="404"/>
       <c r="C223" s="112"/>
-      <c r="D223" s="425"/>
+      <c r="D223" s="407"/>
       <c r="E223" s="128"/>
       <c r="F223" s="98"/>
       <c r="G223" s="98"/>
@@ -16548,7 +16529,7 @@
       <c r="J223" s="98"/>
       <c r="K223" s="98"/>
       <c r="L223" s="89"/>
-      <c r="M223" s="425"/>
+      <c r="M223" s="407"/>
       <c r="N223" s="82"/>
       <c r="O223" s="82"/>
       <c r="P223" s="82"/>
@@ -16568,9 +16549,9 @@
     </row>
     <row r="224" spans="1:29" ht="15.75" customHeight="1">
       <c r="A224" s="83"/>
-      <c r="B224" s="374"/>
+      <c r="B224" s="404"/>
       <c r="C224" s="112"/>
-      <c r="D224" s="425"/>
+      <c r="D224" s="407"/>
       <c r="E224" s="128"/>
       <c r="F224" s="98"/>
       <c r="G224" s="98"/>
@@ -16579,7 +16560,7 @@
       <c r="J224" s="98"/>
       <c r="K224" s="98"/>
       <c r="L224" s="89"/>
-      <c r="M224" s="425"/>
+      <c r="M224" s="407"/>
       <c r="N224" s="82"/>
       <c r="O224" s="82"/>
       <c r="P224" s="82"/>
@@ -16599,9 +16580,9 @@
     </row>
     <row r="225" spans="1:29" ht="15.75" customHeight="1">
       <c r="A225" s="83"/>
-      <c r="B225" s="374"/>
+      <c r="B225" s="404"/>
       <c r="C225" s="112"/>
-      <c r="D225" s="425"/>
+      <c r="D225" s="407"/>
       <c r="E225" s="128"/>
       <c r="F225" s="98"/>
       <c r="G225" s="98"/>
@@ -16610,7 +16591,7 @@
       <c r="J225" s="98"/>
       <c r="K225" s="98"/>
       <c r="L225" s="89"/>
-      <c r="M225" s="425"/>
+      <c r="M225" s="407"/>
       <c r="N225" s="82"/>
       <c r="O225" s="82"/>
       <c r="P225" s="82"/>
@@ -16630,9 +16611,9 @@
     </row>
     <row r="226" spans="1:29" ht="15.75" customHeight="1">
       <c r="A226" s="83"/>
-      <c r="B226" s="374"/>
+      <c r="B226" s="404"/>
       <c r="C226" s="112"/>
-      <c r="D226" s="425"/>
+      <c r="D226" s="407"/>
       <c r="E226" s="109"/>
       <c r="F226" s="98"/>
       <c r="G226" s="98"/>
@@ -16641,7 +16622,7 @@
       <c r="J226" s="98"/>
       <c r="K226" s="98"/>
       <c r="L226" s="89"/>
-      <c r="M226" s="427"/>
+      <c r="M226" s="410"/>
       <c r="N226" s="82"/>
       <c r="O226" s="82"/>
       <c r="P226" s="82"/>
@@ -16661,9 +16642,9 @@
     </row>
     <row r="227" spans="1:29" ht="15.75" customHeight="1">
       <c r="A227" s="83"/>
-      <c r="B227" s="374"/>
+      <c r="B227" s="404"/>
       <c r="C227" s="112"/>
-      <c r="D227" s="425"/>
+      <c r="D227" s="407"/>
       <c r="E227" s="109"/>
       <c r="F227" s="98"/>
       <c r="G227" s="98"/>
@@ -16692,9 +16673,9 @@
     </row>
     <row r="228" spans="1:29" ht="15.75" customHeight="1">
       <c r="A228" s="83"/>
-      <c r="B228" s="374"/>
+      <c r="B228" s="404"/>
       <c r="C228" s="112"/>
-      <c r="D228" s="425"/>
+      <c r="D228" s="407"/>
       <c r="E228" s="109"/>
       <c r="F228" s="98"/>
       <c r="G228" s="98"/>
@@ -16723,9 +16704,9 @@
     </row>
     <row r="229" spans="1:29" ht="15.75" customHeight="1">
       <c r="A229" s="83"/>
-      <c r="B229" s="375"/>
+      <c r="B229" s="405"/>
       <c r="C229" s="112"/>
-      <c r="D229" s="449"/>
+      <c r="D229" s="408"/>
       <c r="E229" s="109"/>
       <c r="F229" s="98"/>
       <c r="G229" s="98"/>
@@ -16789,7 +16770,7 @@
       <c r="C231" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="D231" s="439"/>
+      <c r="D231" s="433"/>
       <c r="E231" s="109"/>
       <c r="F231" s="98"/>
       <c r="G231" s="122"/>
@@ -16820,7 +16801,7 @@
       <c r="A232" s="133"/>
       <c r="B232" s="131"/>
       <c r="C232" s="138"/>
-      <c r="D232" s="425"/>
+      <c r="D232" s="407"/>
       <c r="E232" s="109"/>
       <c r="F232" s="98"/>
       <c r="G232" s="122"/>
@@ -16851,7 +16832,7 @@
       <c r="A233" s="133"/>
       <c r="B233" s="131"/>
       <c r="C233" s="138"/>
-      <c r="D233" s="425"/>
+      <c r="D233" s="407"/>
       <c r="E233" s="109"/>
       <c r="F233" s="98"/>
       <c r="G233" s="122"/>
@@ -16882,7 +16863,7 @@
       <c r="A234" s="133"/>
       <c r="B234" s="131"/>
       <c r="C234" s="131"/>
-      <c r="D234" s="425"/>
+      <c r="D234" s="407"/>
       <c r="E234" s="118"/>
       <c r="F234" s="98"/>
       <c r="G234" s="122"/>
@@ -16913,7 +16894,7 @@
       <c r="A235" s="133"/>
       <c r="B235" s="136"/>
       <c r="C235" s="131"/>
-      <c r="D235" s="425"/>
+      <c r="D235" s="407"/>
       <c r="E235" s="118"/>
       <c r="F235" s="98"/>
       <c r="G235" s="122"/>
@@ -16944,7 +16925,7 @@
       <c r="A236" s="133"/>
       <c r="B236" s="136"/>
       <c r="C236" s="131"/>
-      <c r="D236" s="425"/>
+      <c r="D236" s="407"/>
       <c r="E236" s="118"/>
       <c r="F236" s="98"/>
       <c r="G236" s="122"/>
@@ -16975,7 +16956,7 @@
       <c r="A237" s="133"/>
       <c r="B237" s="136"/>
       <c r="C237" s="131"/>
-      <c r="D237" s="425"/>
+      <c r="D237" s="407"/>
       <c r="E237" s="109"/>
       <c r="F237" s="98"/>
       <c r="G237" s="122"/>
@@ -17006,7 +16987,7 @@
       <c r="A238" s="133"/>
       <c r="B238" s="136"/>
       <c r="C238" s="131"/>
-      <c r="D238" s="425"/>
+      <c r="D238" s="407"/>
       <c r="E238" s="109"/>
       <c r="F238" s="98"/>
       <c r="G238" s="122"/>
@@ -17037,7 +17018,7 @@
       <c r="A239" s="133"/>
       <c r="B239" s="136"/>
       <c r="C239" s="136"/>
-      <c r="D239" s="427"/>
+      <c r="D239" s="410"/>
       <c r="E239" s="109"/>
       <c r="F239" s="98"/>
       <c r="G239" s="122"/>
@@ -18377,8 +18358,8 @@
       <c r="H282" s="157"/>
       <c r="I282" s="157"/>
       <c r="J282" s="157"/>
-      <c r="K282" s="435"/>
-      <c r="L282" s="440"/>
+      <c r="K282" s="434"/>
+      <c r="L282" s="409"/>
       <c r="M282" s="152"/>
       <c r="N282" s="82"/>
       <c r="O282" s="82"/>
@@ -18408,8 +18389,8 @@
       <c r="H283" s="159"/>
       <c r="I283" s="159"/>
       <c r="J283" s="159"/>
-      <c r="K283" s="425"/>
-      <c r="L283" s="425"/>
+      <c r="K283" s="407"/>
+      <c r="L283" s="407"/>
       <c r="M283" s="152"/>
       <c r="N283" s="82"/>
       <c r="O283" s="82"/>
@@ -18439,8 +18420,8 @@
       <c r="H284" s="80"/>
       <c r="I284" s="80"/>
       <c r="J284" s="80"/>
-      <c r="K284" s="427"/>
-      <c r="L284" s="427"/>
+      <c r="K284" s="410"/>
+      <c r="L284" s="410"/>
       <c r="M284" s="152"/>
       <c r="N284" s="82"/>
       <c r="O284" s="82"/>
@@ -18648,9 +18629,9 @@
     <row r="291" spans="1:29" ht="15.75" customHeight="1">
       <c r="A291" s="133"/>
       <c r="B291" s="145"/>
-      <c r="C291" s="436"/>
+      <c r="C291" s="435"/>
       <c r="D291" s="131"/>
-      <c r="E291" s="424"/>
+      <c r="E291" s="436"/>
       <c r="F291" s="91"/>
       <c r="G291" s="91"/>
       <c r="H291" s="91"/>
@@ -18679,9 +18660,9 @@
     <row r="292" spans="1:29" ht="15.75" customHeight="1">
       <c r="A292" s="133"/>
       <c r="B292" s="145"/>
-      <c r="C292" s="425"/>
+      <c r="C292" s="407"/>
       <c r="D292" s="131"/>
-      <c r="E292" s="425"/>
+      <c r="E292" s="407"/>
       <c r="F292" s="91"/>
       <c r="G292" s="91"/>
       <c r="H292" s="91"/>
@@ -18710,9 +18691,9 @@
     <row r="293" spans="1:29" ht="15.75" customHeight="1">
       <c r="A293" s="133"/>
       <c r="B293" s="145"/>
-      <c r="C293" s="425"/>
+      <c r="C293" s="407"/>
       <c r="D293" s="131"/>
-      <c r="E293" s="427"/>
+      <c r="E293" s="410"/>
       <c r="F293" s="91"/>
       <c r="G293" s="91"/>
       <c r="H293" s="91"/>
@@ -18741,7 +18722,7 @@
     <row r="294" spans="1:29" ht="15.75" customHeight="1">
       <c r="A294" s="133"/>
       <c r="B294" s="145"/>
-      <c r="C294" s="425"/>
+      <c r="C294" s="407"/>
       <c r="D294" s="131"/>
       <c r="E294" s="99"/>
       <c r="F294" s="91"/>
@@ -18772,7 +18753,7 @@
     <row r="295" spans="1:29" ht="15.75" customHeight="1">
       <c r="A295" s="133"/>
       <c r="B295" s="145"/>
-      <c r="C295" s="425"/>
+      <c r="C295" s="407"/>
       <c r="D295" s="131"/>
       <c r="E295" s="99"/>
       <c r="F295" s="91"/>
@@ -18803,7 +18784,7 @@
     <row r="296" spans="1:29" ht="15.75" customHeight="1">
       <c r="A296" s="133"/>
       <c r="B296" s="145"/>
-      <c r="C296" s="425"/>
+      <c r="C296" s="407"/>
       <c r="D296" s="131"/>
       <c r="E296" s="99"/>
       <c r="F296" s="155"/>
@@ -18834,7 +18815,7 @@
     <row r="297" spans="1:29" ht="15.75" customHeight="1">
       <c r="A297" s="133"/>
       <c r="B297" s="145"/>
-      <c r="C297" s="427"/>
+      <c r="C297" s="410"/>
       <c r="D297" s="131"/>
       <c r="E297" s="99"/>
       <c r="F297" s="91"/>
@@ -18865,7 +18846,7 @@
     <row r="298" spans="1:29" ht="15.75" customHeight="1">
       <c r="A298" s="133"/>
       <c r="B298" s="145"/>
-      <c r="C298" s="434"/>
+      <c r="C298" s="437"/>
       <c r="D298" s="143"/>
       <c r="E298" s="99"/>
       <c r="F298" s="155"/>
@@ -18896,7 +18877,7 @@
     <row r="299" spans="1:29" ht="15.75" customHeight="1">
       <c r="A299" s="133"/>
       <c r="B299" s="145"/>
-      <c r="C299" s="427"/>
+      <c r="C299" s="410"/>
       <c r="D299" s="163"/>
       <c r="E299" s="99"/>
       <c r="F299" s="155"/>
@@ -18958,7 +18939,7 @@
     <row r="301" spans="1:29" ht="30" customHeight="1">
       <c r="A301" s="133"/>
       <c r="B301" s="145"/>
-      <c r="C301" s="434"/>
+      <c r="C301" s="437"/>
       <c r="D301" s="143"/>
       <c r="E301" s="99"/>
       <c r="F301" s="91"/>
@@ -18989,7 +18970,7 @@
     <row r="302" spans="1:29" ht="15.75" customHeight="1">
       <c r="A302" s="133"/>
       <c r="B302" s="145"/>
-      <c r="C302" s="425"/>
+      <c r="C302" s="407"/>
       <c r="D302" s="144"/>
       <c r="E302" s="99"/>
       <c r="F302" s="91"/>
@@ -19020,7 +19001,7 @@
     <row r="303" spans="1:29" ht="15.75" customHeight="1">
       <c r="A303" s="133"/>
       <c r="B303" s="145"/>
-      <c r="C303" s="425"/>
+      <c r="C303" s="407"/>
       <c r="D303" s="144"/>
       <c r="E303" s="99"/>
       <c r="F303" s="91"/>
@@ -19051,7 +19032,7 @@
     <row r="304" spans="1:29" ht="15.75" customHeight="1">
       <c r="A304" s="133"/>
       <c r="B304" s="145"/>
-      <c r="C304" s="425"/>
+      <c r="C304" s="407"/>
       <c r="D304" s="144"/>
       <c r="E304" s="99"/>
       <c r="F304" s="155"/>
@@ -19082,7 +19063,7 @@
     <row r="305" spans="1:29" ht="15.75" customHeight="1">
       <c r="A305" s="133"/>
       <c r="B305" s="145"/>
-      <c r="C305" s="427"/>
+      <c r="C305" s="410"/>
       <c r="D305" s="144"/>
       <c r="E305" s="165"/>
       <c r="F305" s="91"/>
@@ -19462,7 +19443,7 @@
       <c r="H317" s="155"/>
       <c r="I317" s="155"/>
       <c r="J317" s="155"/>
-      <c r="K317" s="433"/>
+      <c r="K317" s="438"/>
       <c r="L317" s="89"/>
       <c r="M317" s="120"/>
       <c r="N317" s="82"/>
@@ -19493,7 +19474,7 @@
       <c r="H318" s="155"/>
       <c r="I318" s="155"/>
       <c r="J318" s="155"/>
-      <c r="K318" s="427"/>
+      <c r="K318" s="410"/>
       <c r="L318" s="89"/>
       <c r="M318" s="120"/>
       <c r="N318" s="82"/>
@@ -19578,7 +19559,7 @@
     <row r="321" spans="1:29" ht="15.75" customHeight="1">
       <c r="A321" s="133"/>
       <c r="B321" s="145"/>
-      <c r="C321" s="434"/>
+      <c r="C321" s="437"/>
       <c r="D321" s="143"/>
       <c r="E321" s="99"/>
       <c r="F321" s="155"/>
@@ -19586,7 +19567,7 @@
       <c r="H321" s="155"/>
       <c r="I321" s="155"/>
       <c r="J321" s="155"/>
-      <c r="K321" s="435"/>
+      <c r="K321" s="434"/>
       <c r="L321" s="89"/>
       <c r="M321" s="120"/>
       <c r="N321" s="82"/>
@@ -19609,7 +19590,7 @@
     <row r="322" spans="1:29" ht="15.75" customHeight="1">
       <c r="A322" s="133"/>
       <c r="B322" s="145"/>
-      <c r="C322" s="427"/>
+      <c r="C322" s="410"/>
       <c r="D322" s="163"/>
       <c r="E322" s="99"/>
       <c r="F322" s="155"/>
@@ -19617,7 +19598,7 @@
       <c r="H322" s="155"/>
       <c r="I322" s="155"/>
       <c r="J322" s="155"/>
-      <c r="K322" s="427"/>
+      <c r="K322" s="410"/>
       <c r="L322" s="89"/>
       <c r="M322" s="120"/>
       <c r="N322" s="82"/>
@@ -19640,7 +19621,7 @@
     <row r="323" spans="1:29" ht="15.75" customHeight="1">
       <c r="A323" s="133"/>
       <c r="B323" s="145"/>
-      <c r="C323" s="436"/>
+      <c r="C323" s="435"/>
       <c r="D323" s="156"/>
       <c r="E323" s="118"/>
       <c r="F323" s="98"/>
@@ -19671,7 +19652,7 @@
     <row r="324" spans="1:29" ht="15.75" customHeight="1">
       <c r="A324" s="133"/>
       <c r="B324" s="145"/>
-      <c r="C324" s="427"/>
+      <c r="C324" s="410"/>
       <c r="D324" s="116"/>
       <c r="E324" s="118"/>
       <c r="F324" s="98"/>
@@ -19733,7 +19714,7 @@
     <row r="326" spans="1:29" ht="15.75" customHeight="1">
       <c r="A326" s="133"/>
       <c r="B326" s="145"/>
-      <c r="C326" s="434"/>
+      <c r="C326" s="437"/>
       <c r="D326" s="143"/>
       <c r="E326" s="118"/>
       <c r="F326" s="98"/>
@@ -19764,7 +19745,7 @@
     <row r="327" spans="1:29" ht="15.75" customHeight="1">
       <c r="A327" s="133"/>
       <c r="B327" s="145"/>
-      <c r="C327" s="425"/>
+      <c r="C327" s="407"/>
       <c r="D327" s="144"/>
       <c r="E327" s="118"/>
       <c r="F327" s="98"/>
@@ -19795,7 +19776,7 @@
     <row r="328" spans="1:29" ht="15.75" customHeight="1">
       <c r="A328" s="133"/>
       <c r="B328" s="145"/>
-      <c r="C328" s="427"/>
+      <c r="C328" s="410"/>
       <c r="D328" s="163"/>
       <c r="E328" s="118"/>
       <c r="F328" s="98"/>
@@ -19980,10 +19961,10 @@
     </row>
     <row r="334" spans="1:29" ht="15.75" customHeight="1">
       <c r="A334" s="140"/>
-      <c r="B334" s="437"/>
-      <c r="C334" s="436"/>
+      <c r="B334" s="439"/>
+      <c r="C334" s="435"/>
       <c r="D334" s="131"/>
-      <c r="E334" s="436"/>
+      <c r="E334" s="435"/>
       <c r="F334" s="91"/>
       <c r="G334" s="91"/>
       <c r="H334" s="91"/>
@@ -20011,10 +19992,10 @@
     </row>
     <row r="335" spans="1:29" ht="15.75" customHeight="1">
       <c r="A335" s="140"/>
-      <c r="B335" s="425"/>
-      <c r="C335" s="425"/>
+      <c r="B335" s="407"/>
+      <c r="C335" s="407"/>
       <c r="D335" s="131"/>
-      <c r="E335" s="425"/>
+      <c r="E335" s="407"/>
       <c r="F335" s="91"/>
       <c r="G335" s="91"/>
       <c r="H335" s="91"/>
@@ -20042,10 +20023,10 @@
     </row>
     <row r="336" spans="1:29" ht="15.75" customHeight="1">
       <c r="A336" s="140"/>
-      <c r="B336" s="425"/>
-      <c r="C336" s="425"/>
+      <c r="B336" s="407"/>
+      <c r="C336" s="407"/>
       <c r="D336" s="131"/>
-      <c r="E336" s="425"/>
+      <c r="E336" s="407"/>
       <c r="F336" s="91"/>
       <c r="G336" s="91"/>
       <c r="H336" s="91"/>
@@ -20073,10 +20054,10 @@
     </row>
     <row r="337" spans="1:29" ht="15.75" customHeight="1">
       <c r="A337" s="140"/>
-      <c r="B337" s="425"/>
-      <c r="C337" s="425"/>
+      <c r="B337" s="407"/>
+      <c r="C337" s="407"/>
       <c r="D337" s="131"/>
-      <c r="E337" s="425"/>
+      <c r="E337" s="407"/>
       <c r="F337" s="91"/>
       <c r="G337" s="91"/>
       <c r="H337" s="91"/>
@@ -20104,10 +20085,10 @@
     </row>
     <row r="338" spans="1:29" ht="15.75" customHeight="1">
       <c r="A338" s="140"/>
-      <c r="B338" s="425"/>
-      <c r="C338" s="425"/>
+      <c r="B338" s="407"/>
+      <c r="C338" s="407"/>
       <c r="D338" s="131"/>
-      <c r="E338" s="425"/>
+      <c r="E338" s="407"/>
       <c r="F338" s="91"/>
       <c r="G338" s="91"/>
       <c r="H338" s="91"/>
@@ -20135,10 +20116,10 @@
     </row>
     <row r="339" spans="1:29" ht="15.75" customHeight="1">
       <c r="A339" s="140"/>
-      <c r="B339" s="425"/>
-      <c r="C339" s="425"/>
+      <c r="B339" s="407"/>
+      <c r="C339" s="407"/>
       <c r="D339" s="131"/>
-      <c r="E339" s="425"/>
+      <c r="E339" s="407"/>
       <c r="F339" s="155"/>
       <c r="G339" s="155"/>
       <c r="H339" s="155"/>
@@ -20166,10 +20147,10 @@
     </row>
     <row r="340" spans="1:29" ht="15.75" customHeight="1">
       <c r="A340" s="140"/>
-      <c r="B340" s="425"/>
-      <c r="C340" s="425"/>
+      <c r="B340" s="407"/>
+      <c r="C340" s="407"/>
       <c r="D340" s="131"/>
-      <c r="E340" s="425"/>
+      <c r="E340" s="407"/>
       <c r="F340" s="91"/>
       <c r="G340" s="91"/>
       <c r="H340" s="91"/>
@@ -20197,10 +20178,10 @@
     </row>
     <row r="341" spans="1:29" ht="15.75" customHeight="1">
       <c r="A341" s="140"/>
-      <c r="B341" s="425"/>
-      <c r="C341" s="425"/>
+      <c r="B341" s="407"/>
+      <c r="C341" s="407"/>
       <c r="D341" s="131"/>
-      <c r="E341" s="427"/>
+      <c r="E341" s="410"/>
       <c r="F341" s="91"/>
       <c r="G341" s="91"/>
       <c r="H341" s="91"/>
@@ -20228,8 +20209,8 @@
     </row>
     <row r="342" spans="1:29" ht="15.75" customHeight="1">
       <c r="A342" s="140"/>
-      <c r="B342" s="425"/>
-      <c r="C342" s="425"/>
+      <c r="B342" s="407"/>
+      <c r="C342" s="407"/>
       <c r="D342" s="131"/>
       <c r="E342" s="136"/>
       <c r="F342" s="88"/>
@@ -20259,8 +20240,8 @@
     </row>
     <row r="343" spans="1:29" ht="15.75" customHeight="1">
       <c r="A343" s="140"/>
-      <c r="B343" s="425"/>
-      <c r="C343" s="425"/>
+      <c r="B343" s="407"/>
+      <c r="C343" s="407"/>
       <c r="D343" s="131"/>
       <c r="E343" s="136"/>
       <c r="F343" s="89"/>
@@ -20290,10 +20271,10 @@
     </row>
     <row r="344" spans="1:29" ht="15.75" customHeight="1">
       <c r="A344" s="140"/>
-      <c r="B344" s="425"/>
-      <c r="C344" s="425"/>
+      <c r="B344" s="407"/>
+      <c r="C344" s="407"/>
       <c r="D344" s="156"/>
-      <c r="E344" s="436"/>
+      <c r="E344" s="435"/>
       <c r="F344" s="98"/>
       <c r="G344" s="98"/>
       <c r="H344" s="98"/>
@@ -20321,10 +20302,10 @@
     </row>
     <row r="345" spans="1:29" ht="15.75" customHeight="1">
       <c r="A345" s="140"/>
-      <c r="B345" s="425"/>
-      <c r="C345" s="425"/>
+      <c r="B345" s="407"/>
+      <c r="C345" s="407"/>
       <c r="D345" s="137"/>
-      <c r="E345" s="425"/>
+      <c r="E345" s="407"/>
       <c r="F345" s="89"/>
       <c r="G345" s="89"/>
       <c r="H345" s="89"/>
@@ -20352,10 +20333,10 @@
     </row>
     <row r="346" spans="1:29" ht="15.75" customHeight="1">
       <c r="A346" s="140"/>
-      <c r="B346" s="425"/>
-      <c r="C346" s="425"/>
+      <c r="B346" s="407"/>
+      <c r="C346" s="407"/>
       <c r="D346" s="137"/>
-      <c r="E346" s="425"/>
+      <c r="E346" s="407"/>
       <c r="F346" s="89"/>
       <c r="G346" s="89"/>
       <c r="H346" s="89"/>
@@ -20383,10 +20364,10 @@
     </row>
     <row r="347" spans="1:29" ht="15.75" customHeight="1">
       <c r="A347" s="140"/>
-      <c r="B347" s="425"/>
-      <c r="C347" s="427"/>
+      <c r="B347" s="407"/>
+      <c r="C347" s="410"/>
       <c r="D347" s="116"/>
-      <c r="E347" s="427"/>
+      <c r="E347" s="410"/>
       <c r="F347" s="89"/>
       <c r="G347" s="89"/>
       <c r="H347" s="89"/>
@@ -20414,7 +20395,7 @@
     </row>
     <row r="348" spans="1:29" ht="15.75" customHeight="1">
       <c r="A348" s="140"/>
-      <c r="B348" s="425"/>
+      <c r="B348" s="407"/>
       <c r="C348" s="131"/>
       <c r="D348" s="137"/>
       <c r="E348" s="137"/>
@@ -20445,10 +20426,10 @@
     </row>
     <row r="349" spans="1:29" ht="15.75" customHeight="1">
       <c r="A349" s="140"/>
-      <c r="B349" s="425"/>
-      <c r="C349" s="436"/>
+      <c r="B349" s="407"/>
+      <c r="C349" s="435"/>
       <c r="D349" s="156"/>
-      <c r="E349" s="438"/>
+      <c r="E349" s="440"/>
       <c r="F349" s="98"/>
       <c r="G349" s="98"/>
       <c r="H349" s="98"/>
@@ -20476,10 +20457,10 @@
     </row>
     <row r="350" spans="1:29" ht="15.75" customHeight="1">
       <c r="A350" s="140"/>
-      <c r="B350" s="425"/>
-      <c r="C350" s="425"/>
+      <c r="B350" s="407"/>
+      <c r="C350" s="407"/>
       <c r="D350" s="116"/>
-      <c r="E350" s="427"/>
+      <c r="E350" s="410"/>
       <c r="F350" s="98"/>
       <c r="G350" s="98"/>
       <c r="H350" s="98"/>
@@ -20507,10 +20488,10 @@
     </row>
     <row r="351" spans="1:29" ht="15.75" customHeight="1">
       <c r="A351" s="140"/>
-      <c r="B351" s="425"/>
-      <c r="C351" s="425"/>
+      <c r="B351" s="407"/>
+      <c r="C351" s="407"/>
       <c r="D351" s="131"/>
-      <c r="E351" s="438"/>
+      <c r="E351" s="440"/>
       <c r="F351" s="98"/>
       <c r="G351" s="98"/>
       <c r="H351" s="98"/>
@@ -20538,10 +20519,10 @@
     </row>
     <row r="352" spans="1:29" ht="15.75" customHeight="1">
       <c r="A352" s="140"/>
-      <c r="B352" s="425"/>
-      <c r="C352" s="427"/>
+      <c r="B352" s="407"/>
+      <c r="C352" s="410"/>
       <c r="D352" s="131"/>
-      <c r="E352" s="427"/>
+      <c r="E352" s="410"/>
       <c r="F352" s="98"/>
       <c r="G352" s="98"/>
       <c r="H352" s="98"/>
@@ -20569,7 +20550,7 @@
     </row>
     <row r="353" spans="1:29" ht="15.75" customHeight="1">
       <c r="A353" s="140"/>
-      <c r="B353" s="425"/>
+      <c r="B353" s="407"/>
       <c r="C353" s="136"/>
       <c r="D353" s="136"/>
       <c r="E353" s="140"/>
@@ -20600,10 +20581,10 @@
     </row>
     <row r="354" spans="1:29" ht="15.75" customHeight="1">
       <c r="A354" s="140"/>
-      <c r="B354" s="425"/>
-      <c r="C354" s="436"/>
+      <c r="B354" s="407"/>
+      <c r="C354" s="435"/>
       <c r="D354" s="156"/>
-      <c r="E354" s="436"/>
+      <c r="E354" s="435"/>
       <c r="F354" s="98"/>
       <c r="G354" s="98"/>
       <c r="H354" s="98"/>
@@ -20631,10 +20612,10 @@
     </row>
     <row r="355" spans="1:29" ht="15.75" customHeight="1">
       <c r="A355" s="140"/>
-      <c r="B355" s="425"/>
-      <c r="C355" s="425"/>
+      <c r="B355" s="407"/>
+      <c r="C355" s="407"/>
       <c r="D355" s="137"/>
-      <c r="E355" s="425"/>
+      <c r="E355" s="407"/>
       <c r="F355" s="98"/>
       <c r="G355" s="98"/>
       <c r="H355" s="98"/>
@@ -20662,10 +20643,10 @@
     </row>
     <row r="356" spans="1:29" ht="15.75" customHeight="1">
       <c r="A356" s="140"/>
-      <c r="B356" s="425"/>
-      <c r="C356" s="425"/>
+      <c r="B356" s="407"/>
+      <c r="C356" s="407"/>
       <c r="D356" s="137"/>
-      <c r="E356" s="425"/>
+      <c r="E356" s="407"/>
       <c r="F356" s="98"/>
       <c r="G356" s="98"/>
       <c r="H356" s="98"/>
@@ -20693,10 +20674,10 @@
     </row>
     <row r="357" spans="1:29" ht="15.75" customHeight="1">
       <c r="A357" s="140"/>
-      <c r="B357" s="425"/>
-      <c r="C357" s="425"/>
+      <c r="B357" s="407"/>
+      <c r="C357" s="407"/>
       <c r="D357" s="137"/>
-      <c r="E357" s="425"/>
+      <c r="E357" s="407"/>
       <c r="F357" s="98"/>
       <c r="G357" s="98"/>
       <c r="H357" s="98"/>
@@ -20724,10 +20705,10 @@
     </row>
     <row r="358" spans="1:29" ht="15.75" customHeight="1">
       <c r="A358" s="140"/>
-      <c r="B358" s="425"/>
-      <c r="C358" s="425"/>
+      <c r="B358" s="407"/>
+      <c r="C358" s="407"/>
       <c r="D358" s="137"/>
-      <c r="E358" s="425"/>
+      <c r="E358" s="407"/>
       <c r="F358" s="91"/>
       <c r="G358" s="91"/>
       <c r="H358" s="91"/>
@@ -20755,10 +20736,10 @@
     </row>
     <row r="359" spans="1:29" ht="15.75" customHeight="1">
       <c r="A359" s="140"/>
-      <c r="B359" s="425"/>
-      <c r="C359" s="425"/>
+      <c r="B359" s="407"/>
+      <c r="C359" s="407"/>
       <c r="D359" s="116"/>
-      <c r="E359" s="427"/>
+      <c r="E359" s="410"/>
       <c r="F359" s="91"/>
       <c r="G359" s="91"/>
       <c r="H359" s="91"/>
@@ -20786,10 +20767,10 @@
     </row>
     <row r="360" spans="1:29" ht="15.75" customHeight="1">
       <c r="A360" s="140"/>
-      <c r="B360" s="425"/>
-      <c r="C360" s="425"/>
+      <c r="B360" s="407"/>
+      <c r="C360" s="407"/>
       <c r="D360" s="156"/>
-      <c r="E360" s="436"/>
+      <c r="E360" s="435"/>
       <c r="F360" s="98"/>
       <c r="G360" s="98"/>
       <c r="H360" s="98"/>
@@ -20817,10 +20798,10 @@
     </row>
     <row r="361" spans="1:29" ht="15.75" customHeight="1">
       <c r="A361" s="140"/>
-      <c r="B361" s="425"/>
-      <c r="C361" s="425"/>
+      <c r="B361" s="407"/>
+      <c r="C361" s="407"/>
       <c r="D361" s="137"/>
-      <c r="E361" s="425"/>
+      <c r="E361" s="407"/>
       <c r="F361" s="89"/>
       <c r="G361" s="89"/>
       <c r="H361" s="89"/>
@@ -20848,10 +20829,10 @@
     </row>
     <row r="362" spans="1:29" ht="15.75" customHeight="1">
       <c r="A362" s="140"/>
-      <c r="B362" s="425"/>
-      <c r="C362" s="425"/>
+      <c r="B362" s="407"/>
+      <c r="C362" s="407"/>
       <c r="D362" s="137"/>
-      <c r="E362" s="425"/>
+      <c r="E362" s="407"/>
       <c r="F362" s="89"/>
       <c r="G362" s="89"/>
       <c r="H362" s="89"/>
@@ -20879,10 +20860,10 @@
     </row>
     <row r="363" spans="1:29" ht="15.75" customHeight="1">
       <c r="A363" s="140"/>
-      <c r="B363" s="427"/>
-      <c r="C363" s="427"/>
+      <c r="B363" s="410"/>
+      <c r="C363" s="410"/>
       <c r="D363" s="116"/>
-      <c r="E363" s="427"/>
+      <c r="E363" s="410"/>
       <c r="F363" s="89"/>
       <c r="G363" s="89"/>
       <c r="H363" s="89"/>
@@ -23632,6 +23613,41 @@
     <row r="1045" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="D163:D164"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D66"/>
+    <mergeCell ref="D68:D79"/>
+    <mergeCell ref="D81:D87"/>
+    <mergeCell ref="D89:D99"/>
+    <mergeCell ref="D101:D105"/>
+    <mergeCell ref="K317:K318"/>
+    <mergeCell ref="C321:C322"/>
+    <mergeCell ref="K321:K322"/>
+    <mergeCell ref="C323:C324"/>
+    <mergeCell ref="B334:B363"/>
+    <mergeCell ref="C354:C363"/>
+    <mergeCell ref="E354:E359"/>
+    <mergeCell ref="E360:E363"/>
+    <mergeCell ref="C349:C352"/>
+    <mergeCell ref="E349:E350"/>
+    <mergeCell ref="E351:E352"/>
+    <mergeCell ref="C298:C299"/>
+    <mergeCell ref="C301:C305"/>
+    <mergeCell ref="C326:C328"/>
+    <mergeCell ref="C334:C347"/>
+    <mergeCell ref="E334:E341"/>
+    <mergeCell ref="E344:E347"/>
+    <mergeCell ref="D231:D239"/>
+    <mergeCell ref="K282:K284"/>
+    <mergeCell ref="L282:L284"/>
+    <mergeCell ref="C291:C297"/>
+    <mergeCell ref="E291:E293"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="B10:B229"/>
     <mergeCell ref="D219:D229"/>
@@ -23647,44 +23663,9 @@
     <mergeCell ref="D137:D138"/>
     <mergeCell ref="D140:D150"/>
     <mergeCell ref="C10:C119"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D231:D239"/>
-    <mergeCell ref="K282:K284"/>
-    <mergeCell ref="L282:L284"/>
-    <mergeCell ref="C291:C297"/>
-    <mergeCell ref="E291:E293"/>
-    <mergeCell ref="C298:C299"/>
-    <mergeCell ref="C301:C305"/>
-    <mergeCell ref="C326:C328"/>
-    <mergeCell ref="C334:C347"/>
-    <mergeCell ref="E334:E341"/>
-    <mergeCell ref="E344:E347"/>
-    <mergeCell ref="K317:K318"/>
-    <mergeCell ref="C321:C322"/>
-    <mergeCell ref="K321:K322"/>
-    <mergeCell ref="C323:C324"/>
-    <mergeCell ref="B334:B363"/>
-    <mergeCell ref="C354:C363"/>
-    <mergeCell ref="E354:E359"/>
-    <mergeCell ref="E360:E363"/>
-    <mergeCell ref="C349:C352"/>
-    <mergeCell ref="E349:E350"/>
-    <mergeCell ref="E351:E352"/>
     <mergeCell ref="D152:D161"/>
-    <mergeCell ref="D163:D164"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D66"/>
-    <mergeCell ref="D68:D79"/>
-    <mergeCell ref="D81:D87"/>
-    <mergeCell ref="D89:D99"/>
-    <mergeCell ref="D101:D105"/>
   </mergeCells>
-  <conditionalFormatting sqref="L8 L10:L106">
+  <conditionalFormatting sqref="L8">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
@@ -23698,31 +23679,31 @@
       <formula>"Out of Scope"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L140:L150 L152:L155 L157:L161 L163:L164 L166:L172 L174:L431 K265:K270 K272:K273 K310 K324:K333 L115:L138 L107:L113">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+  <conditionalFormatting sqref="L10:L138">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Not Executed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Out of Scope"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L114">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="L140:L150 L152:L155 L157:L161 L163:L164 L166:L172 L174:L431 K265:K270 K272:K273 K310 K324:K333">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"Not Executed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"Out of Scope"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23776,39 +23757,39 @@
     <row r="2" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="3" spans="1:26" ht="8.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="25.5" customHeight="1" thickBot="1">
-      <c r="B4" s="404" t="s">
+      <c r="B4" s="458" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="405"/>
-      <c r="D4" s="405"/>
-      <c r="E4" s="405"/>
-      <c r="F4" s="405"/>
-      <c r="G4" s="406"/>
+      <c r="C4" s="459"/>
+      <c r="D4" s="459"/>
+      <c r="E4" s="459"/>
+      <c r="F4" s="459"/>
+      <c r="G4" s="460"/>
       <c r="K4" s="183"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
       <c r="B5" s="250" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="407" t="s">
+      <c r="C5" s="461" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="391"/>
-      <c r="E5" s="391"/>
-      <c r="F5" s="391"/>
-      <c r="G5" s="392"/>
+      <c r="D5" s="462"/>
+      <c r="E5" s="462"/>
+      <c r="F5" s="462"/>
+      <c r="G5" s="463"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
       <c r="B6" s="251" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="407" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="391"/>
-      <c r="E6" s="391"/>
-      <c r="F6" s="391"/>
-      <c r="G6" s="392"/>
+      <c r="C6" s="461" t="s">
+        <v>664</v>
+      </c>
+      <c r="D6" s="462"/>
+      <c r="E6" s="462"/>
+      <c r="F6" s="462"/>
+      <c r="G6" s="463"/>
       <c r="I6" s="184" t="s">
         <v>49</v>
       </c>
@@ -23824,11 +23805,13 @@
       <c r="B7" s="250" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="390"/>
-      <c r="D7" s="391"/>
-      <c r="E7" s="391"/>
-      <c r="F7" s="391"/>
-      <c r="G7" s="392"/>
+      <c r="C7" s="464">
+        <v>1</v>
+      </c>
+      <c r="D7" s="462"/>
+      <c r="E7" s="462"/>
+      <c r="F7" s="462"/>
+      <c r="G7" s="463"/>
       <c r="I7" s="187">
         <f>C15</f>
         <v>86</v>
@@ -23843,11 +23826,13 @@
       <c r="B8" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="390"/>
-      <c r="D8" s="391"/>
-      <c r="E8" s="391"/>
-      <c r="F8" s="391"/>
-      <c r="G8" s="392"/>
+      <c r="C8" s="464" t="s">
+        <v>665</v>
+      </c>
+      <c r="D8" s="462"/>
+      <c r="E8" s="462"/>
+      <c r="F8" s="462"/>
+      <c r="G8" s="463"/>
       <c r="I8" s="187">
         <f>D15</f>
         <v>12</v>
@@ -23862,11 +23847,13 @@
       <c r="B9" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="387"/>
-      <c r="D9" s="388"/>
-      <c r="E9" s="388"/>
-      <c r="F9" s="388"/>
-      <c r="G9" s="389"/>
+      <c r="C9" s="464" t="s">
+        <v>665</v>
+      </c>
+      <c r="D9" s="462"/>
+      <c r="E9" s="462"/>
+      <c r="F9" s="462"/>
+      <c r="G9" s="463"/>
       <c r="I9" s="187">
         <f>E15</f>
         <v>0</v>
@@ -23893,11 +23880,13 @@
       <c r="B10" s="250" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="390"/>
-      <c r="D10" s="391"/>
-      <c r="E10" s="391"/>
-      <c r="F10" s="391"/>
-      <c r="G10" s="392"/>
+      <c r="C10" s="464" t="s">
+        <v>502</v>
+      </c>
+      <c r="D10" s="462"/>
+      <c r="E10" s="462"/>
+      <c r="F10" s="462"/>
+      <c r="G10" s="463"/>
       <c r="I10" s="187">
         <f>F15</f>
         <v>0</v>
@@ -23913,22 +23902,22 @@
       <c r="P10" s="100"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B11" s="393" t="s">
+      <c r="B11" s="473" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="394"/>
-      <c r="D11" s="394"/>
-      <c r="E11" s="394"/>
-      <c r="F11" s="394"/>
-      <c r="G11" s="395"/>
+      <c r="C11" s="403"/>
+      <c r="D11" s="403"/>
+      <c r="E11" s="403"/>
+      <c r="F11" s="403"/>
+      <c r="G11" s="474"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B12" s="384"/>
-      <c r="C12" s="385"/>
-      <c r="D12" s="385"/>
-      <c r="E12" s="385"/>
-      <c r="F12" s="385"/>
-      <c r="G12" s="386"/>
+      <c r="B12" s="470"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+      <c r="G12" s="472"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="B13" s="192" t="s">
@@ -24063,21 +24052,21 @@
       <c r="R17" s="195"/>
     </row>
     <row r="18" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B18" s="396" t="s">
+      <c r="B18" s="475" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="397"/>
-      <c r="D18" s="397"/>
-      <c r="E18" s="397"/>
-      <c r="F18" s="397"/>
-      <c r="G18" s="398"/>
+      <c r="C18" s="399"/>
+      <c r="D18" s="399"/>
+      <c r="E18" s="399"/>
+      <c r="F18" s="399"/>
+      <c r="G18" s="400"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B19" s="399" t="s">
+      <c r="B19" s="476" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="397"/>
-      <c r="D19" s="398"/>
+      <c r="C19" s="399"/>
+      <c r="D19" s="400"/>
       <c r="E19" s="208"/>
       <c r="F19" s="208" t="s">
         <v>67</v>
@@ -24087,11 +24076,11 @@
       </c>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B20" s="400" t="s">
+      <c r="B20" s="477" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="397"/>
-      <c r="D20" s="398"/>
+      <c r="C20" s="399"/>
+      <c r="D20" s="400"/>
       <c r="E20" s="209"/>
       <c r="F20" s="209" t="s">
         <v>70</v>
@@ -24101,11 +24090,11 @@
       </c>
     </row>
     <row r="21" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B21" s="400" t="s">
+      <c r="B21" s="477" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="397"/>
-      <c r="D21" s="398"/>
+      <c r="C21" s="399"/>
+      <c r="D21" s="400"/>
       <c r="E21" s="209"/>
       <c r="F21" s="209" t="s">
         <v>70</v>
@@ -24116,306 +24105,306 @@
     </row>
     <row r="22" spans="2:18" ht="15.75" customHeight="1"/>
     <row r="23" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B23" s="403"/>
-      <c r="C23" s="401" t="s">
+      <c r="B23" s="480"/>
+      <c r="C23" s="478" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="402" t="s">
+      <c r="D23" s="479" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="379"/>
-      <c r="F23" s="379"/>
-      <c r="G23" s="380"/>
+      <c r="E23" s="466"/>
+      <c r="F23" s="466"/>
+      <c r="G23" s="467"/>
     </row>
     <row r="24" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B24" s="374"/>
-      <c r="C24" s="374"/>
-      <c r="D24" s="381"/>
-      <c r="E24" s="382"/>
-      <c r="F24" s="382"/>
-      <c r="G24" s="383"/>
+      <c r="B24" s="404"/>
+      <c r="C24" s="404"/>
+      <c r="D24" s="468"/>
+      <c r="E24" s="419"/>
+      <c r="F24" s="419"/>
+      <c r="G24" s="469"/>
     </row>
     <row r="25" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B25" s="374"/>
-      <c r="C25" s="374"/>
-      <c r="D25" s="381"/>
-      <c r="E25" s="382"/>
-      <c r="F25" s="382"/>
-      <c r="G25" s="383"/>
+      <c r="B25" s="404"/>
+      <c r="C25" s="404"/>
+      <c r="D25" s="468"/>
+      <c r="E25" s="419"/>
+      <c r="F25" s="419"/>
+      <c r="G25" s="469"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B26" s="375"/>
-      <c r="C26" s="375"/>
-      <c r="D26" s="384"/>
-      <c r="E26" s="385"/>
-      <c r="F26" s="385"/>
-      <c r="G26" s="386"/>
+      <c r="B26" s="405"/>
+      <c r="C26" s="405"/>
+      <c r="D26" s="470"/>
+      <c r="E26" s="471"/>
+      <c r="F26" s="471"/>
+      <c r="G26" s="472"/>
     </row>
     <row r="27" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B27" s="376" t="s">
+      <c r="B27" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="373" t="s">
+      <c r="C27" s="482" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="378" t="s">
+      <c r="D27" s="465" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="379"/>
-      <c r="F27" s="379"/>
-      <c r="G27" s="380"/>
+      <c r="E27" s="466"/>
+      <c r="F27" s="466"/>
+      <c r="G27" s="467"/>
     </row>
     <row r="28" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B28" s="374"/>
-      <c r="C28" s="374"/>
-      <c r="D28" s="381"/>
-      <c r="E28" s="382"/>
-      <c r="F28" s="382"/>
-      <c r="G28" s="383"/>
+      <c r="B28" s="404"/>
+      <c r="C28" s="404"/>
+      <c r="D28" s="468"/>
+      <c r="E28" s="419"/>
+      <c r="F28" s="419"/>
+      <c r="G28" s="469"/>
     </row>
     <row r="29" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B29" s="374"/>
-      <c r="C29" s="374"/>
-      <c r="D29" s="381"/>
-      <c r="E29" s="382"/>
-      <c r="F29" s="382"/>
-      <c r="G29" s="383"/>
+      <c r="B29" s="404"/>
+      <c r="C29" s="404"/>
+      <c r="D29" s="468"/>
+      <c r="E29" s="419"/>
+      <c r="F29" s="419"/>
+      <c r="G29" s="469"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B30" s="375"/>
-      <c r="C30" s="375"/>
-      <c r="D30" s="384"/>
-      <c r="E30" s="385"/>
-      <c r="F30" s="385"/>
-      <c r="G30" s="386"/>
+      <c r="B30" s="405"/>
+      <c r="C30" s="405"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
+      <c r="G30" s="472"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B31" s="376" t="s">
+      <c r="B31" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="373" t="s">
+      <c r="C31" s="482" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="378" t="s">
+      <c r="D31" s="465" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="379"/>
-      <c r="F31" s="379"/>
-      <c r="G31" s="380"/>
+      <c r="E31" s="466"/>
+      <c r="F31" s="466"/>
+      <c r="G31" s="467"/>
     </row>
     <row r="32" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B32" s="374"/>
-      <c r="C32" s="374"/>
-      <c r="D32" s="381"/>
-      <c r="E32" s="382"/>
-      <c r="F32" s="382"/>
-      <c r="G32" s="383"/>
+      <c r="B32" s="404"/>
+      <c r="C32" s="404"/>
+      <c r="D32" s="468"/>
+      <c r="E32" s="419"/>
+      <c r="F32" s="419"/>
+      <c r="G32" s="469"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="374"/>
-      <c r="C33" s="374"/>
-      <c r="D33" s="381"/>
-      <c r="E33" s="382"/>
-      <c r="F33" s="382"/>
-      <c r="G33" s="383"/>
+      <c r="B33" s="404"/>
+      <c r="C33" s="404"/>
+      <c r="D33" s="468"/>
+      <c r="E33" s="419"/>
+      <c r="F33" s="419"/>
+      <c r="G33" s="469"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="375"/>
-      <c r="C34" s="375"/>
-      <c r="D34" s="384"/>
-      <c r="E34" s="385"/>
-      <c r="F34" s="385"/>
-      <c r="G34" s="386"/>
+      <c r="B34" s="405"/>
+      <c r="C34" s="405"/>
+      <c r="D34" s="470"/>
+      <c r="E34" s="471"/>
+      <c r="F34" s="471"/>
+      <c r="G34" s="472"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B35" s="376" t="s">
+      <c r="B35" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="373" t="s">
+      <c r="C35" s="482" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="378" t="s">
+      <c r="D35" s="465" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="379"/>
-      <c r="F35" s="379"/>
-      <c r="G35" s="380"/>
+      <c r="E35" s="466"/>
+      <c r="F35" s="466"/>
+      <c r="G35" s="467"/>
     </row>
     <row r="36" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B36" s="374"/>
-      <c r="C36" s="374"/>
-      <c r="D36" s="381"/>
-      <c r="E36" s="382"/>
-      <c r="F36" s="382"/>
-      <c r="G36" s="383"/>
+      <c r="B36" s="404"/>
+      <c r="C36" s="404"/>
+      <c r="D36" s="468"/>
+      <c r="E36" s="419"/>
+      <c r="F36" s="419"/>
+      <c r="G36" s="469"/>
     </row>
     <row r="37" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B37" s="374"/>
-      <c r="C37" s="374"/>
-      <c r="D37" s="381"/>
-      <c r="E37" s="382"/>
-      <c r="F37" s="382"/>
-      <c r="G37" s="383"/>
+      <c r="B37" s="404"/>
+      <c r="C37" s="404"/>
+      <c r="D37" s="468"/>
+      <c r="E37" s="419"/>
+      <c r="F37" s="419"/>
+      <c r="G37" s="469"/>
     </row>
     <row r="38" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B38" s="375"/>
-      <c r="C38" s="375"/>
-      <c r="D38" s="384"/>
-      <c r="E38" s="385"/>
-      <c r="F38" s="385"/>
-      <c r="G38" s="386"/>
+      <c r="B38" s="405"/>
+      <c r="C38" s="405"/>
+      <c r="D38" s="470"/>
+      <c r="E38" s="471"/>
+      <c r="F38" s="471"/>
+      <c r="G38" s="472"/>
     </row>
     <row r="39" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B39" s="376" t="s">
+      <c r="B39" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="373" t="s">
+      <c r="C39" s="482" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="378" t="s">
+      <c r="D39" s="465" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="379"/>
-      <c r="F39" s="379"/>
-      <c r="G39" s="380"/>
+      <c r="E39" s="466"/>
+      <c r="F39" s="466"/>
+      <c r="G39" s="467"/>
     </row>
     <row r="40" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B40" s="374"/>
-      <c r="C40" s="374"/>
-      <c r="D40" s="381"/>
-      <c r="E40" s="382"/>
-      <c r="F40" s="382"/>
-      <c r="G40" s="383"/>
+      <c r="B40" s="404"/>
+      <c r="C40" s="404"/>
+      <c r="D40" s="468"/>
+      <c r="E40" s="419"/>
+      <c r="F40" s="419"/>
+      <c r="G40" s="469"/>
     </row>
     <row r="41" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B41" s="374"/>
-      <c r="C41" s="374"/>
-      <c r="D41" s="381"/>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="383"/>
+      <c r="B41" s="404"/>
+      <c r="C41" s="404"/>
+      <c r="D41" s="468"/>
+      <c r="E41" s="419"/>
+      <c r="F41" s="419"/>
+      <c r="G41" s="469"/>
     </row>
     <row r="42" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B42" s="375"/>
-      <c r="C42" s="375"/>
-      <c r="D42" s="384"/>
-      <c r="E42" s="385"/>
-      <c r="F42" s="385"/>
-      <c r="G42" s="386"/>
+      <c r="B42" s="405"/>
+      <c r="C42" s="405"/>
+      <c r="D42" s="470"/>
+      <c r="E42" s="471"/>
+      <c r="F42" s="471"/>
+      <c r="G42" s="472"/>
     </row>
     <row r="43" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B43" s="376" t="s">
+      <c r="B43" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="377" t="s">
+      <c r="C43" s="483" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="378" t="s">
+      <c r="D43" s="465" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="379"/>
-      <c r="F43" s="379"/>
-      <c r="G43" s="380"/>
+      <c r="E43" s="466"/>
+      <c r="F43" s="466"/>
+      <c r="G43" s="467"/>
     </row>
     <row r="44" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B44" s="374"/>
-      <c r="C44" s="374"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="382"/>
-      <c r="F44" s="382"/>
-      <c r="G44" s="383"/>
+      <c r="B44" s="404"/>
+      <c r="C44" s="404"/>
+      <c r="D44" s="468"/>
+      <c r="E44" s="419"/>
+      <c r="F44" s="419"/>
+      <c r="G44" s="469"/>
     </row>
     <row r="45" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B45" s="374"/>
-      <c r="C45" s="374"/>
-      <c r="D45" s="381"/>
-      <c r="E45" s="382"/>
-      <c r="F45" s="382"/>
-      <c r="G45" s="383"/>
+      <c r="B45" s="404"/>
+      <c r="C45" s="404"/>
+      <c r="D45" s="468"/>
+      <c r="E45" s="419"/>
+      <c r="F45" s="419"/>
+      <c r="G45" s="469"/>
     </row>
     <row r="46" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B46" s="375"/>
-      <c r="C46" s="375"/>
-      <c r="D46" s="384"/>
-      <c r="E46" s="385"/>
-      <c r="F46" s="385"/>
-      <c r="G46" s="386"/>
+      <c r="B46" s="405"/>
+      <c r="C46" s="405"/>
+      <c r="D46" s="470"/>
+      <c r="E46" s="471"/>
+      <c r="F46" s="471"/>
+      <c r="G46" s="472"/>
     </row>
     <row r="47" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B47" s="376" t="s">
+      <c r="B47" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="377" t="s">
+      <c r="C47" s="483" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="378" t="s">
+      <c r="D47" s="465" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="379"/>
-      <c r="F47" s="379"/>
-      <c r="G47" s="380"/>
+      <c r="E47" s="466"/>
+      <c r="F47" s="466"/>
+      <c r="G47" s="467"/>
     </row>
     <row r="48" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B48" s="374"/>
-      <c r="C48" s="374"/>
-      <c r="D48" s="381"/>
-      <c r="E48" s="382"/>
-      <c r="F48" s="382"/>
-      <c r="G48" s="383"/>
+      <c r="B48" s="404"/>
+      <c r="C48" s="404"/>
+      <c r="D48" s="468"/>
+      <c r="E48" s="419"/>
+      <c r="F48" s="419"/>
+      <c r="G48" s="469"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B49" s="374"/>
-      <c r="C49" s="374"/>
-      <c r="D49" s="381"/>
-      <c r="E49" s="382"/>
-      <c r="F49" s="382"/>
-      <c r="G49" s="383"/>
+      <c r="B49" s="404"/>
+      <c r="C49" s="404"/>
+      <c r="D49" s="468"/>
+      <c r="E49" s="419"/>
+      <c r="F49" s="419"/>
+      <c r="G49" s="469"/>
     </row>
     <row r="50" spans="2:7" ht="33.75" customHeight="1">
-      <c r="B50" s="375"/>
-      <c r="C50" s="375"/>
-      <c r="D50" s="384"/>
-      <c r="E50" s="385"/>
-      <c r="F50" s="385"/>
-      <c r="G50" s="386"/>
+      <c r="B50" s="405"/>
+      <c r="C50" s="405"/>
+      <c r="D50" s="470"/>
+      <c r="E50" s="471"/>
+      <c r="F50" s="471"/>
+      <c r="G50" s="472"/>
     </row>
     <row r="51" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B51" s="376" t="s">
+      <c r="B51" s="481" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="377" t="s">
+      <c r="C51" s="483" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="378" t="s">
+      <c r="D51" s="465" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="379"/>
-      <c r="F51" s="379"/>
-      <c r="G51" s="380"/>
+      <c r="E51" s="466"/>
+      <c r="F51" s="466"/>
+      <c r="G51" s="467"/>
     </row>
     <row r="52" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B52" s="374"/>
-      <c r="C52" s="374"/>
-      <c r="D52" s="381"/>
-      <c r="E52" s="382"/>
-      <c r="F52" s="382"/>
-      <c r="G52" s="383"/>
+      <c r="B52" s="404"/>
+      <c r="C52" s="404"/>
+      <c r="D52" s="468"/>
+      <c r="E52" s="419"/>
+      <c r="F52" s="419"/>
+      <c r="G52" s="469"/>
     </row>
     <row r="53" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B53" s="374"/>
-      <c r="C53" s="374"/>
-      <c r="D53" s="381"/>
-      <c r="E53" s="382"/>
-      <c r="F53" s="382"/>
-      <c r="G53" s="383"/>
+      <c r="B53" s="404"/>
+      <c r="C53" s="404"/>
+      <c r="D53" s="468"/>
+      <c r="E53" s="419"/>
+      <c r="F53" s="419"/>
+      <c r="G53" s="469"/>
     </row>
     <row r="54" spans="2:7" ht="39" customHeight="1">
-      <c r="B54" s="375"/>
-      <c r="C54" s="375"/>
-      <c r="D54" s="384"/>
-      <c r="E54" s="385"/>
-      <c r="F54" s="385"/>
-      <c r="G54" s="386"/>
+      <c r="B54" s="405"/>
+      <c r="C54" s="405"/>
+      <c r="D54" s="470"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
+      <c r="G54" s="472"/>
     </row>
     <row r="55" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="56" spans="2:7" ht="15.75" customHeight="1"/>
@@ -25365,11 +25354,21 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="D47:G50"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D51:G54"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:G42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:G46"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="D27:G30"/>
@@ -25386,21 +25385,11 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="D47:G50"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D51:G54"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:G42"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:G46"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -25478,21 +25467,21 @@
       <c r="Z2" s="185"/>
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1">
-      <c r="B3" s="460" t="s">
+      <c r="B3" s="484" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="379"/>
-      <c r="D3" s="379"/>
-      <c r="E3" s="380"/>
+      <c r="C3" s="466"/>
+      <c r="D3" s="466"/>
+      <c r="E3" s="467"/>
       <c r="F3" s="211"/>
       <c r="G3" s="211"/>
       <c r="H3" s="211"/>
     </row>
     <row r="4" spans="1:26" ht="45.75" customHeight="1">
-      <c r="B4" s="384"/>
-      <c r="C4" s="385"/>
-      <c r="D4" s="385"/>
-      <c r="E4" s="386"/>
+      <c r="B4" s="470"/>
+      <c r="C4" s="471"/>
+      <c r="D4" s="471"/>
+      <c r="E4" s="472"/>
       <c r="F4" s="211"/>
       <c r="G4" s="211"/>
       <c r="H4" s="211"/>
@@ -25523,7 +25512,7 @@
         <v>91</v>
       </c>
       <c r="E6" s="372" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F6" s="214"/>
       <c r="G6" s="214"/>
@@ -25559,7 +25548,7 @@
         <v>93</v>
       </c>
       <c r="E7" s="372" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="214"/>
@@ -25595,7 +25584,7 @@
         <v>95</v>
       </c>
       <c r="E8" s="372" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F8" s="220"/>
       <c r="G8" s="220"/>
@@ -25631,7 +25620,7 @@
         <v>97</v>
       </c>
       <c r="E9" s="372" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F9" s="220"/>
       <c r="G9" s="220"/>
@@ -25667,7 +25656,7 @@
         <v>99</v>
       </c>
       <c r="E10" s="372" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F10" s="220"/>
       <c r="G10" s="220"/>
@@ -29872,143 +29861,143 @@
     <row r="1" spans="4:14" ht="13.5" customHeight="1"/>
     <row r="2" spans="4:14" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D3" s="485" t="s">
+      <c r="D3" s="500" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="380"/>
-      <c r="G3" s="470" t="s">
+      <c r="E3" s="467"/>
+      <c r="G3" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="471"/>
-      <c r="J3" s="470" t="s">
+      <c r="H3" s="507"/>
+      <c r="J3" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="471"/>
-      <c r="M3" s="470" t="s">
+      <c r="K3" s="507"/>
+      <c r="M3" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="N3" s="471"/>
+      <c r="N3" s="507"/>
     </row>
     <row r="4" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D4" s="381"/>
-      <c r="E4" s="383"/>
-      <c r="G4" s="472"/>
-      <c r="H4" s="473"/>
-      <c r="J4" s="472"/>
-      <c r="K4" s="473"/>
-      <c r="M4" s="472"/>
-      <c r="N4" s="473"/>
+      <c r="D4" s="468"/>
+      <c r="E4" s="469"/>
+      <c r="G4" s="508"/>
+      <c r="H4" s="509"/>
+      <c r="J4" s="508"/>
+      <c r="K4" s="509"/>
+      <c r="M4" s="508"/>
+      <c r="N4" s="509"/>
     </row>
     <row r="5" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D5" s="381"/>
-      <c r="E5" s="383"/>
-      <c r="G5" s="472"/>
-      <c r="H5" s="473"/>
-      <c r="J5" s="472"/>
-      <c r="K5" s="473"/>
-      <c r="M5" s="472"/>
-      <c r="N5" s="473"/>
+      <c r="D5" s="468"/>
+      <c r="E5" s="469"/>
+      <c r="G5" s="508"/>
+      <c r="H5" s="509"/>
+      <c r="J5" s="508"/>
+      <c r="K5" s="509"/>
+      <c r="M5" s="508"/>
+      <c r="N5" s="509"/>
     </row>
     <row r="6" spans="4:14" ht="13.5" customHeight="1" thickBot="1">
-      <c r="D6" s="384"/>
-      <c r="E6" s="386"/>
-      <c r="G6" s="474"/>
-      <c r="H6" s="475"/>
-      <c r="J6" s="474"/>
-      <c r="K6" s="475"/>
-      <c r="M6" s="474"/>
-      <c r="N6" s="475"/>
+      <c r="D6" s="470"/>
+      <c r="E6" s="472"/>
+      <c r="G6" s="510"/>
+      <c r="H6" s="511"/>
+      <c r="J6" s="510"/>
+      <c r="K6" s="511"/>
+      <c r="M6" s="510"/>
+      <c r="N6" s="511"/>
     </row>
     <row r="7" spans="4:14" ht="15" customHeight="1">
-      <c r="D7" s="486" t="s">
+      <c r="D7" s="501" t="s">
+        <v>354</v>
+      </c>
+      <c r="E7" s="474"/>
+      <c r="G7" s="512" t="s">
+        <v>359</v>
+      </c>
+      <c r="H7" s="509"/>
+      <c r="J7" s="512" t="s">
+        <v>363</v>
+      </c>
+      <c r="K7" s="509"/>
+      <c r="M7" s="512" t="s">
+        <v>366</v>
+      </c>
+      <c r="N7" s="509"/>
+    </row>
+    <row r="8" spans="4:14" ht="18.75" customHeight="1">
+      <c r="D8" s="502"/>
+      <c r="E8" s="503"/>
+      <c r="G8" s="508"/>
+      <c r="H8" s="509"/>
+      <c r="J8" s="508"/>
+      <c r="K8" s="509"/>
+      <c r="M8" s="508"/>
+      <c r="N8" s="509"/>
+    </row>
+    <row r="9" spans="4:14" ht="13.5" customHeight="1">
+      <c r="D9" s="504" t="s">
         <v>355</v>
       </c>
-      <c r="E7" s="395"/>
-      <c r="G7" s="476" t="s">
+      <c r="E9" s="474"/>
+      <c r="G9" s="515" t="s">
         <v>360</v>
       </c>
-      <c r="H7" s="473"/>
-      <c r="J7" s="476" t="s">
+      <c r="H9" s="509"/>
+      <c r="J9" s="495" t="s">
         <v>364</v>
       </c>
-      <c r="K7" s="473"/>
-      <c r="M7" s="476" t="s">
+      <c r="K9" s="513"/>
+      <c r="M9" s="495" t="s">
         <v>367</v>
       </c>
-      <c r="N7" s="473"/>
-    </row>
-    <row r="8" spans="4:14" ht="18.75" customHeight="1">
-      <c r="D8" s="487"/>
-      <c r="E8" s="488"/>
-      <c r="G8" s="472"/>
-      <c r="H8" s="473"/>
-      <c r="J8" s="472"/>
-      <c r="K8" s="473"/>
-      <c r="M8" s="472"/>
-      <c r="N8" s="473"/>
-    </row>
-    <row r="9" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D9" s="489" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="395"/>
-      <c r="G9" s="484" t="s">
-        <v>361</v>
-      </c>
-      <c r="H9" s="473"/>
-      <c r="J9" s="467" t="s">
-        <v>365</v>
-      </c>
-      <c r="K9" s="477"/>
-      <c r="M9" s="467" t="s">
-        <v>368</v>
-      </c>
-      <c r="N9" s="477"/>
+      <c r="N9" s="513"/>
     </row>
     <row r="10" spans="4:14" ht="21" customHeight="1">
-      <c r="D10" s="487"/>
-      <c r="E10" s="488"/>
+      <c r="D10" s="502"/>
+      <c r="E10" s="503"/>
       <c r="F10" s="283"/>
-      <c r="G10" s="472"/>
-      <c r="H10" s="473"/>
-      <c r="J10" s="478"/>
-      <c r="K10" s="477"/>
-      <c r="M10" s="478"/>
-      <c r="N10" s="477"/>
+      <c r="G10" s="508"/>
+      <c r="H10" s="509"/>
+      <c r="J10" s="514"/>
+      <c r="K10" s="513"/>
+      <c r="M10" s="514"/>
+      <c r="N10" s="513"/>
     </row>
     <row r="11" spans="4:14" ht="21" customHeight="1">
-      <c r="D11" s="490" t="s">
+      <c r="D11" s="505" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="491"/>
-      <c r="G11" s="461" t="s">
+      <c r="E11" s="506"/>
+      <c r="G11" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="H11" s="473"/>
-      <c r="J11" s="461" t="s">
+      <c r="H11" s="509"/>
+      <c r="J11" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="K11" s="473"/>
-      <c r="M11" s="461" t="s">
+      <c r="K11" s="509"/>
+      <c r="M11" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="N11" s="473"/>
+      <c r="N11" s="509"/>
     </row>
     <row r="12" spans="4:14" ht="126.6" customHeight="1">
       <c r="D12" s="270" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E12" s="221"/>
       <c r="G12" s="273" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H12" s="274"/>
       <c r="J12" s="273" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K12" s="274"/>
       <c r="M12" s="273" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N12" s="274"/>
     </row>
@@ -30032,55 +30021,55 @@
     </row>
     <row r="14" spans="4:14" ht="27" customHeight="1">
       <c r="D14" s="271" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E14" s="221"/>
       <c r="G14" s="281" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H14" s="274"/>
       <c r="J14" s="279" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K14" s="274"/>
       <c r="M14" s="279" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N14" s="274"/>
     </row>
     <row r="15" spans="4:14" ht="27" customHeight="1">
       <c r="D15" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E15" s="221"/>
       <c r="G15" s="279" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H15" s="274"/>
       <c r="J15" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K15" s="274"/>
       <c r="M15" s="279" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N15" s="274"/>
     </row>
     <row r="16" spans="4:14" ht="27" customHeight="1">
       <c r="D16" s="271" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E16" s="221"/>
       <c r="G16" s="279" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H16" s="274"/>
       <c r="J16" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K16" s="274"/>
       <c r="M16" s="279" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N16" s="274"/>
     </row>
@@ -30089,22 +30078,22 @@
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
       <c r="D17" s="272" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E17" s="221"/>
       <c r="F17" s="185"/>
       <c r="G17" s="282" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H17" s="274"/>
       <c r="I17" s="185"/>
       <c r="J17" s="282" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K17" s="274"/>
       <c r="L17" s="185"/>
       <c r="M17" s="282" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N17" s="274"/>
       <c r="O17" s="185"/>
@@ -30140,142 +30129,142 @@
     <row r="20" spans="1:24" ht="13.5" customHeight="1"/>
     <row r="21" spans="1:24" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="22" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D22" s="470" t="s">
+      <c r="D22" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="479"/>
-      <c r="G22" s="470" t="s">
+      <c r="E22" s="486"/>
+      <c r="G22" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="479"/>
-      <c r="J22" s="470" t="s">
+      <c r="H22" s="486"/>
+      <c r="J22" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="K22" s="479"/>
-      <c r="M22" s="470" t="s">
+      <c r="K22" s="486"/>
+      <c r="M22" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="N22" s="479"/>
+      <c r="N22" s="486"/>
     </row>
     <row r="23" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D23" s="480"/>
-      <c r="E23" s="481"/>
-      <c r="G23" s="480"/>
-      <c r="H23" s="481"/>
-      <c r="J23" s="480"/>
-      <c r="K23" s="481"/>
-      <c r="M23" s="480"/>
-      <c r="N23" s="481"/>
+      <c r="D23" s="487"/>
+      <c r="E23" s="488"/>
+      <c r="G23" s="487"/>
+      <c r="H23" s="488"/>
+      <c r="J23" s="487"/>
+      <c r="K23" s="488"/>
+      <c r="M23" s="487"/>
+      <c r="N23" s="488"/>
     </row>
     <row r="24" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D24" s="480"/>
-      <c r="E24" s="481"/>
-      <c r="G24" s="480"/>
-      <c r="H24" s="481"/>
-      <c r="J24" s="480"/>
-      <c r="K24" s="481"/>
-      <c r="M24" s="480"/>
-      <c r="N24" s="481"/>
+      <c r="D24" s="487"/>
+      <c r="E24" s="488"/>
+      <c r="G24" s="487"/>
+      <c r="H24" s="488"/>
+      <c r="J24" s="487"/>
+      <c r="K24" s="488"/>
+      <c r="M24" s="487"/>
+      <c r="N24" s="488"/>
     </row>
     <row r="25" spans="1:24" ht="13.2" customHeight="1" thickBot="1">
-      <c r="D25" s="482"/>
-      <c r="E25" s="483"/>
-      <c r="G25" s="482"/>
-      <c r="H25" s="483"/>
-      <c r="J25" s="482"/>
-      <c r="K25" s="483"/>
-      <c r="M25" s="482"/>
-      <c r="N25" s="483"/>
+      <c r="D25" s="489"/>
+      <c r="E25" s="490"/>
+      <c r="G25" s="489"/>
+      <c r="H25" s="490"/>
+      <c r="J25" s="489"/>
+      <c r="K25" s="490"/>
+      <c r="M25" s="489"/>
+      <c r="N25" s="490"/>
     </row>
     <row r="26" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D26" s="463" t="s">
+      <c r="D26" s="491" t="s">
+        <v>373</v>
+      </c>
+      <c r="E26" s="492"/>
+      <c r="G26" s="491" t="s">
+        <v>376</v>
+      </c>
+      <c r="H26" s="492"/>
+      <c r="J26" s="491" t="s">
+        <v>385</v>
+      </c>
+      <c r="K26" s="492"/>
+      <c r="M26" s="491" t="s">
+        <v>386</v>
+      </c>
+      <c r="N26" s="492"/>
+    </row>
+    <row r="27" spans="1:24" ht="13.5" customHeight="1">
+      <c r="D27" s="493"/>
+      <c r="E27" s="494"/>
+      <c r="G27" s="493"/>
+      <c r="H27" s="494"/>
+      <c r="J27" s="493"/>
+      <c r="K27" s="494"/>
+      <c r="M27" s="493"/>
+      <c r="N27" s="494"/>
+    </row>
+    <row r="28" spans="1:24" ht="30" customHeight="1">
+      <c r="D28" s="495" t="s">
+        <v>369</v>
+      </c>
+      <c r="E28" s="496"/>
+      <c r="G28" s="495" t="s">
+        <v>371</v>
+      </c>
+      <c r="H28" s="496"/>
+      <c r="J28" s="495" t="s">
         <v>374</v>
       </c>
-      <c r="E26" s="464"/>
-      <c r="G26" s="463" t="s">
+      <c r="K28" s="496"/>
+      <c r="M28" s="495" t="s">
         <v>377</v>
       </c>
-      <c r="H26" s="464"/>
-      <c r="J26" s="463" t="s">
-        <v>386</v>
-      </c>
-      <c r="K26" s="464"/>
-      <c r="M26" s="463" t="s">
-        <v>387</v>
-      </c>
-      <c r="N26" s="464"/>
-    </row>
-    <row r="27" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D27" s="465"/>
-      <c r="E27" s="466"/>
-      <c r="G27" s="465"/>
-      <c r="H27" s="466"/>
-      <c r="J27" s="465"/>
-      <c r="K27" s="466"/>
-      <c r="M27" s="465"/>
-      <c r="N27" s="466"/>
-    </row>
-    <row r="28" spans="1:24" ht="30" customHeight="1">
-      <c r="D28" s="467" t="s">
-        <v>370</v>
-      </c>
-      <c r="E28" s="468"/>
-      <c r="G28" s="467" t="s">
-        <v>372</v>
-      </c>
-      <c r="H28" s="468"/>
-      <c r="J28" s="467" t="s">
-        <v>375</v>
-      </c>
-      <c r="K28" s="468"/>
-      <c r="M28" s="467" t="s">
-        <v>378</v>
-      </c>
-      <c r="N28" s="468"/>
+      <c r="N28" s="496"/>
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D29" s="469"/>
-      <c r="E29" s="468"/>
-      <c r="G29" s="469"/>
-      <c r="H29" s="468"/>
-      <c r="J29" s="469"/>
-      <c r="K29" s="468"/>
-      <c r="M29" s="469"/>
-      <c r="N29" s="468"/>
+      <c r="D29" s="497"/>
+      <c r="E29" s="496"/>
+      <c r="G29" s="497"/>
+      <c r="H29" s="496"/>
+      <c r="J29" s="497"/>
+      <c r="K29" s="496"/>
+      <c r="M29" s="497"/>
+      <c r="N29" s="496"/>
     </row>
     <row r="30" spans="1:24" ht="19.8" customHeight="1">
-      <c r="D30" s="461" t="s">
+      <c r="D30" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="462"/>
-      <c r="G30" s="461" t="s">
+      <c r="E30" s="499"/>
+      <c r="G30" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="462"/>
-      <c r="J30" s="461" t="s">
+      <c r="H30" s="499"/>
+      <c r="J30" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="K30" s="462"/>
-      <c r="M30" s="461" t="s">
+      <c r="K30" s="499"/>
+      <c r="M30" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="N30" s="462"/>
+      <c r="N30" s="499"/>
     </row>
     <row r="31" spans="1:24" ht="177" customHeight="1">
       <c r="D31" s="273" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E31" s="274"/>
       <c r="G31" s="273" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H31" s="274"/>
       <c r="J31" s="280" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K31" s="274"/>
       <c r="M31" s="273" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N31" s="274"/>
     </row>
@@ -30317,58 +30306,58 @@
     </row>
     <row r="34" spans="4:14" ht="28.2" customHeight="1">
       <c r="D34" s="360" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E34" s="274"/>
       <c r="G34" s="279" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H34" s="274"/>
       <c r="J34" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K34" s="274"/>
       <c r="M34" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N34" s="274"/>
     </row>
     <row r="35" spans="4:14" ht="23.4" customHeight="1">
       <c r="D35" s="281" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E35" s="274"/>
       <c r="G35" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H35" s="274"/>
       <c r="J35" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K35" s="274"/>
       <c r="M35" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N35" s="274"/>
     </row>
     <row r="36" spans="4:14" ht="21.6" customHeight="1">
       <c r="D36" s="284" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E36" s="274"/>
       <c r="F36" s="185"/>
       <c r="G36" s="284" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H36" s="274"/>
       <c r="I36" s="185"/>
       <c r="J36" s="284" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K36" s="274"/>
       <c r="L36" s="185"/>
       <c r="M36" s="284" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N36" s="274"/>
     </row>
@@ -30393,142 +30382,142 @@
     <row r="38" spans="4:14" ht="13.5" customHeight="1"/>
     <row r="39" spans="4:14" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="40" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D40" s="470" t="s">
+      <c r="D40" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="E40" s="479"/>
-      <c r="G40" s="470" t="s">
+      <c r="E40" s="486"/>
+      <c r="G40" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="H40" s="479"/>
-      <c r="J40" s="470" t="s">
+      <c r="H40" s="486"/>
+      <c r="J40" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="K40" s="479"/>
-      <c r="M40" s="470" t="s">
+      <c r="K40" s="486"/>
+      <c r="M40" s="485" t="s">
         <v>112</v>
       </c>
-      <c r="N40" s="479"/>
+      <c r="N40" s="486"/>
     </row>
     <row r="41" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D41" s="480"/>
-      <c r="E41" s="481"/>
-      <c r="G41" s="480"/>
-      <c r="H41" s="481"/>
-      <c r="J41" s="480"/>
-      <c r="K41" s="481"/>
-      <c r="M41" s="480"/>
-      <c r="N41" s="481"/>
+      <c r="D41" s="487"/>
+      <c r="E41" s="488"/>
+      <c r="G41" s="487"/>
+      <c r="H41" s="488"/>
+      <c r="J41" s="487"/>
+      <c r="K41" s="488"/>
+      <c r="M41" s="487"/>
+      <c r="N41" s="488"/>
     </row>
     <row r="42" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D42" s="480"/>
-      <c r="E42" s="481"/>
-      <c r="G42" s="480"/>
-      <c r="H42" s="481"/>
-      <c r="J42" s="480"/>
-      <c r="K42" s="481"/>
-      <c r="M42" s="480"/>
-      <c r="N42" s="481"/>
+      <c r="D42" s="487"/>
+      <c r="E42" s="488"/>
+      <c r="G42" s="487"/>
+      <c r="H42" s="488"/>
+      <c r="J42" s="487"/>
+      <c r="K42" s="488"/>
+      <c r="M42" s="487"/>
+      <c r="N42" s="488"/>
     </row>
     <row r="43" spans="4:14" ht="13.5" customHeight="1" thickBot="1">
-      <c r="D43" s="482"/>
-      <c r="E43" s="483"/>
-      <c r="G43" s="482"/>
-      <c r="H43" s="483"/>
-      <c r="J43" s="482"/>
-      <c r="K43" s="483"/>
-      <c r="M43" s="482"/>
-      <c r="N43" s="483"/>
+      <c r="D43" s="489"/>
+      <c r="E43" s="490"/>
+      <c r="G43" s="489"/>
+      <c r="H43" s="490"/>
+      <c r="J43" s="489"/>
+      <c r="K43" s="490"/>
+      <c r="M43" s="489"/>
+      <c r="N43" s="490"/>
     </row>
     <row r="44" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D44" s="463" t="s">
+      <c r="D44" s="491" t="s">
+        <v>499</v>
+      </c>
+      <c r="E44" s="492"/>
+      <c r="G44" s="491" t="s">
         <v>500</v>
       </c>
-      <c r="E44" s="464"/>
-      <c r="G44" s="463" t="s">
+      <c r="H44" s="492"/>
+      <c r="J44" s="491" t="s">
         <v>501</v>
       </c>
-      <c r="H44" s="464"/>
-      <c r="J44" s="463" t="s">
-        <v>502</v>
-      </c>
-      <c r="K44" s="464"/>
-      <c r="M44" s="463" t="s">
+      <c r="K44" s="492"/>
+      <c r="M44" s="491" t="s">
+        <v>661</v>
+      </c>
+      <c r="N44" s="492"/>
+    </row>
+    <row r="45" spans="4:14" ht="13.5" customHeight="1">
+      <c r="D45" s="493"/>
+      <c r="E45" s="494"/>
+      <c r="G45" s="493"/>
+      <c r="H45" s="494"/>
+      <c r="J45" s="493"/>
+      <c r="K45" s="494"/>
+      <c r="M45" s="493"/>
+      <c r="N45" s="494"/>
+    </row>
+    <row r="46" spans="4:14" ht="18.600000000000001" customHeight="1">
+      <c r="D46" s="497" t="s">
+        <v>389</v>
+      </c>
+      <c r="E46" s="496"/>
+      <c r="G46" s="497" t="s">
+        <v>387</v>
+      </c>
+      <c r="H46" s="496"/>
+      <c r="J46" s="497" t="s">
+        <v>391</v>
+      </c>
+      <c r="K46" s="496"/>
+      <c r="M46" s="495" t="s">
         <v>662</v>
       </c>
-      <c r="N44" s="464"/>
-    </row>
-    <row r="45" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D45" s="465"/>
-      <c r="E45" s="466"/>
-      <c r="G45" s="465"/>
-      <c r="H45" s="466"/>
-      <c r="J45" s="465"/>
-      <c r="K45" s="466"/>
-      <c r="M45" s="465"/>
-      <c r="N45" s="466"/>
-    </row>
-    <row r="46" spans="4:14" ht="18.600000000000001" customHeight="1">
-      <c r="D46" s="469" t="s">
-        <v>390</v>
-      </c>
-      <c r="E46" s="468"/>
-      <c r="G46" s="469" t="s">
-        <v>388</v>
-      </c>
-      <c r="H46" s="468"/>
-      <c r="J46" s="469" t="s">
-        <v>392</v>
-      </c>
-      <c r="K46" s="468"/>
-      <c r="M46" s="467" t="s">
-        <v>663</v>
-      </c>
-      <c r="N46" s="468"/>
+      <c r="N46" s="496"/>
     </row>
     <row r="47" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D47" s="469"/>
-      <c r="E47" s="468"/>
-      <c r="G47" s="469"/>
-      <c r="H47" s="468"/>
-      <c r="J47" s="469"/>
-      <c r="K47" s="468"/>
-      <c r="M47" s="469"/>
-      <c r="N47" s="468"/>
+      <c r="D47" s="497"/>
+      <c r="E47" s="496"/>
+      <c r="G47" s="497"/>
+      <c r="H47" s="496"/>
+      <c r="J47" s="497"/>
+      <c r="K47" s="496"/>
+      <c r="M47" s="497"/>
+      <c r="N47" s="496"/>
     </row>
     <row r="48" spans="4:14" ht="19.2" customHeight="1">
-      <c r="D48" s="461" t="s">
+      <c r="D48" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="462"/>
-      <c r="G48" s="461" t="s">
+      <c r="E48" s="499"/>
+      <c r="G48" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="H48" s="462"/>
-      <c r="J48" s="461" t="s">
+      <c r="H48" s="499"/>
+      <c r="J48" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="K48" s="462"/>
-      <c r="M48" s="461" t="s">
+      <c r="K48" s="499"/>
+      <c r="M48" s="498" t="s">
         <v>113</v>
       </c>
-      <c r="N48" s="462"/>
+      <c r="N48" s="499"/>
     </row>
     <row r="49" spans="4:14" ht="187.8" customHeight="1">
       <c r="D49" s="273" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E49" s="274"/>
       <c r="G49" s="273" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H49" s="274"/>
       <c r="J49" s="280" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K49" s="274"/>
       <c r="M49" s="273" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N49" s="274"/>
     </row>
@@ -30564,63 +30553,63 @@
       </c>
       <c r="K51" s="274"/>
       <c r="M51" s="281" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N51" s="274"/>
     </row>
     <row r="52" spans="4:14" ht="21.6" customHeight="1">
       <c r="D52" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E52" s="274"/>
       <c r="G52" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H52" s="274"/>
       <c r="J52" s="279" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K52" s="274"/>
       <c r="M52" s="279" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N52" s="274"/>
     </row>
     <row r="53" spans="4:14" ht="22.2" customHeight="1">
       <c r="D53" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E53" s="274"/>
       <c r="G53" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H53" s="274"/>
       <c r="J53" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K53" s="274"/>
       <c r="M53" s="279" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N53" s="274"/>
     </row>
     <row r="54" spans="4:14" ht="22.2" customHeight="1">
       <c r="D54" s="284" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E54" s="274"/>
       <c r="F54" s="185"/>
       <c r="G54" s="285" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H54" s="274"/>
       <c r="I54" s="185"/>
       <c r="J54" s="284" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K54" s="274"/>
       <c r="M54" s="284" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N54" s="274"/>
     </row>
@@ -31592,29 +31581,15 @@
     <row r="1003" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="M40:N43"/>
-    <mergeCell ref="M44:N45"/>
-    <mergeCell ref="M46:N47"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="J46:K47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="G40:H43"/>
-    <mergeCell ref="J40:K43"/>
-    <mergeCell ref="D44:E45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="J44:K45"/>
-    <mergeCell ref="D3:E6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D40:E43"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="J26:K27"/>
+    <mergeCell ref="M26:N27"/>
+    <mergeCell ref="G28:H29"/>
+    <mergeCell ref="J28:K29"/>
+    <mergeCell ref="M28:N29"/>
+    <mergeCell ref="G26:H27"/>
     <mergeCell ref="M3:N6"/>
     <mergeCell ref="M7:N8"/>
     <mergeCell ref="M9:N10"/>
@@ -31631,15 +31606,29 @@
     <mergeCell ref="G7:H8"/>
     <mergeCell ref="G9:H10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="J26:K27"/>
-    <mergeCell ref="M26:N27"/>
-    <mergeCell ref="G28:H29"/>
-    <mergeCell ref="J28:K29"/>
-    <mergeCell ref="M28:N29"/>
-    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="D3:E6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D40:E43"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="M40:N43"/>
+    <mergeCell ref="M44:N45"/>
+    <mergeCell ref="M46:N47"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="J46:K47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="G40:H43"/>
+    <mergeCell ref="J40:K43"/>
+    <mergeCell ref="D44:E45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="J44:K45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D17" r:id="rId1" display="Take spaces in mobile number field" xr:uid="{00000000-0004-0000-0400-000000000000}"/>

--- a/TestCase_Chaldal.xlsx
+++ b/TestCase_Chaldal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Full Stack Sqa Course\ChalDal\Chaldal-Manual-Testing-TestCases--Writing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BEFBB6-86DF-4EE1-945E-1EF469E3EA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DEF6B-1365-436B-9D49-3D6CF1911FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="6" r:id="rId1"/>
@@ -5774,11 +5774,80 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5798,38 +5867,102 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="56" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="41" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="43" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="43" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5850,7 +5983,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5874,204 +6006,42 @@
     <xf numFmtId="0" fontId="41" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="43" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="43" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="20" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="6" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6086,9 +6056,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6761,48 +6761,48 @@
   <sheetData>
     <row r="5" spans="10:25" ht="13.8" customHeight="1"/>
     <row r="6" spans="10:25">
-      <c r="J6" s="384" t="s">
+      <c r="J6" s="415" t="s">
         <v>403</v>
       </c>
-      <c r="K6" s="384"/>
-      <c r="L6" s="384"/>
-      <c r="M6" s="384"/>
-      <c r="N6" s="384"/>
-      <c r="O6" s="384"/>
-      <c r="P6" s="384"/>
-      <c r="Q6" s="384"/>
-      <c r="R6" s="384"/>
-      <c r="S6" s="384"/>
-      <c r="T6" s="384"/>
-      <c r="U6" s="384"/>
+      <c r="K6" s="415"/>
+      <c r="L6" s="415"/>
+      <c r="M6" s="415"/>
+      <c r="N6" s="415"/>
+      <c r="O6" s="415"/>
+      <c r="P6" s="415"/>
+      <c r="Q6" s="415"/>
+      <c r="R6" s="415"/>
+      <c r="S6" s="415"/>
+      <c r="T6" s="415"/>
+      <c r="U6" s="415"/>
     </row>
     <row r="7" spans="10:25">
-      <c r="J7" s="384"/>
-      <c r="K7" s="384"/>
-      <c r="L7" s="384"/>
-      <c r="M7" s="384"/>
-      <c r="N7" s="384"/>
-      <c r="O7" s="384"/>
-      <c r="P7" s="384"/>
-      <c r="Q7" s="384"/>
-      <c r="R7" s="384"/>
-      <c r="S7" s="384"/>
-      <c r="T7" s="384"/>
-      <c r="U7" s="384"/>
+      <c r="J7" s="415"/>
+      <c r="K7" s="415"/>
+      <c r="L7" s="415"/>
+      <c r="M7" s="415"/>
+      <c r="N7" s="415"/>
+      <c r="O7" s="415"/>
+      <c r="P7" s="415"/>
+      <c r="Q7" s="415"/>
+      <c r="R7" s="415"/>
+      <c r="S7" s="415"/>
+      <c r="T7" s="415"/>
+      <c r="U7" s="415"/>
     </row>
     <row r="8" spans="10:25">
-      <c r="J8" s="384"/>
-      <c r="K8" s="384"/>
-      <c r="L8" s="384"/>
-      <c r="M8" s="384"/>
-      <c r="N8" s="384"/>
-      <c r="O8" s="384"/>
-      <c r="P8" s="384"/>
-      <c r="Q8" s="384"/>
-      <c r="R8" s="384"/>
-      <c r="S8" s="384"/>
-      <c r="T8" s="384"/>
-      <c r="U8" s="384"/>
+      <c r="J8" s="415"/>
+      <c r="K8" s="415"/>
+      <c r="L8" s="415"/>
+      <c r="M8" s="415"/>
+      <c r="N8" s="415"/>
+      <c r="O8" s="415"/>
+      <c r="P8" s="415"/>
+      <c r="Q8" s="415"/>
+      <c r="R8" s="415"/>
+      <c r="S8" s="415"/>
+      <c r="T8" s="415"/>
+      <c r="U8" s="415"/>
       <c r="V8" s="283"/>
       <c r="W8" s="283"/>
       <c r="X8" s="283"/>
@@ -6853,74 +6853,74 @@
     <row r="7" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="8" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="9" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q9" s="383" t="s">
+      <c r="Q9" s="416" t="s">
         <v>404</v>
       </c>
-      <c r="R9" s="383"/>
-      <c r="S9" s="383"/>
-      <c r="T9" s="383"/>
-      <c r="U9" s="383"/>
-      <c r="V9" s="383"/>
-      <c r="W9" s="383"/>
-      <c r="X9" s="383"/>
-      <c r="Y9" s="383"/>
-      <c r="Z9" s="383"/>
-      <c r="AA9" s="383"/>
-      <c r="AB9" s="383"/>
-      <c r="AC9" s="383"/>
-      <c r="AD9" s="383"/>
-      <c r="AE9" s="383"/>
+      <c r="R9" s="416"/>
+      <c r="S9" s="416"/>
+      <c r="T9" s="416"/>
+      <c r="U9" s="416"/>
+      <c r="V9" s="416"/>
+      <c r="W9" s="416"/>
+      <c r="X9" s="416"/>
+      <c r="Y9" s="416"/>
+      <c r="Z9" s="416"/>
+      <c r="AA9" s="416"/>
+      <c r="AB9" s="416"/>
+      <c r="AC9" s="416"/>
+      <c r="AD9" s="416"/>
+      <c r="AE9" s="416"/>
     </row>
     <row r="10" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q10" s="383"/>
-      <c r="R10" s="383"/>
-      <c r="S10" s="383"/>
-      <c r="T10" s="383"/>
-      <c r="U10" s="383"/>
-      <c r="V10" s="383"/>
-      <c r="W10" s="383"/>
-      <c r="X10" s="383"/>
-      <c r="Y10" s="383"/>
-      <c r="Z10" s="383"/>
-      <c r="AA10" s="383"/>
-      <c r="AB10" s="383"/>
-      <c r="AC10" s="383"/>
-      <c r="AD10" s="383"/>
-      <c r="AE10" s="383"/>
+      <c r="Q10" s="416"/>
+      <c r="R10" s="416"/>
+      <c r="S10" s="416"/>
+      <c r="T10" s="416"/>
+      <c r="U10" s="416"/>
+      <c r="V10" s="416"/>
+      <c r="W10" s="416"/>
+      <c r="X10" s="416"/>
+      <c r="Y10" s="416"/>
+      <c r="Z10" s="416"/>
+      <c r="AA10" s="416"/>
+      <c r="AB10" s="416"/>
+      <c r="AC10" s="416"/>
+      <c r="AD10" s="416"/>
+      <c r="AE10" s="416"/>
     </row>
     <row r="11" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q11" s="383"/>
-      <c r="R11" s="383"/>
-      <c r="S11" s="383"/>
-      <c r="T11" s="383"/>
-      <c r="U11" s="383"/>
-      <c r="V11" s="383"/>
-      <c r="W11" s="383"/>
-      <c r="X11" s="383"/>
-      <c r="Y11" s="383"/>
-      <c r="Z11" s="383"/>
-      <c r="AA11" s="383"/>
-      <c r="AB11" s="383"/>
-      <c r="AC11" s="383"/>
-      <c r="AD11" s="383"/>
-      <c r="AE11" s="383"/>
+      <c r="Q11" s="416"/>
+      <c r="R11" s="416"/>
+      <c r="S11" s="416"/>
+      <c r="T11" s="416"/>
+      <c r="U11" s="416"/>
+      <c r="V11" s="416"/>
+      <c r="W11" s="416"/>
+      <c r="X11" s="416"/>
+      <c r="Y11" s="416"/>
+      <c r="Z11" s="416"/>
+      <c r="AA11" s="416"/>
+      <c r="AB11" s="416"/>
+      <c r="AC11" s="416"/>
+      <c r="AD11" s="416"/>
+      <c r="AE11" s="416"/>
     </row>
     <row r="12" spans="17:31" ht="13.5" customHeight="1">
-      <c r="Q12" s="383"/>
-      <c r="R12" s="383"/>
-      <c r="S12" s="383"/>
-      <c r="T12" s="383"/>
-      <c r="U12" s="383"/>
-      <c r="V12" s="383"/>
-      <c r="W12" s="383"/>
-      <c r="X12" s="383"/>
-      <c r="Y12" s="383"/>
-      <c r="Z12" s="383"/>
-      <c r="AA12" s="383"/>
-      <c r="AB12" s="383"/>
-      <c r="AC12" s="383"/>
-      <c r="AD12" s="383"/>
-      <c r="AE12" s="383"/>
+      <c r="Q12" s="416"/>
+      <c r="R12" s="416"/>
+      <c r="S12" s="416"/>
+      <c r="T12" s="416"/>
+      <c r="U12" s="416"/>
+      <c r="V12" s="416"/>
+      <c r="W12" s="416"/>
+      <c r="X12" s="416"/>
+      <c r="Y12" s="416"/>
+      <c r="Z12" s="416"/>
+      <c r="AA12" s="416"/>
+      <c r="AB12" s="416"/>
+      <c r="AC12" s="416"/>
+      <c r="AD12" s="416"/>
+      <c r="AE12" s="416"/>
     </row>
     <row r="13" spans="17:31" ht="13.5" customHeight="1"/>
     <row r="14" spans="17:31" ht="13.5" customHeight="1"/>
@@ -7936,10 +7936,10 @@
       <c r="A4" s="312" t="s">
         <v>405</v>
       </c>
-      <c r="B4" s="385" t="s">
+      <c r="B4" s="422" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="386"/>
+      <c r="C4" s="423"/>
       <c r="D4" s="289"/>
       <c r="E4" s="289"/>
     </row>
@@ -7947,10 +7947,10 @@
       <c r="A5" s="312" t="s">
         <v>406</v>
       </c>
-      <c r="B5" s="387" t="s">
+      <c r="B5" s="424" t="s">
         <v>407</v>
       </c>
-      <c r="C5" s="388"/>
+      <c r="C5" s="425"/>
       <c r="D5" s="289"/>
       <c r="E5" s="289"/>
     </row>
@@ -7958,10 +7958,10 @@
       <c r="A6" s="312" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="389" t="s">
+      <c r="B6" s="426" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="390"/>
+      <c r="C6" s="427"/>
       <c r="D6" s="289"/>
       <c r="E6" s="289"/>
     </row>
@@ -7969,10 +7969,10 @@
       <c r="A7" s="312" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="391">
+      <c r="B7" s="428">
         <v>46145</v>
       </c>
-      <c r="C7" s="392"/>
+      <c r="C7" s="429"/>
       <c r="D7" s="289"/>
       <c r="E7" s="289"/>
     </row>
@@ -7980,8 +7980,8 @@
       <c r="A8" s="312" t="s">
         <v>410</v>
       </c>
-      <c r="B8" s="389"/>
-      <c r="C8" s="390"/>
+      <c r="B8" s="426"/>
+      <c r="C8" s="427"/>
       <c r="D8" s="289"/>
       <c r="E8" s="289"/>
     </row>
@@ -8007,28 +8007,28 @@
       <c r="E11" s="289"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="393" t="s">
+      <c r="A12" s="417" t="s">
         <v>411</v>
       </c>
-      <c r="B12" s="395" t="s">
+      <c r="B12" s="419" t="s">
         <v>412</v>
       </c>
-      <c r="C12" s="397" t="s">
+      <c r="C12" s="421" t="s">
         <v>413</v>
       </c>
-      <c r="D12" s="395" t="s">
+      <c r="D12" s="419" t="s">
         <v>414</v>
       </c>
-      <c r="E12" s="395" t="s">
+      <c r="E12" s="419" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="394"/>
-      <c r="B13" s="396"/>
-      <c r="C13" s="396"/>
-      <c r="D13" s="396"/>
-      <c r="E13" s="396"/>
+      <c r="A13" s="418"/>
+      <c r="B13" s="420"/>
+      <c r="C13" s="420"/>
+      <c r="D13" s="420"/>
+      <c r="E13" s="420"/>
     </row>
     <row r="14" spans="1:5" ht="14.4">
       <c r="A14" s="295" t="s">
@@ -8188,16 +8188,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="62" type="noConversion"/>
   <hyperlinks>
@@ -8234,10 +8234,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="29.25" customHeight="1">
-      <c r="A1" s="429" t="s">
+      <c r="A1" s="457" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="430"/>
+      <c r="B1" s="458"/>
       <c r="C1" s="234" t="s">
         <v>117</v>
       </c>
@@ -8257,10 +8257,10 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="431" t="s">
+      <c r="L1" s="459" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="432"/>
+      <c r="M1" s="460"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -8279,10 +8279,10 @@
       <c r="AC1" s="3"/>
     </row>
     <row r="2" spans="1:29" ht="32.25" customHeight="1">
-      <c r="A2" s="429" t="s">
+      <c r="A2" s="457" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="430"/>
+      <c r="B2" s="458"/>
       <c r="C2" s="235" t="s">
         <v>118</v>
       </c>
@@ -8327,10 +8327,10 @@
       <c r="AC2" s="3"/>
     </row>
     <row r="3" spans="1:29" ht="33" customHeight="1">
-      <c r="A3" s="429" t="s">
+      <c r="A3" s="457" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="430"/>
+      <c r="B3" s="458"/>
       <c r="C3" s="4"/>
       <c r="D3" s="231" t="s">
         <v>9</v>
@@ -8373,10 +8373,10 @@
       <c r="AC3" s="3"/>
     </row>
     <row r="4" spans="1:29" ht="34.5" customHeight="1">
-      <c r="A4" s="429" t="s">
+      <c r="A4" s="457" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="430"/>
+      <c r="B4" s="458"/>
       <c r="C4" s="4"/>
       <c r="D4" s="231" t="s">
         <v>14</v>
@@ -8419,15 +8419,15 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" ht="31.5" customHeight="1">
-      <c r="A5" s="411" t="s">
+      <c r="A5" s="466" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="400"/>
-      <c r="C5" s="398"/>
-      <c r="D5" s="399"/>
-      <c r="E5" s="399"/>
-      <c r="F5" s="399"/>
-      <c r="G5" s="400"/>
+      <c r="B5" s="405"/>
+      <c r="C5" s="461"/>
+      <c r="D5" s="404"/>
+      <c r="E5" s="404"/>
+      <c r="F5" s="404"/>
+      <c r="G5" s="405"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -8631,13 +8631,13 @@
       <c r="A10" s="32">
         <v>2</v>
       </c>
-      <c r="B10" s="401" t="s">
+      <c r="B10" s="462" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="426" t="s">
+      <c r="C10" s="480" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="415" t="s">
+      <c r="D10" s="470" t="s">
         <v>119</v>
       </c>
       <c r="E10" s="244" t="s">
@@ -8682,9 +8682,9 @@
       <c r="A11" s="32">
         <v>3</v>
       </c>
-      <c r="B11" s="402"/>
-      <c r="C11" s="427"/>
-      <c r="D11" s="416"/>
+      <c r="B11" s="463"/>
+      <c r="C11" s="481"/>
+      <c r="D11" s="471"/>
       <c r="E11" s="244" t="s">
         <v>124</v>
       </c>
@@ -8727,9 +8727,9 @@
       <c r="A12" s="32">
         <v>4</v>
       </c>
-      <c r="B12" s="402"/>
-      <c r="C12" s="427"/>
-      <c r="D12" s="416"/>
+      <c r="B12" s="463"/>
+      <c r="C12" s="481"/>
+      <c r="D12" s="471"/>
       <c r="E12" s="244" t="s">
         <v>127</v>
       </c>
@@ -8772,9 +8772,9 @@
       <c r="A13" s="32">
         <v>5</v>
       </c>
-      <c r="B13" s="402"/>
-      <c r="C13" s="427"/>
-      <c r="D13" s="416"/>
+      <c r="B13" s="463"/>
+      <c r="C13" s="481"/>
+      <c r="D13" s="471"/>
       <c r="E13" s="244" t="s">
         <v>131</v>
       </c>
@@ -8817,9 +8817,9 @@
       <c r="A14" s="32">
         <v>6</v>
       </c>
-      <c r="B14" s="402"/>
-      <c r="C14" s="427"/>
-      <c r="D14" s="416"/>
+      <c r="B14" s="463"/>
+      <c r="C14" s="481"/>
+      <c r="D14" s="471"/>
       <c r="E14" s="244" t="s">
         <v>136</v>
       </c>
@@ -8862,9 +8862,9 @@
       <c r="A15" s="32">
         <v>7</v>
       </c>
-      <c r="B15" s="402"/>
-      <c r="C15" s="427"/>
-      <c r="D15" s="416"/>
+      <c r="B15" s="463"/>
+      <c r="C15" s="481"/>
+      <c r="D15" s="471"/>
       <c r="E15" s="244" t="s">
         <v>142</v>
       </c>
@@ -8909,9 +8909,9 @@
       <c r="A16" s="32">
         <v>8</v>
       </c>
-      <c r="B16" s="402"/>
-      <c r="C16" s="427"/>
-      <c r="D16" s="416"/>
+      <c r="B16" s="463"/>
+      <c r="C16" s="481"/>
+      <c r="D16" s="471"/>
       <c r="E16" s="244" t="s">
         <v>147</v>
       </c>
@@ -8954,9 +8954,9 @@
       <c r="A17" s="32">
         <v>9</v>
       </c>
-      <c r="B17" s="402"/>
-      <c r="C17" s="427"/>
-      <c r="D17" s="416"/>
+      <c r="B17" s="463"/>
+      <c r="C17" s="481"/>
+      <c r="D17" s="471"/>
       <c r="E17" s="244" t="s">
         <v>155</v>
       </c>
@@ -8999,9 +8999,9 @@
       <c r="A18" s="32">
         <v>10</v>
       </c>
-      <c r="B18" s="402"/>
-      <c r="C18" s="427"/>
-      <c r="D18" s="416"/>
+      <c r="B18" s="463"/>
+      <c r="C18" s="481"/>
+      <c r="D18" s="471"/>
       <c r="E18" s="244" t="s">
         <v>159</v>
       </c>
@@ -9044,9 +9044,9 @@
       <c r="A19" s="32">
         <v>11</v>
       </c>
-      <c r="B19" s="402"/>
-      <c r="C19" s="427"/>
-      <c r="D19" s="416"/>
+      <c r="B19" s="463"/>
+      <c r="C19" s="481"/>
+      <c r="D19" s="471"/>
       <c r="E19" s="244" t="s">
         <v>193</v>
       </c>
@@ -9089,9 +9089,9 @@
       <c r="A20" s="32">
         <v>12</v>
       </c>
-      <c r="B20" s="402"/>
-      <c r="C20" s="427"/>
-      <c r="D20" s="416"/>
+      <c r="B20" s="463"/>
+      <c r="C20" s="481"/>
+      <c r="D20" s="471"/>
       <c r="E20" s="244" t="s">
         <v>195</v>
       </c>
@@ -9134,9 +9134,9 @@
       <c r="A21" s="32">
         <v>13</v>
       </c>
-      <c r="B21" s="402"/>
-      <c r="C21" s="427"/>
-      <c r="D21" s="416"/>
+      <c r="B21" s="463"/>
+      <c r="C21" s="481"/>
+      <c r="D21" s="471"/>
       <c r="E21" s="244" t="s">
         <v>200</v>
       </c>
@@ -9179,9 +9179,9 @@
       <c r="A22" s="32">
         <v>14</v>
       </c>
-      <c r="B22" s="402"/>
-      <c r="C22" s="427"/>
-      <c r="D22" s="416"/>
+      <c r="B22" s="463"/>
+      <c r="C22" s="481"/>
+      <c r="D22" s="471"/>
       <c r="E22" s="244" t="s">
         <v>204</v>
       </c>
@@ -9224,9 +9224,9 @@
       <c r="A23" s="32">
         <v>15</v>
       </c>
-      <c r="B23" s="402"/>
-      <c r="C23" s="427"/>
-      <c r="D23" s="416"/>
+      <c r="B23" s="463"/>
+      <c r="C23" s="481"/>
+      <c r="D23" s="471"/>
       <c r="E23" s="238" t="s">
         <v>190</v>
       </c>
@@ -9269,9 +9269,9 @@
       <c r="A24" s="32">
         <v>16</v>
       </c>
-      <c r="B24" s="402"/>
-      <c r="C24" s="427"/>
-      <c r="D24" s="416"/>
+      <c r="B24" s="463"/>
+      <c r="C24" s="481"/>
+      <c r="D24" s="471"/>
       <c r="E24" s="242" t="s">
         <v>167</v>
       </c>
@@ -9314,9 +9314,9 @@
       <c r="A25" s="32">
         <v>17</v>
       </c>
-      <c r="B25" s="402"/>
-      <c r="C25" s="427"/>
-      <c r="D25" s="416"/>
+      <c r="B25" s="463"/>
+      <c r="C25" s="481"/>
+      <c r="D25" s="471"/>
       <c r="E25" s="242" t="s">
         <v>172</v>
       </c>
@@ -9359,9 +9359,9 @@
       <c r="A26" s="32">
         <v>18</v>
       </c>
-      <c r="B26" s="402"/>
-      <c r="C26" s="427"/>
-      <c r="D26" s="416"/>
+      <c r="B26" s="463"/>
+      <c r="C26" s="481"/>
+      <c r="D26" s="471"/>
       <c r="E26" s="242" t="s">
         <v>177</v>
       </c>
@@ -9404,9 +9404,9 @@
       <c r="A27" s="32">
         <v>19</v>
       </c>
-      <c r="B27" s="402"/>
-      <c r="C27" s="427"/>
-      <c r="D27" s="416"/>
+      <c r="B27" s="463"/>
+      <c r="C27" s="481"/>
+      <c r="D27" s="471"/>
       <c r="E27" s="242" t="s">
         <v>182</v>
       </c>
@@ -9449,9 +9449,9 @@
       <c r="A28" s="32">
         <v>20</v>
       </c>
-      <c r="B28" s="402"/>
-      <c r="C28" s="427"/>
-      <c r="D28" s="416"/>
+      <c r="B28" s="463"/>
+      <c r="C28" s="481"/>
+      <c r="D28" s="471"/>
       <c r="E28" s="242" t="s">
         <v>183</v>
       </c>
@@ -9494,9 +9494,9 @@
       <c r="A29" s="32">
         <v>21</v>
       </c>
-      <c r="B29" s="402"/>
-      <c r="C29" s="427"/>
-      <c r="D29" s="416"/>
+      <c r="B29" s="463"/>
+      <c r="C29" s="481"/>
+      <c r="D29" s="471"/>
       <c r="E29" s="242" t="s">
         <v>211</v>
       </c>
@@ -9539,9 +9539,9 @@
       <c r="A30" s="32">
         <v>22</v>
       </c>
-      <c r="B30" s="402"/>
-      <c r="C30" s="427"/>
-      <c r="D30" s="416"/>
+      <c r="B30" s="463"/>
+      <c r="C30" s="481"/>
+      <c r="D30" s="471"/>
       <c r="E30" s="242" t="s">
         <v>212</v>
       </c>
@@ -9584,9 +9584,9 @@
       <c r="A31" s="32">
         <v>23</v>
       </c>
-      <c r="B31" s="402"/>
-      <c r="C31" s="427"/>
-      <c r="D31" s="416"/>
+      <c r="B31" s="463"/>
+      <c r="C31" s="481"/>
+      <c r="D31" s="471"/>
       <c r="E31" s="242" t="s">
         <v>215</v>
       </c>
@@ -9629,9 +9629,9 @@
       <c r="A32" s="32">
         <v>24</v>
       </c>
-      <c r="B32" s="402"/>
-      <c r="C32" s="427"/>
-      <c r="D32" s="416"/>
+      <c r="B32" s="463"/>
+      <c r="C32" s="481"/>
+      <c r="D32" s="471"/>
       <c r="E32" s="242" t="s">
         <v>220</v>
       </c>
@@ -9674,9 +9674,9 @@
       <c r="A33" s="32">
         <v>25</v>
       </c>
-      <c r="B33" s="402"/>
-      <c r="C33" s="427"/>
-      <c r="D33" s="416"/>
+      <c r="B33" s="463"/>
+      <c r="C33" s="481"/>
+      <c r="D33" s="471"/>
       <c r="E33" s="242" t="s">
         <v>225</v>
       </c>
@@ -9719,9 +9719,9 @@
       <c r="A34" s="32">
         <v>26</v>
       </c>
-      <c r="B34" s="402"/>
-      <c r="C34" s="427"/>
-      <c r="D34" s="416"/>
+      <c r="B34" s="463"/>
+      <c r="C34" s="481"/>
+      <c r="D34" s="471"/>
       <c r="E34" s="242" t="s">
         <v>229</v>
       </c>
@@ -9764,9 +9764,9 @@
       <c r="A35" s="32">
         <v>27</v>
       </c>
-      <c r="B35" s="402"/>
-      <c r="C35" s="427"/>
-      <c r="D35" s="416"/>
+      <c r="B35" s="463"/>
+      <c r="C35" s="481"/>
+      <c r="D35" s="471"/>
       <c r="E35" s="242" t="s">
         <v>233</v>
       </c>
@@ -9809,9 +9809,9 @@
       <c r="A36" s="32">
         <v>28</v>
       </c>
-      <c r="B36" s="402"/>
-      <c r="C36" s="427"/>
-      <c r="D36" s="416"/>
+      <c r="B36" s="463"/>
+      <c r="C36" s="481"/>
+      <c r="D36" s="471"/>
       <c r="E36" s="242" t="s">
         <v>237</v>
       </c>
@@ -9854,9 +9854,9 @@
       <c r="A37" s="32">
         <v>29</v>
       </c>
-      <c r="B37" s="402"/>
-      <c r="C37" s="427"/>
-      <c r="D37" s="416"/>
+      <c r="B37" s="463"/>
+      <c r="C37" s="481"/>
+      <c r="D37" s="471"/>
       <c r="E37" s="242" t="s">
         <v>241</v>
       </c>
@@ -9899,9 +9899,9 @@
       <c r="A38" s="32">
         <v>30</v>
       </c>
-      <c r="B38" s="402"/>
-      <c r="C38" s="427"/>
-      <c r="D38" s="416"/>
+      <c r="B38" s="463"/>
+      <c r="C38" s="481"/>
+      <c r="D38" s="471"/>
       <c r="E38" s="242" t="s">
         <v>246</v>
       </c>
@@ -9946,9 +9946,9 @@
       <c r="A39" s="32">
         <v>31</v>
       </c>
-      <c r="B39" s="402"/>
-      <c r="C39" s="427"/>
-      <c r="D39" s="416"/>
+      <c r="B39" s="463"/>
+      <c r="C39" s="481"/>
+      <c r="D39" s="471"/>
       <c r="E39" s="242" t="s">
         <v>249</v>
       </c>
@@ -9993,9 +9993,9 @@
       <c r="A40" s="32">
         <v>32</v>
       </c>
-      <c r="B40" s="402"/>
-      <c r="C40" s="427"/>
-      <c r="D40" s="416"/>
+      <c r="B40" s="463"/>
+      <c r="C40" s="481"/>
+      <c r="D40" s="471"/>
       <c r="E40" s="242" t="s">
         <v>252</v>
       </c>
@@ -10038,9 +10038,9 @@
       <c r="A41" s="32">
         <v>33</v>
       </c>
-      <c r="B41" s="402"/>
-      <c r="C41" s="427"/>
-      <c r="D41" s="416"/>
+      <c r="B41" s="463"/>
+      <c r="C41" s="481"/>
+      <c r="D41" s="471"/>
       <c r="E41" s="242" t="s">
         <v>254</v>
       </c>
@@ -10083,9 +10083,9 @@
       <c r="A42" s="32">
         <v>34</v>
       </c>
-      <c r="B42" s="402"/>
-      <c r="C42" s="427"/>
-      <c r="D42" s="416"/>
+      <c r="B42" s="463"/>
+      <c r="C42" s="481"/>
+      <c r="D42" s="471"/>
       <c r="E42" s="242" t="s">
         <v>262</v>
       </c>
@@ -10128,9 +10128,9 @@
       <c r="A43" s="32">
         <v>35</v>
       </c>
-      <c r="B43" s="402"/>
-      <c r="C43" s="427"/>
-      <c r="D43" s="416"/>
+      <c r="B43" s="463"/>
+      <c r="C43" s="481"/>
+      <c r="D43" s="471"/>
       <c r="E43" s="242" t="s">
         <v>266</v>
       </c>
@@ -10173,9 +10173,9 @@
       <c r="A44" s="32">
         <v>36</v>
       </c>
-      <c r="B44" s="402"/>
-      <c r="C44" s="427"/>
-      <c r="D44" s="417"/>
+      <c r="B44" s="463"/>
+      <c r="C44" s="481"/>
+      <c r="D44" s="472"/>
       <c r="E44" s="242" t="s">
         <v>270</v>
       </c>
@@ -10218,8 +10218,8 @@
     </row>
     <row r="45" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A45" s="348"/>
-      <c r="B45" s="402"/>
-      <c r="C45" s="427"/>
+      <c r="B45" s="463"/>
+      <c r="C45" s="481"/>
       <c r="D45" s="356"/>
       <c r="E45" s="314"/>
       <c r="F45" s="316"/>
@@ -10251,9 +10251,9 @@
       <c r="A46" s="370">
         <v>37</v>
       </c>
-      <c r="B46" s="403"/>
-      <c r="C46" s="427"/>
-      <c r="D46" s="443" t="s">
+      <c r="B46" s="401"/>
+      <c r="C46" s="481"/>
+      <c r="D46" s="434" t="s">
         <v>430</v>
       </c>
       <c r="E46" s="342" t="s">
@@ -10298,9 +10298,9 @@
       <c r="A47" s="370">
         <v>38</v>
       </c>
-      <c r="B47" s="403"/>
-      <c r="C47" s="427"/>
-      <c r="D47" s="444"/>
+      <c r="B47" s="401"/>
+      <c r="C47" s="481"/>
+      <c r="D47" s="435"/>
       <c r="E47" s="343" t="s">
         <v>437</v>
       </c>
@@ -10343,9 +10343,9 @@
       <c r="A48" s="370">
         <v>39</v>
       </c>
-      <c r="B48" s="403"/>
-      <c r="C48" s="427"/>
-      <c r="D48" s="445"/>
+      <c r="B48" s="401"/>
+      <c r="C48" s="481"/>
+      <c r="D48" s="436"/>
       <c r="E48" s="345" t="s">
         <v>439</v>
       </c>
@@ -10386,8 +10386,8 @@
     </row>
     <row r="49" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A49" s="348"/>
-      <c r="B49" s="403"/>
-      <c r="C49" s="427"/>
+      <c r="B49" s="401"/>
+      <c r="C49" s="481"/>
       <c r="D49" s="356"/>
       <c r="E49" s="361"/>
       <c r="F49" s="361"/>
@@ -10419,9 +10419,9 @@
       <c r="A50" s="371">
         <v>40</v>
       </c>
-      <c r="B50" s="402"/>
-      <c r="C50" s="427"/>
-      <c r="D50" s="446" t="s">
+      <c r="B50" s="463"/>
+      <c r="C50" s="481"/>
+      <c r="D50" s="437" t="s">
         <v>273</v>
       </c>
       <c r="E50" s="315" t="s">
@@ -10468,9 +10468,9 @@
       <c r="A51" s="23">
         <v>41</v>
       </c>
-      <c r="B51" s="402"/>
-      <c r="C51" s="427"/>
-      <c r="D51" s="447"/>
+      <c r="B51" s="463"/>
+      <c r="C51" s="481"/>
+      <c r="D51" s="438"/>
       <c r="E51" s="253" t="s">
         <v>279</v>
       </c>
@@ -10515,9 +10515,9 @@
       <c r="A52" s="371">
         <v>42</v>
       </c>
-      <c r="B52" s="402"/>
-      <c r="C52" s="427"/>
-      <c r="D52" s="447"/>
+      <c r="B52" s="463"/>
+      <c r="C52" s="481"/>
+      <c r="D52" s="438"/>
       <c r="E52" s="253" t="s">
         <v>316</v>
       </c>
@@ -10560,9 +10560,9 @@
       <c r="A53" s="23">
         <v>43</v>
       </c>
-      <c r="B53" s="402"/>
-      <c r="C53" s="427"/>
-      <c r="D53" s="447"/>
+      <c r="B53" s="463"/>
+      <c r="C53" s="481"/>
+      <c r="D53" s="438"/>
       <c r="E53" s="253" t="s">
         <v>282</v>
       </c>
@@ -10607,9 +10607,9 @@
       <c r="A54" s="371">
         <v>44</v>
       </c>
-      <c r="B54" s="402"/>
-      <c r="C54" s="427"/>
-      <c r="D54" s="447"/>
+      <c r="B54" s="463"/>
+      <c r="C54" s="481"/>
+      <c r="D54" s="438"/>
       <c r="E54" s="253" t="s">
         <v>286</v>
       </c>
@@ -10654,9 +10654,9 @@
       <c r="A55" s="23">
         <v>45</v>
       </c>
-      <c r="B55" s="402"/>
-      <c r="C55" s="427"/>
-      <c r="D55" s="447"/>
+      <c r="B55" s="463"/>
+      <c r="C55" s="481"/>
+      <c r="D55" s="438"/>
       <c r="E55" s="253" t="s">
         <v>290</v>
       </c>
@@ -10701,9 +10701,9 @@
       <c r="A56" s="371">
         <v>46</v>
       </c>
-      <c r="B56" s="402"/>
-      <c r="C56" s="427"/>
-      <c r="D56" s="447"/>
+      <c r="B56" s="463"/>
+      <c r="C56" s="481"/>
+      <c r="D56" s="438"/>
       <c r="E56" s="253" t="s">
         <v>298</v>
       </c>
@@ -10748,9 +10748,9 @@
       <c r="A57" s="23">
         <v>47</v>
       </c>
-      <c r="B57" s="402"/>
-      <c r="C57" s="427"/>
-      <c r="D57" s="447"/>
+      <c r="B57" s="463"/>
+      <c r="C57" s="481"/>
+      <c r="D57" s="438"/>
       <c r="E57" s="253" t="s">
         <v>299</v>
       </c>
@@ -10795,9 +10795,9 @@
       <c r="A58" s="371">
         <v>48</v>
       </c>
-      <c r="B58" s="402"/>
-      <c r="C58" s="427"/>
-      <c r="D58" s="447"/>
+      <c r="B58" s="463"/>
+      <c r="C58" s="481"/>
+      <c r="D58" s="438"/>
       <c r="E58" s="253" t="s">
         <v>306</v>
       </c>
@@ -10840,9 +10840,9 @@
       <c r="A59" s="23">
         <v>49</v>
       </c>
-      <c r="B59" s="402"/>
-      <c r="C59" s="427"/>
-      <c r="D59" s="447"/>
+      <c r="B59" s="463"/>
+      <c r="C59" s="481"/>
+      <c r="D59" s="438"/>
       <c r="E59" s="253" t="s">
         <v>311</v>
       </c>
@@ -10885,9 +10885,9 @@
       <c r="A60" s="371">
         <v>50</v>
       </c>
-      <c r="B60" s="402"/>
-      <c r="C60" s="427"/>
-      <c r="D60" s="447"/>
+      <c r="B60" s="463"/>
+      <c r="C60" s="481"/>
+      <c r="D60" s="438"/>
       <c r="E60" s="43" t="s">
         <v>195</v>
       </c>
@@ -10930,9 +10930,9 @@
       <c r="A61" s="23">
         <v>51</v>
       </c>
-      <c r="B61" s="402"/>
-      <c r="C61" s="427"/>
-      <c r="D61" s="447"/>
+      <c r="B61" s="463"/>
+      <c r="C61" s="481"/>
+      <c r="D61" s="438"/>
       <c r="E61" s="50" t="s">
         <v>200</v>
       </c>
@@ -10975,9 +10975,9 @@
       <c r="A62" s="371">
         <v>52</v>
       </c>
-      <c r="B62" s="402"/>
-      <c r="C62" s="427"/>
-      <c r="D62" s="447"/>
+      <c r="B62" s="463"/>
+      <c r="C62" s="481"/>
+      <c r="D62" s="438"/>
       <c r="E62" s="50" t="s">
         <v>323</v>
       </c>
@@ -11020,9 +11020,9 @@
       <c r="A63" s="23">
         <v>53</v>
       </c>
-      <c r="B63" s="402"/>
-      <c r="C63" s="427"/>
-      <c r="D63" s="447"/>
+      <c r="B63" s="463"/>
+      <c r="C63" s="481"/>
+      <c r="D63" s="438"/>
       <c r="E63" s="50" t="s">
         <v>327</v>
       </c>
@@ -11065,9 +11065,9 @@
       <c r="A64" s="371">
         <v>54</v>
       </c>
-      <c r="B64" s="402"/>
-      <c r="C64" s="427"/>
-      <c r="D64" s="447"/>
+      <c r="B64" s="463"/>
+      <c r="C64" s="481"/>
+      <c r="D64" s="438"/>
       <c r="E64" s="50" t="s">
         <v>331</v>
       </c>
@@ -11110,9 +11110,9 @@
       <c r="A65" s="23">
         <v>55</v>
       </c>
-      <c r="B65" s="402"/>
-      <c r="C65" s="427"/>
-      <c r="D65" s="447"/>
+      <c r="B65" s="463"/>
+      <c r="C65" s="481"/>
+      <c r="D65" s="438"/>
       <c r="E65" s="253" t="s">
         <v>337</v>
       </c>
@@ -11155,9 +11155,9 @@
       <c r="A66" s="371">
         <v>56</v>
       </c>
-      <c r="B66" s="402"/>
-      <c r="C66" s="427"/>
-      <c r="D66" s="447"/>
+      <c r="B66" s="463"/>
+      <c r="C66" s="481"/>
+      <c r="D66" s="438"/>
       <c r="E66" s="253" t="s">
         <v>343</v>
       </c>
@@ -11198,8 +11198,8 @@
     </row>
     <row r="67" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A67" s="348"/>
-      <c r="B67" s="402"/>
-      <c r="C67" s="427"/>
+      <c r="B67" s="463"/>
+      <c r="C67" s="481"/>
       <c r="D67" s="356"/>
       <c r="E67" s="314"/>
       <c r="F67" s="316"/>
@@ -11231,9 +11231,9 @@
       <c r="A68" s="23">
         <v>57</v>
       </c>
-      <c r="B68" s="402"/>
-      <c r="C68" s="427"/>
-      <c r="D68" s="448" t="s">
+      <c r="B68" s="463"/>
+      <c r="C68" s="481"/>
+      <c r="D68" s="439" t="s">
         <v>490</v>
       </c>
       <c r="E68" s="357" t="s">
@@ -11278,9 +11278,9 @@
       <c r="A69" s="23">
         <v>58</v>
       </c>
-      <c r="B69" s="402"/>
-      <c r="C69" s="427"/>
-      <c r="D69" s="449"/>
+      <c r="B69" s="463"/>
+      <c r="C69" s="481"/>
+      <c r="D69" s="440"/>
       <c r="E69" s="357" t="s">
         <v>455</v>
       </c>
@@ -11323,9 +11323,9 @@
       <c r="A70" s="23">
         <v>59</v>
       </c>
-      <c r="B70" s="402"/>
-      <c r="C70" s="427"/>
-      <c r="D70" s="449"/>
+      <c r="B70" s="463"/>
+      <c r="C70" s="481"/>
+      <c r="D70" s="440"/>
       <c r="E70" s="357" t="s">
         <v>444</v>
       </c>
@@ -11368,9 +11368,9 @@
       <c r="A71" s="23">
         <v>60</v>
       </c>
-      <c r="B71" s="402"/>
-      <c r="C71" s="427"/>
-      <c r="D71" s="449"/>
+      <c r="B71" s="463"/>
+      <c r="C71" s="481"/>
+      <c r="D71" s="440"/>
       <c r="E71" s="357" t="s">
         <v>445</v>
       </c>
@@ -11413,9 +11413,9 @@
       <c r="A72" s="23">
         <v>61</v>
       </c>
-      <c r="B72" s="402"/>
-      <c r="C72" s="427"/>
-      <c r="D72" s="449"/>
+      <c r="B72" s="463"/>
+      <c r="C72" s="481"/>
+      <c r="D72" s="440"/>
       <c r="E72" s="358" t="s">
         <v>446</v>
       </c>
@@ -11458,9 +11458,9 @@
       <c r="A73" s="23">
         <v>62</v>
       </c>
-      <c r="B73" s="402"/>
-      <c r="C73" s="427"/>
-      <c r="D73" s="449"/>
+      <c r="B73" s="463"/>
+      <c r="C73" s="481"/>
+      <c r="D73" s="440"/>
       <c r="E73" s="357" t="s">
         <v>447</v>
       </c>
@@ -11503,9 +11503,9 @@
       <c r="A74" s="23">
         <v>63</v>
       </c>
-      <c r="B74" s="402"/>
-      <c r="C74" s="427"/>
-      <c r="D74" s="449"/>
+      <c r="B74" s="463"/>
+      <c r="C74" s="481"/>
+      <c r="D74" s="440"/>
       <c r="E74" s="357" t="s">
         <v>448</v>
       </c>
@@ -11548,9 +11548,9 @@
       <c r="A75" s="23">
         <v>64</v>
       </c>
-      <c r="B75" s="402"/>
-      <c r="C75" s="427"/>
-      <c r="D75" s="449"/>
+      <c r="B75" s="463"/>
+      <c r="C75" s="481"/>
+      <c r="D75" s="440"/>
       <c r="E75" s="357" t="s">
         <v>449</v>
       </c>
@@ -11593,9 +11593,9 @@
       <c r="A76" s="23">
         <v>65</v>
       </c>
-      <c r="B76" s="402"/>
-      <c r="C76" s="427"/>
-      <c r="D76" s="449"/>
+      <c r="B76" s="463"/>
+      <c r="C76" s="481"/>
+      <c r="D76" s="440"/>
       <c r="E76" s="357" t="s">
         <v>452</v>
       </c>
@@ -11638,9 +11638,9 @@
       <c r="A77" s="23">
         <v>66</v>
       </c>
-      <c r="B77" s="402"/>
-      <c r="C77" s="427"/>
-      <c r="D77" s="449"/>
+      <c r="B77" s="463"/>
+      <c r="C77" s="481"/>
+      <c r="D77" s="440"/>
       <c r="E77" s="357" t="s">
         <v>450</v>
       </c>
@@ -11683,9 +11683,9 @@
       <c r="A78" s="23">
         <v>67</v>
       </c>
-      <c r="B78" s="402"/>
-      <c r="C78" s="427"/>
-      <c r="D78" s="449"/>
+      <c r="B78" s="463"/>
+      <c r="C78" s="481"/>
+      <c r="D78" s="440"/>
       <c r="E78" s="357" t="s">
         <v>477</v>
       </c>
@@ -11728,9 +11728,9 @@
       <c r="A79" s="23">
         <v>68</v>
       </c>
-      <c r="B79" s="402"/>
-      <c r="C79" s="427"/>
-      <c r="D79" s="450"/>
+      <c r="B79" s="463"/>
+      <c r="C79" s="481"/>
+      <c r="D79" s="441"/>
       <c r="E79" s="359" t="s">
         <v>451</v>
       </c>
@@ -11771,8 +11771,8 @@
     </row>
     <row r="80" spans="1:29" ht="16.2" customHeight="1" thickBot="1">
       <c r="A80" s="348"/>
-      <c r="B80" s="402"/>
-      <c r="C80" s="427"/>
+      <c r="B80" s="463"/>
+      <c r="C80" s="481"/>
       <c r="D80" s="356"/>
       <c r="E80" s="314"/>
       <c r="F80" s="316"/>
@@ -11804,9 +11804,9 @@
       <c r="A81" s="23">
         <v>69</v>
       </c>
-      <c r="B81" s="402"/>
-      <c r="C81" s="427"/>
-      <c r="D81" s="451" t="s">
+      <c r="B81" s="463"/>
+      <c r="C81" s="481"/>
+      <c r="D81" s="442" t="s">
         <v>503</v>
       </c>
       <c r="E81" s="374" t="s">
@@ -11851,9 +11851,9 @@
       <c r="A82" s="23">
         <v>70</v>
       </c>
-      <c r="B82" s="402"/>
-      <c r="C82" s="427"/>
-      <c r="D82" s="452"/>
+      <c r="B82" s="463"/>
+      <c r="C82" s="481"/>
+      <c r="D82" s="443"/>
       <c r="E82" s="375" t="s">
         <v>522</v>
       </c>
@@ -11896,9 +11896,9 @@
       <c r="A83" s="23">
         <v>71</v>
       </c>
-      <c r="B83" s="402"/>
-      <c r="C83" s="427"/>
-      <c r="D83" s="452"/>
+      <c r="B83" s="463"/>
+      <c r="C83" s="481"/>
+      <c r="D83" s="443"/>
       <c r="E83" s="376" t="s">
         <v>521</v>
       </c>
@@ -11943,9 +11943,9 @@
       <c r="A84" s="23">
         <v>72</v>
       </c>
-      <c r="B84" s="402"/>
-      <c r="C84" s="427"/>
-      <c r="D84" s="452"/>
+      <c r="B84" s="463"/>
+      <c r="C84" s="481"/>
+      <c r="D84" s="443"/>
       <c r="E84" s="376" t="s">
         <v>520</v>
       </c>
@@ -11988,9 +11988,9 @@
       <c r="A85" s="23">
         <v>73</v>
       </c>
-      <c r="B85" s="402"/>
-      <c r="C85" s="427"/>
-      <c r="D85" s="452"/>
+      <c r="B85" s="463"/>
+      <c r="C85" s="481"/>
+      <c r="D85" s="443"/>
       <c r="E85" s="376" t="s">
         <v>519</v>
       </c>
@@ -12033,9 +12033,9 @@
       <c r="A86" s="23">
         <v>74</v>
       </c>
-      <c r="B86" s="402"/>
-      <c r="C86" s="427"/>
-      <c r="D86" s="452"/>
+      <c r="B86" s="463"/>
+      <c r="C86" s="481"/>
+      <c r="D86" s="443"/>
       <c r="E86" s="376" t="s">
         <v>528</v>
       </c>
@@ -12078,9 +12078,9 @@
       <c r="A87" s="23">
         <v>75</v>
       </c>
-      <c r="B87" s="402"/>
-      <c r="C87" s="427"/>
-      <c r="D87" s="452"/>
+      <c r="B87" s="463"/>
+      <c r="C87" s="481"/>
+      <c r="D87" s="443"/>
       <c r="E87" s="376" t="s">
         <v>533</v>
       </c>
@@ -12121,8 +12121,8 @@
     </row>
     <row r="88" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A88" s="55"/>
-      <c r="B88" s="402"/>
-      <c r="C88" s="427"/>
+      <c r="B88" s="463"/>
+      <c r="C88" s="481"/>
       <c r="D88" s="379"/>
       <c r="E88" s="378"/>
       <c r="F88" s="56"/>
@@ -12154,9 +12154,9 @@
       <c r="A89" s="23">
         <v>76</v>
       </c>
-      <c r="B89" s="402"/>
-      <c r="C89" s="427"/>
-      <c r="D89" s="453" t="s">
+      <c r="B89" s="463"/>
+      <c r="C89" s="481"/>
+      <c r="D89" s="444" t="s">
         <v>538</v>
       </c>
       <c r="E89" s="252" t="s">
@@ -12201,9 +12201,9 @@
       <c r="A90" s="23">
         <v>77</v>
       </c>
-      <c r="B90" s="402"/>
-      <c r="C90" s="427"/>
-      <c r="D90" s="454"/>
+      <c r="B90" s="463"/>
+      <c r="C90" s="481"/>
+      <c r="D90" s="445"/>
       <c r="E90" s="253" t="s">
         <v>543</v>
       </c>
@@ -12246,9 +12246,9 @@
       <c r="A91" s="23">
         <v>78</v>
       </c>
-      <c r="B91" s="402"/>
-      <c r="C91" s="427"/>
-      <c r="D91" s="454"/>
+      <c r="B91" s="463"/>
+      <c r="C91" s="481"/>
+      <c r="D91" s="445"/>
       <c r="E91" s="253" t="s">
         <v>549</v>
       </c>
@@ -12291,9 +12291,9 @@
       <c r="A92" s="23">
         <v>79</v>
       </c>
-      <c r="B92" s="402"/>
-      <c r="C92" s="427"/>
-      <c r="D92" s="454"/>
+      <c r="B92" s="463"/>
+      <c r="C92" s="481"/>
+      <c r="D92" s="445"/>
       <c r="E92" s="253" t="s">
         <v>554</v>
       </c>
@@ -12336,9 +12336,9 @@
       <c r="A93" s="23">
         <v>80</v>
       </c>
-      <c r="B93" s="402"/>
-      <c r="C93" s="427"/>
-      <c r="D93" s="454"/>
+      <c r="B93" s="463"/>
+      <c r="C93" s="481"/>
+      <c r="D93" s="445"/>
       <c r="E93" s="380" t="s">
         <v>559</v>
       </c>
@@ -12381,9 +12381,9 @@
       <c r="A94" s="23">
         <v>81</v>
       </c>
-      <c r="B94" s="402"/>
-      <c r="C94" s="427"/>
-      <c r="D94" s="454"/>
+      <c r="B94" s="463"/>
+      <c r="C94" s="481"/>
+      <c r="D94" s="445"/>
       <c r="E94" s="380" t="s">
         <v>564</v>
       </c>
@@ -12426,9 +12426,9 @@
       <c r="A95" s="23">
         <v>82</v>
       </c>
-      <c r="B95" s="402"/>
-      <c r="C95" s="427"/>
-      <c r="D95" s="454"/>
+      <c r="B95" s="463"/>
+      <c r="C95" s="481"/>
+      <c r="D95" s="445"/>
       <c r="E95" s="380" t="s">
         <v>568</v>
       </c>
@@ -12471,9 +12471,9 @@
       <c r="A96" s="23">
         <v>83</v>
       </c>
-      <c r="B96" s="402"/>
-      <c r="C96" s="427"/>
-      <c r="D96" s="454"/>
+      <c r="B96" s="463"/>
+      <c r="C96" s="481"/>
+      <c r="D96" s="445"/>
       <c r="E96" s="380" t="s">
         <v>573</v>
       </c>
@@ -12516,9 +12516,9 @@
       <c r="A97" s="23">
         <v>84</v>
       </c>
-      <c r="B97" s="402"/>
-      <c r="C97" s="427"/>
-      <c r="D97" s="454"/>
+      <c r="B97" s="463"/>
+      <c r="C97" s="481"/>
+      <c r="D97" s="445"/>
       <c r="E97" s="380" t="s">
         <v>578</v>
       </c>
@@ -12561,9 +12561,9 @@
       <c r="A98" s="23">
         <v>85</v>
       </c>
-      <c r="B98" s="402"/>
-      <c r="C98" s="427"/>
-      <c r="D98" s="454"/>
+      <c r="B98" s="463"/>
+      <c r="C98" s="481"/>
+      <c r="D98" s="445"/>
       <c r="E98" s="380" t="s">
         <v>583</v>
       </c>
@@ -12606,9 +12606,9 @@
       <c r="A99" s="23">
         <v>86</v>
       </c>
-      <c r="B99" s="402"/>
-      <c r="C99" s="427"/>
-      <c r="D99" s="455"/>
+      <c r="B99" s="463"/>
+      <c r="C99" s="481"/>
+      <c r="D99" s="446"/>
       <c r="E99" s="265" t="s">
         <v>587</v>
       </c>
@@ -12630,8 +12630,8 @@
     </row>
     <row r="100" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A100" s="55"/>
-      <c r="B100" s="402"/>
-      <c r="C100" s="427"/>
+      <c r="B100" s="463"/>
+      <c r="C100" s="481"/>
       <c r="D100" s="379"/>
       <c r="E100" s="378"/>
       <c r="F100" s="56"/>
@@ -12663,9 +12663,9 @@
       <c r="A101" s="23">
         <v>87</v>
       </c>
-      <c r="B101" s="402"/>
-      <c r="C101" s="427"/>
-      <c r="D101" s="456" t="s">
+      <c r="B101" s="463"/>
+      <c r="C101" s="481"/>
+      <c r="D101" s="447" t="s">
         <v>593</v>
       </c>
       <c r="E101" s="265" t="s">
@@ -12691,9 +12691,9 @@
       <c r="A102" s="23">
         <v>88</v>
       </c>
-      <c r="B102" s="402"/>
-      <c r="C102" s="427"/>
-      <c r="D102" s="457"/>
+      <c r="B102" s="463"/>
+      <c r="C102" s="481"/>
+      <c r="D102" s="448"/>
       <c r="E102" s="265" t="s">
         <v>598</v>
       </c>
@@ -12717,9 +12717,9 @@
       <c r="A103" s="23">
         <v>89</v>
       </c>
-      <c r="B103" s="402"/>
-      <c r="C103" s="427"/>
-      <c r="D103" s="457"/>
+      <c r="B103" s="463"/>
+      <c r="C103" s="481"/>
+      <c r="D103" s="448"/>
       <c r="E103" s="265" t="s">
         <v>602</v>
       </c>
@@ -12743,9 +12743,9 @@
       <c r="A104" s="23">
         <v>90</v>
       </c>
-      <c r="B104" s="402"/>
-      <c r="C104" s="427"/>
-      <c r="D104" s="457"/>
+      <c r="B104" s="463"/>
+      <c r="C104" s="481"/>
+      <c r="D104" s="448"/>
       <c r="E104" s="265" t="s">
         <v>609</v>
       </c>
@@ -12769,9 +12769,9 @@
       <c r="A105" s="23">
         <v>91</v>
       </c>
-      <c r="B105" s="402"/>
-      <c r="C105" s="427"/>
-      <c r="D105" s="457"/>
+      <c r="B105" s="463"/>
+      <c r="C105" s="481"/>
+      <c r="D105" s="448"/>
       <c r="E105" s="265" t="s">
         <v>614</v>
       </c>
@@ -12793,8 +12793,8 @@
     </row>
     <row r="106" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A106" s="55"/>
-      <c r="B106" s="402"/>
-      <c r="C106" s="427"/>
+      <c r="B106" s="463"/>
+      <c r="C106" s="481"/>
       <c r="D106" s="379"/>
       <c r="E106" s="378"/>
       <c r="F106" s="56"/>
@@ -12826,9 +12826,9 @@
       <c r="A107" s="42">
         <v>92</v>
       </c>
-      <c r="B107" s="402"/>
-      <c r="C107" s="427"/>
-      <c r="D107" s="412"/>
+      <c r="B107" s="463"/>
+      <c r="C107" s="481"/>
+      <c r="D107" s="467"/>
       <c r="E107" s="252" t="s">
         <v>621</v>
       </c>
@@ -12871,9 +12871,9 @@
       <c r="A108" s="42">
         <v>93</v>
       </c>
-      <c r="B108" s="402"/>
-      <c r="C108" s="427"/>
-      <c r="D108" s="413"/>
+      <c r="B108" s="463"/>
+      <c r="C108" s="481"/>
+      <c r="D108" s="468"/>
       <c r="E108" s="253" t="s">
         <v>626</v>
       </c>
@@ -12916,9 +12916,9 @@
       <c r="A109" s="42">
         <v>94</v>
       </c>
-      <c r="B109" s="402"/>
-      <c r="C109" s="427"/>
-      <c r="D109" s="413"/>
+      <c r="B109" s="463"/>
+      <c r="C109" s="481"/>
+      <c r="D109" s="468"/>
       <c r="E109" s="253" t="s">
         <v>631</v>
       </c>
@@ -12961,9 +12961,9 @@
       <c r="A110" s="42">
         <v>95</v>
       </c>
-      <c r="B110" s="402"/>
-      <c r="C110" s="427"/>
-      <c r="D110" s="413"/>
+      <c r="B110" s="463"/>
+      <c r="C110" s="481"/>
+      <c r="D110" s="468"/>
       <c r="E110" s="253" t="s">
         <v>636</v>
       </c>
@@ -13006,9 +13006,9 @@
       <c r="A111" s="42">
         <v>96</v>
       </c>
-      <c r="B111" s="402"/>
-      <c r="C111" s="427"/>
-      <c r="D111" s="413"/>
+      <c r="B111" s="463"/>
+      <c r="C111" s="481"/>
+      <c r="D111" s="468"/>
       <c r="E111" s="253" t="s">
         <v>641</v>
       </c>
@@ -13051,9 +13051,9 @@
       <c r="A112" s="42">
         <v>97</v>
       </c>
-      <c r="B112" s="402"/>
-      <c r="C112" s="427"/>
-      <c r="D112" s="413"/>
+      <c r="B112" s="463"/>
+      <c r="C112" s="481"/>
+      <c r="D112" s="468"/>
       <c r="E112" s="381" t="s">
         <v>646</v>
       </c>
@@ -13096,9 +13096,9 @@
       <c r="A113" s="42">
         <v>98</v>
       </c>
-      <c r="B113" s="402"/>
-      <c r="C113" s="427"/>
-      <c r="D113" s="413"/>
+      <c r="B113" s="463"/>
+      <c r="C113" s="481"/>
+      <c r="D113" s="468"/>
       <c r="E113" s="382" t="s">
         <v>651</v>
       </c>
@@ -13139,9 +13139,9 @@
     </row>
     <row r="114" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A114" s="55"/>
-      <c r="B114" s="402"/>
-      <c r="C114" s="427"/>
-      <c r="D114" s="413"/>
+      <c r="B114" s="463"/>
+      <c r="C114" s="481"/>
+      <c r="D114" s="468"/>
       <c r="E114" s="378"/>
       <c r="F114" s="56"/>
       <c r="G114" s="56"/>
@@ -13170,9 +13170,9 @@
     </row>
     <row r="115" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A115" s="42"/>
-      <c r="B115" s="402"/>
-      <c r="C115" s="427"/>
-      <c r="D115" s="413"/>
+      <c r="B115" s="463"/>
+      <c r="C115" s="481"/>
+      <c r="D115" s="468"/>
       <c r="E115" s="62"/>
       <c r="F115" s="54"/>
       <c r="G115" s="54"/>
@@ -13201,9 +13201,9 @@
     </row>
     <row r="116" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A116" s="42"/>
-      <c r="B116" s="402"/>
-      <c r="C116" s="427"/>
-      <c r="D116" s="413"/>
+      <c r="B116" s="463"/>
+      <c r="C116" s="481"/>
+      <c r="D116" s="468"/>
       <c r="E116" s="62"/>
       <c r="F116" s="54"/>
       <c r="G116" s="44"/>
@@ -13232,9 +13232,9 @@
     </row>
     <row r="117" spans="1:29" ht="30.75" customHeight="1" thickBot="1">
       <c r="A117" s="42"/>
-      <c r="B117" s="402"/>
-      <c r="C117" s="427"/>
-      <c r="D117" s="413"/>
+      <c r="B117" s="463"/>
+      <c r="C117" s="481"/>
+      <c r="D117" s="468"/>
       <c r="E117" s="34"/>
       <c r="F117" s="54"/>
       <c r="G117" s="44"/>
@@ -13263,9 +13263,9 @@
     </row>
     <row r="118" spans="1:29" ht="30.75" customHeight="1" thickBot="1">
       <c r="A118" s="42"/>
-      <c r="B118" s="402"/>
-      <c r="C118" s="427"/>
-      <c r="D118" s="414"/>
+      <c r="B118" s="463"/>
+      <c r="C118" s="481"/>
+      <c r="D118" s="469"/>
       <c r="E118" s="50"/>
       <c r="F118" s="54"/>
       <c r="G118" s="44"/>
@@ -13294,8 +13294,8 @@
     </row>
     <row r="119" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A119" s="55"/>
-      <c r="B119" s="402"/>
-      <c r="C119" s="428"/>
+      <c r="B119" s="463"/>
+      <c r="C119" s="482"/>
       <c r="D119" s="373"/>
       <c r="E119" s="63"/>
       <c r="F119" s="56"/>
@@ -13325,9 +13325,9 @@
     </row>
     <row r="120" spans="1:29" ht="30" customHeight="1" thickBot="1">
       <c r="A120" s="42"/>
-      <c r="B120" s="404"/>
-      <c r="C120" s="422"/>
-      <c r="D120" s="423"/>
+      <c r="B120" s="384"/>
+      <c r="C120" s="476"/>
+      <c r="D120" s="477"/>
       <c r="E120" s="64"/>
       <c r="F120" s="44"/>
       <c r="G120" s="44"/>
@@ -13356,9 +13356,9 @@
     </row>
     <row r="121" spans="1:29" ht="28.5" customHeight="1" thickBot="1">
       <c r="A121" s="42"/>
-      <c r="B121" s="404"/>
-      <c r="C121" s="404"/>
-      <c r="D121" s="404"/>
+      <c r="B121" s="384"/>
+      <c r="C121" s="384"/>
+      <c r="D121" s="384"/>
       <c r="E121" s="64"/>
       <c r="F121" s="44"/>
       <c r="G121" s="44"/>
@@ -13387,9 +13387,9 @@
     </row>
     <row r="122" spans="1:29" ht="26.25" customHeight="1">
       <c r="A122" s="42"/>
-      <c r="B122" s="404"/>
-      <c r="C122" s="404"/>
-      <c r="D122" s="404"/>
+      <c r="B122" s="384"/>
+      <c r="C122" s="384"/>
+      <c r="D122" s="384"/>
       <c r="E122" s="44"/>
       <c r="F122" s="65"/>
       <c r="G122" s="44"/>
@@ -13418,9 +13418,9 @@
     </row>
     <row r="123" spans="1:29" ht="30" customHeight="1">
       <c r="A123" s="42"/>
-      <c r="B123" s="404"/>
-      <c r="C123" s="404"/>
-      <c r="D123" s="405"/>
+      <c r="B123" s="384"/>
+      <c r="C123" s="384"/>
+      <c r="D123" s="385"/>
       <c r="E123" s="44"/>
       <c r="F123" s="44"/>
       <c r="G123" s="44"/>
@@ -13449,8 +13449,8 @@
     </row>
     <row r="124" spans="1:29" ht="15.75" customHeight="1">
       <c r="A124" s="42"/>
-      <c r="B124" s="404"/>
-      <c r="C124" s="405"/>
+      <c r="B124" s="384"/>
+      <c r="C124" s="385"/>
       <c r="D124" s="66"/>
       <c r="E124" s="67"/>
       <c r="F124" s="44"/>
@@ -13480,7 +13480,7 @@
     </row>
     <row r="125" spans="1:29" ht="15.75" customHeight="1">
       <c r="A125" s="68"/>
-      <c r="B125" s="404"/>
+      <c r="B125" s="384"/>
       <c r="C125" s="69"/>
       <c r="D125" s="66"/>
       <c r="E125" s="67"/>
@@ -13511,7 +13511,7 @@
     </row>
     <row r="126" spans="1:29" ht="15.75" customHeight="1">
       <c r="A126" s="68"/>
-      <c r="B126" s="404"/>
+      <c r="B126" s="384"/>
       <c r="C126" s="69"/>
       <c r="D126" s="66"/>
       <c r="E126" s="70"/>
@@ -13542,7 +13542,7 @@
     </row>
     <row r="127" spans="1:29" ht="15.75" customHeight="1">
       <c r="A127" s="68"/>
-      <c r="B127" s="404"/>
+      <c r="B127" s="384"/>
       <c r="C127" s="69"/>
       <c r="D127" s="66"/>
       <c r="E127" s="70"/>
@@ -13573,7 +13573,7 @@
     </row>
     <row r="128" spans="1:29" ht="15.75" customHeight="1">
       <c r="A128" s="68"/>
-      <c r="B128" s="404"/>
+      <c r="B128" s="384"/>
       <c r="C128" s="69"/>
       <c r="D128" s="66"/>
       <c r="E128" s="70"/>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="129" spans="1:29" ht="15.75" customHeight="1">
       <c r="A129" s="68"/>
-      <c r="B129" s="404"/>
+      <c r="B129" s="384"/>
       <c r="C129" s="69"/>
       <c r="D129" s="66"/>
       <c r="E129" s="70"/>
@@ -13635,7 +13635,7 @@
     </row>
     <row r="130" spans="1:29" ht="15.75" customHeight="1">
       <c r="A130" s="68"/>
-      <c r="B130" s="404"/>
+      <c r="B130" s="384"/>
       <c r="C130" s="69"/>
       <c r="D130" s="71"/>
       <c r="E130" s="70"/>
@@ -13666,9 +13666,9 @@
     </row>
     <row r="131" spans="1:29" ht="15.75" customHeight="1">
       <c r="A131" s="68"/>
-      <c r="B131" s="404"/>
+      <c r="B131" s="384"/>
       <c r="C131" s="69"/>
-      <c r="D131" s="424"/>
+      <c r="D131" s="478"/>
       <c r="E131" s="70"/>
       <c r="F131" s="65"/>
       <c r="G131" s="44"/>
@@ -13697,9 +13697,9 @@
     </row>
     <row r="132" spans="1:29" ht="15.75" customHeight="1">
       <c r="A132" s="68"/>
-      <c r="B132" s="404"/>
+      <c r="B132" s="384"/>
       <c r="C132" s="69"/>
-      <c r="D132" s="404"/>
+      <c r="D132" s="384"/>
       <c r="E132" s="70"/>
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
@@ -13728,9 +13728,9 @@
     </row>
     <row r="133" spans="1:29" ht="15.75" customHeight="1">
       <c r="A133" s="68"/>
-      <c r="B133" s="404"/>
+      <c r="B133" s="384"/>
       <c r="C133" s="69"/>
-      <c r="D133" s="404"/>
+      <c r="D133" s="384"/>
       <c r="E133" s="72"/>
       <c r="F133" s="49"/>
       <c r="G133" s="44"/>
@@ -13759,9 +13759,9 @@
     </row>
     <row r="134" spans="1:29" ht="15.75" customHeight="1">
       <c r="A134" s="68"/>
-      <c r="B134" s="404"/>
+      <c r="B134" s="384"/>
       <c r="C134" s="69"/>
-      <c r="D134" s="404"/>
+      <c r="D134" s="384"/>
       <c r="E134" s="72"/>
       <c r="F134" s="49"/>
       <c r="G134" s="44"/>
@@ -13790,9 +13790,9 @@
     </row>
     <row r="135" spans="1:29" ht="15.75" customHeight="1">
       <c r="A135" s="68"/>
-      <c r="B135" s="404"/>
+      <c r="B135" s="384"/>
       <c r="C135" s="69"/>
-      <c r="D135" s="405"/>
+      <c r="D135" s="385"/>
       <c r="E135" s="72"/>
       <c r="F135" s="49"/>
       <c r="G135" s="44"/>
@@ -13821,7 +13821,7 @@
     </row>
     <row r="136" spans="1:29" ht="15.75" customHeight="1">
       <c r="A136" s="68"/>
-      <c r="B136" s="404"/>
+      <c r="B136" s="384"/>
       <c r="C136" s="69"/>
       <c r="D136" s="73"/>
       <c r="E136" s="74"/>
@@ -13852,9 +13852,9 @@
     </row>
     <row r="137" spans="1:29" ht="15.75" customHeight="1">
       <c r="A137" s="68"/>
-      <c r="B137" s="404"/>
+      <c r="B137" s="384"/>
       <c r="C137" s="69"/>
-      <c r="D137" s="424"/>
+      <c r="D137" s="478"/>
       <c r="E137" s="67"/>
       <c r="F137" s="44"/>
       <c r="G137" s="44"/>
@@ -13883,9 +13883,9 @@
     </row>
     <row r="138" spans="1:29" ht="15.75" customHeight="1">
       <c r="A138" s="68"/>
-      <c r="B138" s="404"/>
+      <c r="B138" s="384"/>
       <c r="C138" s="69"/>
-      <c r="D138" s="405"/>
+      <c r="D138" s="385"/>
       <c r="E138" s="67"/>
       <c r="F138" s="44"/>
       <c r="G138" s="44"/>
@@ -13914,7 +13914,7 @@
     </row>
     <row r="139" spans="1:29" ht="15.75" customHeight="1">
       <c r="A139" s="68"/>
-      <c r="B139" s="404"/>
+      <c r="B139" s="384"/>
       <c r="C139" s="69"/>
       <c r="D139" s="75"/>
       <c r="E139" s="70"/>
@@ -13945,9 +13945,9 @@
     </row>
     <row r="140" spans="1:29" ht="15.75" customHeight="1">
       <c r="A140" s="68"/>
-      <c r="B140" s="404"/>
+      <c r="B140" s="384"/>
       <c r="C140" s="69"/>
-      <c r="D140" s="425"/>
+      <c r="D140" s="479"/>
       <c r="E140" s="70"/>
       <c r="F140" s="44"/>
       <c r="G140" s="44"/>
@@ -13976,9 +13976,9 @@
     </row>
     <row r="141" spans="1:29" ht="15.75" customHeight="1">
       <c r="A141" s="68"/>
-      <c r="B141" s="404"/>
+      <c r="B141" s="384"/>
       <c r="C141" s="69"/>
-      <c r="D141" s="404"/>
+      <c r="D141" s="384"/>
       <c r="E141" s="70"/>
       <c r="F141" s="44"/>
       <c r="G141" s="44"/>
@@ -14007,9 +14007,9 @@
     </row>
     <row r="142" spans="1:29" ht="15.75" customHeight="1">
       <c r="A142" s="68"/>
-      <c r="B142" s="404"/>
+      <c r="B142" s="384"/>
       <c r="C142" s="69"/>
-      <c r="D142" s="404"/>
+      <c r="D142" s="384"/>
       <c r="E142" s="72"/>
       <c r="F142" s="49"/>
       <c r="G142" s="44"/>
@@ -14038,9 +14038,9 @@
     </row>
     <row r="143" spans="1:29" ht="15.75" customHeight="1">
       <c r="A143" s="68"/>
-      <c r="B143" s="404"/>
+      <c r="B143" s="384"/>
       <c r="C143" s="69"/>
-      <c r="D143" s="404"/>
+      <c r="D143" s="384"/>
       <c r="E143" s="67"/>
       <c r="F143" s="44"/>
       <c r="G143" s="44"/>
@@ -14069,9 +14069,9 @@
     </row>
     <row r="144" spans="1:29" ht="15.75" customHeight="1">
       <c r="A144" s="68"/>
-      <c r="B144" s="404"/>
+      <c r="B144" s="384"/>
       <c r="C144" s="69"/>
-      <c r="D144" s="404"/>
+      <c r="D144" s="384"/>
       <c r="E144" s="67"/>
       <c r="F144" s="44"/>
       <c r="G144" s="44"/>
@@ -14100,9 +14100,9 @@
     </row>
     <row r="145" spans="1:29" ht="15.75" customHeight="1">
       <c r="A145" s="68"/>
-      <c r="B145" s="404"/>
+      <c r="B145" s="384"/>
       <c r="C145" s="69"/>
-      <c r="D145" s="404"/>
+      <c r="D145" s="384"/>
       <c r="E145" s="70"/>
       <c r="F145" s="44"/>
       <c r="G145" s="44"/>
@@ -14131,9 +14131,9 @@
     </row>
     <row r="146" spans="1:29" ht="15.75" customHeight="1">
       <c r="A146" s="68"/>
-      <c r="B146" s="404"/>
+      <c r="B146" s="384"/>
       <c r="C146" s="69"/>
-      <c r="D146" s="404"/>
+      <c r="D146" s="384"/>
       <c r="E146" s="70"/>
       <c r="F146" s="44"/>
       <c r="G146" s="44"/>
@@ -14162,9 +14162,9 @@
     </row>
     <row r="147" spans="1:29" ht="15.75" customHeight="1">
       <c r="A147" s="68"/>
-      <c r="B147" s="404"/>
+      <c r="B147" s="384"/>
       <c r="C147" s="69"/>
-      <c r="D147" s="404"/>
+      <c r="D147" s="384"/>
       <c r="E147" s="70"/>
       <c r="F147" s="44"/>
       <c r="G147" s="44"/>
@@ -14193,9 +14193,9 @@
     </row>
     <row r="148" spans="1:29" ht="15.75" customHeight="1">
       <c r="A148" s="68"/>
-      <c r="B148" s="404"/>
+      <c r="B148" s="384"/>
       <c r="C148" s="69"/>
-      <c r="D148" s="404"/>
+      <c r="D148" s="384"/>
       <c r="E148" s="72"/>
       <c r="F148" s="49"/>
       <c r="G148" s="44"/>
@@ -14224,9 +14224,9 @@
     </row>
     <row r="149" spans="1:29" ht="15.75" customHeight="1">
       <c r="A149" s="68"/>
-      <c r="B149" s="404"/>
+      <c r="B149" s="384"/>
       <c r="C149" s="69"/>
-      <c r="D149" s="404"/>
+      <c r="D149" s="384"/>
       <c r="E149" s="74"/>
       <c r="F149" s="45"/>
       <c r="G149" s="45"/>
@@ -14255,9 +14255,9 @@
     </row>
     <row r="150" spans="1:29" ht="15.75" customHeight="1">
       <c r="A150" s="68"/>
-      <c r="B150" s="404"/>
+      <c r="B150" s="384"/>
       <c r="C150" s="69"/>
-      <c r="D150" s="405"/>
+      <c r="D150" s="385"/>
       <c r="E150" s="67"/>
       <c r="F150" s="44"/>
       <c r="G150" s="44"/>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="151" spans="1:29" ht="15.75" customHeight="1">
       <c r="A151" s="68"/>
-      <c r="B151" s="404"/>
+      <c r="B151" s="384"/>
       <c r="C151" s="69"/>
       <c r="D151" s="75"/>
       <c r="E151" s="67"/>
@@ -14317,9 +14317,9 @@
     </row>
     <row r="152" spans="1:29" ht="15.75" customHeight="1">
       <c r="A152" s="68"/>
-      <c r="B152" s="404"/>
+      <c r="B152" s="384"/>
       <c r="C152" s="69"/>
-      <c r="D152" s="441"/>
+      <c r="D152" s="483"/>
       <c r="E152" s="70"/>
       <c r="F152" s="44"/>
       <c r="G152" s="44"/>
@@ -14348,9 +14348,9 @@
     </row>
     <row r="153" spans="1:29" ht="15.75" customHeight="1">
       <c r="A153" s="68"/>
-      <c r="B153" s="404"/>
+      <c r="B153" s="384"/>
       <c r="C153" s="69"/>
-      <c r="D153" s="419"/>
+      <c r="D153" s="392"/>
       <c r="E153" s="70"/>
       <c r="F153" s="44"/>
       <c r="G153" s="44"/>
@@ -14379,9 +14379,9 @@
     </row>
     <row r="154" spans="1:29" ht="15.75" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="404"/>
+      <c r="B154" s="384"/>
       <c r="C154" s="69"/>
-      <c r="D154" s="419"/>
+      <c r="D154" s="392"/>
       <c r="E154" s="70"/>
       <c r="F154" s="44"/>
       <c r="G154" s="44"/>
@@ -14410,9 +14410,9 @@
     </row>
     <row r="155" spans="1:29" ht="15.75" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="404"/>
+      <c r="B155" s="384"/>
       <c r="C155" s="69"/>
-      <c r="D155" s="419"/>
+      <c r="D155" s="392"/>
       <c r="E155" s="72"/>
       <c r="F155" s="49"/>
       <c r="G155" s="44"/>
@@ -14441,9 +14441,9 @@
     </row>
     <row r="156" spans="1:29" ht="15.75" customHeight="1">
       <c r="A156" s="77"/>
-      <c r="B156" s="404"/>
+      <c r="B156" s="384"/>
       <c r="C156" s="78"/>
-      <c r="D156" s="419"/>
+      <c r="D156" s="392"/>
       <c r="E156" s="79"/>
       <c r="F156" s="80"/>
       <c r="G156" s="80"/>
@@ -14472,9 +14472,9 @@
     </row>
     <row r="157" spans="1:29" ht="15.75" customHeight="1">
       <c r="A157" s="83"/>
-      <c r="B157" s="404"/>
+      <c r="B157" s="384"/>
       <c r="C157" s="78"/>
-      <c r="D157" s="419"/>
+      <c r="D157" s="392"/>
       <c r="E157" s="84"/>
       <c r="F157" s="85"/>
       <c r="G157" s="86"/>
@@ -14503,9 +14503,9 @@
     </row>
     <row r="158" spans="1:29" ht="15.75" customHeight="1">
       <c r="A158" s="83"/>
-      <c r="B158" s="404"/>
+      <c r="B158" s="384"/>
       <c r="C158" s="78"/>
-      <c r="D158" s="419"/>
+      <c r="D158" s="392"/>
       <c r="E158" s="90"/>
       <c r="F158" s="91"/>
       <c r="G158" s="91"/>
@@ -14534,9 +14534,9 @@
     </row>
     <row r="159" spans="1:29" ht="15.75" customHeight="1">
       <c r="A159" s="83"/>
-      <c r="B159" s="404"/>
+      <c r="B159" s="384"/>
       <c r="C159" s="78"/>
-      <c r="D159" s="419"/>
+      <c r="D159" s="392"/>
       <c r="E159" s="90"/>
       <c r="F159" s="91"/>
       <c r="G159" s="91"/>
@@ -14565,9 +14565,9 @@
     </row>
     <row r="160" spans="1:29" ht="15.75" customHeight="1">
       <c r="A160" s="83"/>
-      <c r="B160" s="404"/>
+      <c r="B160" s="384"/>
       <c r="C160" s="78"/>
-      <c r="D160" s="419"/>
+      <c r="D160" s="392"/>
       <c r="E160" s="94"/>
       <c r="F160" s="91"/>
       <c r="G160" s="91"/>
@@ -14596,9 +14596,9 @@
     </row>
     <row r="161" spans="1:29" ht="15.75" customHeight="1">
       <c r="A161" s="83"/>
-      <c r="B161" s="404"/>
+      <c r="B161" s="384"/>
       <c r="C161" s="78"/>
-      <c r="D161" s="419"/>
+      <c r="D161" s="392"/>
       <c r="E161" s="95"/>
       <c r="F161" s="85"/>
       <c r="G161" s="86"/>
@@ -14627,7 +14627,7 @@
     </row>
     <row r="162" spans="1:29" ht="15.75" customHeight="1">
       <c r="A162" s="83"/>
-      <c r="B162" s="404"/>
+      <c r="B162" s="384"/>
       <c r="C162" s="78"/>
       <c r="D162" s="96"/>
       <c r="E162" s="84"/>
@@ -14658,9 +14658,9 @@
     </row>
     <row r="163" spans="1:29" ht="15.75" customHeight="1">
       <c r="A163" s="83"/>
-      <c r="B163" s="404"/>
+      <c r="B163" s="384"/>
       <c r="C163" s="78"/>
-      <c r="D163" s="436"/>
+      <c r="D163" s="430"/>
       <c r="E163" s="97"/>
       <c r="F163" s="85"/>
       <c r="G163" s="86"/>
@@ -14689,9 +14689,9 @@
     </row>
     <row r="164" spans="1:29" ht="15.75" customHeight="1">
       <c r="A164" s="83"/>
-      <c r="B164" s="404"/>
+      <c r="B164" s="384"/>
       <c r="C164" s="78"/>
-      <c r="D164" s="407"/>
+      <c r="D164" s="431"/>
       <c r="E164" s="99"/>
       <c r="F164" s="91"/>
       <c r="G164" s="91"/>
@@ -14720,7 +14720,7 @@
     </row>
     <row r="165" spans="1:29" ht="15.75" customHeight="1">
       <c r="A165" s="83"/>
-      <c r="B165" s="404"/>
+      <c r="B165" s="384"/>
       <c r="C165" s="78"/>
       <c r="D165" s="100"/>
       <c r="E165" s="101"/>
@@ -14751,9 +14751,9 @@
     </row>
     <row r="166" spans="1:29" ht="15.75" customHeight="1">
       <c r="A166" s="83"/>
-      <c r="B166" s="404"/>
+      <c r="B166" s="384"/>
       <c r="C166" s="78"/>
-      <c r="D166" s="442"/>
+      <c r="D166" s="432"/>
       <c r="E166" s="99"/>
       <c r="F166" s="91"/>
       <c r="G166" s="91"/>
@@ -14782,9 +14782,9 @@
     </row>
     <row r="167" spans="1:29" ht="15.75" customHeight="1">
       <c r="A167" s="83"/>
-      <c r="B167" s="404"/>
+      <c r="B167" s="384"/>
       <c r="C167" s="78"/>
-      <c r="D167" s="407"/>
+      <c r="D167" s="431"/>
       <c r="E167" s="97"/>
       <c r="F167" s="91"/>
       <c r="G167" s="91"/>
@@ -14813,9 +14813,9 @@
     </row>
     <row r="168" spans="1:29" ht="15.75" customHeight="1">
       <c r="A168" s="83"/>
-      <c r="B168" s="404"/>
+      <c r="B168" s="384"/>
       <c r="C168" s="78"/>
-      <c r="D168" s="407"/>
+      <c r="D168" s="431"/>
       <c r="E168" s="99"/>
       <c r="F168" s="91"/>
       <c r="G168" s="91"/>
@@ -14844,9 +14844,9 @@
     </row>
     <row r="169" spans="1:29" ht="15.75" customHeight="1">
       <c r="A169" s="83"/>
-      <c r="B169" s="404"/>
+      <c r="B169" s="384"/>
       <c r="C169" s="78"/>
-      <c r="D169" s="407"/>
+      <c r="D169" s="431"/>
       <c r="E169" s="97"/>
       <c r="F169" s="85"/>
       <c r="G169" s="86"/>
@@ -14875,9 +14875,9 @@
     </row>
     <row r="170" spans="1:29" ht="15.75" customHeight="1">
       <c r="A170" s="83"/>
-      <c r="B170" s="404"/>
+      <c r="B170" s="384"/>
       <c r="C170" s="78"/>
-      <c r="D170" s="407"/>
+      <c r="D170" s="431"/>
       <c r="E170" s="102"/>
       <c r="F170" s="103"/>
       <c r="G170" s="93"/>
@@ -14906,9 +14906,9 @@
     </row>
     <row r="171" spans="1:29" ht="15.75" customHeight="1">
       <c r="A171" s="83"/>
-      <c r="B171" s="404"/>
+      <c r="B171" s="384"/>
       <c r="C171" s="78"/>
-      <c r="D171" s="407"/>
+      <c r="D171" s="431"/>
       <c r="E171" s="97"/>
       <c r="F171" s="104"/>
       <c r="G171" s="86"/>
@@ -14937,9 +14937,9 @@
     </row>
     <row r="172" spans="1:29" ht="15.75" customHeight="1">
       <c r="A172" s="83"/>
-      <c r="B172" s="404"/>
+      <c r="B172" s="384"/>
       <c r="C172" s="78"/>
-      <c r="D172" s="410"/>
+      <c r="D172" s="433"/>
       <c r="E172" s="102"/>
       <c r="F172" s="105"/>
       <c r="G172" s="93"/>
@@ -14968,7 +14968,7 @@
     </row>
     <row r="173" spans="1:29" ht="15.75" customHeight="1">
       <c r="A173" s="83"/>
-      <c r="B173" s="404"/>
+      <c r="B173" s="384"/>
       <c r="C173" s="78"/>
       <c r="D173" s="106"/>
       <c r="E173" s="102"/>
@@ -14999,9 +14999,9 @@
     </row>
     <row r="174" spans="1:29" ht="15.75" customHeight="1">
       <c r="A174" s="83"/>
-      <c r="B174" s="404"/>
+      <c r="B174" s="384"/>
       <c r="C174" s="78"/>
-      <c r="D174" s="418"/>
+      <c r="D174" s="473"/>
       <c r="E174" s="107"/>
       <c r="F174" s="108"/>
       <c r="G174" s="93"/>
@@ -15030,9 +15030,9 @@
     </row>
     <row r="175" spans="1:29" ht="15.75" customHeight="1">
       <c r="A175" s="83"/>
-      <c r="B175" s="404"/>
+      <c r="B175" s="384"/>
       <c r="C175" s="78"/>
-      <c r="D175" s="419"/>
+      <c r="D175" s="392"/>
       <c r="E175" s="102"/>
       <c r="F175" s="108"/>
       <c r="G175" s="93"/>
@@ -15061,9 +15061,9 @@
     </row>
     <row r="176" spans="1:29" ht="15.75" customHeight="1">
       <c r="A176" s="83"/>
-      <c r="B176" s="404"/>
+      <c r="B176" s="384"/>
       <c r="C176" s="78"/>
-      <c r="D176" s="419"/>
+      <c r="D176" s="392"/>
       <c r="E176" s="109"/>
       <c r="F176" s="98"/>
       <c r="G176" s="98"/>
@@ -15092,9 +15092,9 @@
     </row>
     <row r="177" spans="1:29" ht="15.75" customHeight="1">
       <c r="A177" s="83"/>
-      <c r="B177" s="404"/>
+      <c r="B177" s="384"/>
       <c r="C177" s="78"/>
-      <c r="D177" s="419"/>
+      <c r="D177" s="392"/>
       <c r="E177" s="109"/>
       <c r="F177" s="98"/>
       <c r="G177" s="98"/>
@@ -15123,9 +15123,9 @@
     </row>
     <row r="178" spans="1:29" ht="15.75" customHeight="1">
       <c r="A178" s="83"/>
-      <c r="B178" s="404"/>
+      <c r="B178" s="384"/>
       <c r="C178" s="78"/>
-      <c r="D178" s="419"/>
+      <c r="D178" s="392"/>
       <c r="E178" s="109"/>
       <c r="F178" s="98"/>
       <c r="G178" s="98"/>
@@ -15154,9 +15154,9 @@
     </row>
     <row r="179" spans="1:29" ht="15.75" customHeight="1">
       <c r="A179" s="83"/>
-      <c r="B179" s="404"/>
+      <c r="B179" s="384"/>
       <c r="C179" s="78"/>
-      <c r="D179" s="419"/>
+      <c r="D179" s="392"/>
       <c r="E179" s="109"/>
       <c r="F179" s="98"/>
       <c r="G179" s="98"/>
@@ -15185,9 +15185,9 @@
     </row>
     <row r="180" spans="1:29" ht="15.75" customHeight="1">
       <c r="A180" s="83"/>
-      <c r="B180" s="404"/>
+      <c r="B180" s="384"/>
       <c r="C180" s="78"/>
-      <c r="D180" s="419"/>
+      <c r="D180" s="392"/>
       <c r="E180" s="109"/>
       <c r="F180" s="98"/>
       <c r="G180" s="98"/>
@@ -15216,9 +15216,9 @@
     </row>
     <row r="181" spans="1:29" ht="15.75" customHeight="1">
       <c r="A181" s="83"/>
-      <c r="B181" s="404"/>
+      <c r="B181" s="384"/>
       <c r="C181" s="78"/>
-      <c r="D181" s="419"/>
+      <c r="D181" s="392"/>
       <c r="E181" s="109"/>
       <c r="F181" s="98"/>
       <c r="G181" s="98"/>
@@ -15247,9 +15247,9 @@
     </row>
     <row r="182" spans="1:29" ht="15.75" customHeight="1">
       <c r="A182" s="83"/>
-      <c r="B182" s="404"/>
+      <c r="B182" s="384"/>
       <c r="C182" s="78"/>
-      <c r="D182" s="420"/>
+      <c r="D182" s="474"/>
       <c r="E182" s="109"/>
       <c r="F182" s="98"/>
       <c r="G182" s="98"/>
@@ -15278,7 +15278,7 @@
     </row>
     <row r="183" spans="1:29" ht="15.75" customHeight="1">
       <c r="A183" s="83"/>
-      <c r="B183" s="404"/>
+      <c r="B183" s="384"/>
       <c r="C183" s="110"/>
       <c r="D183" s="111"/>
       <c r="E183" s="109"/>
@@ -15309,7 +15309,7 @@
     </row>
     <row r="184" spans="1:29" ht="15.75" customHeight="1">
       <c r="A184" s="83"/>
-      <c r="B184" s="404"/>
+      <c r="B184" s="384"/>
       <c r="C184" s="112"/>
       <c r="D184" s="111"/>
       <c r="E184" s="109"/>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="185" spans="1:29" ht="15.75" customHeight="1">
       <c r="A185" s="83"/>
-      <c r="B185" s="404"/>
+      <c r="B185" s="384"/>
       <c r="C185" s="112"/>
       <c r="D185" s="113"/>
       <c r="E185" s="109"/>
@@ -15371,9 +15371,9 @@
     </row>
     <row r="186" spans="1:29" ht="15.75" customHeight="1">
       <c r="A186" s="83"/>
-      <c r="B186" s="404"/>
+      <c r="B186" s="384"/>
       <c r="C186" s="112"/>
-      <c r="D186" s="421"/>
+      <c r="D186" s="475"/>
       <c r="E186" s="115"/>
       <c r="F186" s="98"/>
       <c r="G186" s="98"/>
@@ -15402,9 +15402,9 @@
     </row>
     <row r="187" spans="1:29" ht="15.75" customHeight="1">
       <c r="A187" s="83"/>
-      <c r="B187" s="404"/>
+      <c r="B187" s="384"/>
       <c r="C187" s="112"/>
-      <c r="D187" s="410"/>
+      <c r="D187" s="433"/>
       <c r="E187" s="115"/>
       <c r="F187" s="98"/>
       <c r="G187" s="98"/>
@@ -15433,7 +15433,7 @@
     </row>
     <row r="188" spans="1:29" ht="15.75" customHeight="1">
       <c r="A188" s="83"/>
-      <c r="B188" s="404"/>
+      <c r="B188" s="384"/>
       <c r="C188" s="112"/>
       <c r="D188" s="116"/>
       <c r="E188" s="109"/>
@@ -15464,7 +15464,7 @@
     </row>
     <row r="189" spans="1:29" ht="15.75" customHeight="1">
       <c r="A189" s="83"/>
-      <c r="B189" s="404"/>
+      <c r="B189" s="384"/>
       <c r="C189" s="112"/>
       <c r="D189" s="117"/>
       <c r="E189" s="109"/>
@@ -15495,7 +15495,7 @@
     </row>
     <row r="190" spans="1:29" ht="15.75" customHeight="1">
       <c r="A190" s="83"/>
-      <c r="B190" s="404"/>
+      <c r="B190" s="384"/>
       <c r="C190" s="112"/>
       <c r="D190" s="117"/>
       <c r="E190" s="118"/>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="191" spans="1:29" ht="15.75" customHeight="1">
       <c r="A191" s="83"/>
-      <c r="B191" s="404"/>
+      <c r="B191" s="384"/>
       <c r="C191" s="112"/>
       <c r="D191" s="117"/>
       <c r="E191" s="109"/>
@@ -15557,7 +15557,7 @@
     </row>
     <row r="192" spans="1:29" ht="15.75" customHeight="1">
       <c r="A192" s="83"/>
-      <c r="B192" s="404"/>
+      <c r="B192" s="384"/>
       <c r="C192" s="112"/>
       <c r="D192" s="117"/>
       <c r="E192" s="109"/>
@@ -15588,7 +15588,7 @@
     </row>
     <row r="193" spans="1:29" ht="15.75" customHeight="1">
       <c r="A193" s="83"/>
-      <c r="B193" s="404"/>
+      <c r="B193" s="384"/>
       <c r="C193" s="112"/>
       <c r="D193" s="117"/>
       <c r="E193" s="109"/>
@@ -15619,7 +15619,7 @@
     </row>
     <row r="194" spans="1:29" ht="15.75" customHeight="1">
       <c r="A194" s="83"/>
-      <c r="B194" s="404"/>
+      <c r="B194" s="384"/>
       <c r="C194" s="112"/>
       <c r="D194" s="117"/>
       <c r="E194" s="109"/>
@@ -15650,7 +15650,7 @@
     </row>
     <row r="195" spans="1:29" ht="15.75" customHeight="1">
       <c r="A195" s="83"/>
-      <c r="B195" s="404"/>
+      <c r="B195" s="384"/>
       <c r="C195" s="112"/>
       <c r="D195" s="117"/>
       <c r="E195" s="118"/>
@@ -15681,7 +15681,7 @@
     </row>
     <row r="196" spans="1:29" ht="15.75" customHeight="1">
       <c r="A196" s="83"/>
-      <c r="B196" s="404"/>
+      <c r="B196" s="384"/>
       <c r="C196" s="112"/>
       <c r="D196" s="117"/>
       <c r="E196" s="118"/>
@@ -15712,7 +15712,7 @@
     </row>
     <row r="197" spans="1:29" ht="15.75" customHeight="1">
       <c r="A197" s="83"/>
-      <c r="B197" s="404"/>
+      <c r="B197" s="384"/>
       <c r="C197" s="112"/>
       <c r="D197" s="117"/>
       <c r="E197" s="118"/>
@@ -15743,7 +15743,7 @@
     </row>
     <row r="198" spans="1:29" ht="15.75" customHeight="1">
       <c r="A198" s="83"/>
-      <c r="B198" s="404"/>
+      <c r="B198" s="384"/>
       <c r="C198" s="112"/>
       <c r="D198" s="117"/>
       <c r="E198" s="109"/>
@@ -15774,7 +15774,7 @@
     </row>
     <row r="199" spans="1:29" ht="15.75" customHeight="1">
       <c r="A199" s="83"/>
-      <c r="B199" s="404"/>
+      <c r="B199" s="384"/>
       <c r="C199" s="112"/>
       <c r="D199" s="117"/>
       <c r="E199" s="109"/>
@@ -15805,7 +15805,7 @@
     </row>
     <row r="200" spans="1:29" ht="15.75" customHeight="1">
       <c r="A200" s="83"/>
-      <c r="B200" s="404"/>
+      <c r="B200" s="384"/>
       <c r="C200" s="112"/>
       <c r="D200" s="117"/>
       <c r="E200" s="109"/>
@@ -15836,7 +15836,7 @@
     </row>
     <row r="201" spans="1:29" ht="15.75" customHeight="1">
       <c r="A201" s="83"/>
-      <c r="B201" s="404"/>
+      <c r="B201" s="384"/>
       <c r="C201" s="112"/>
       <c r="D201" s="117"/>
       <c r="E201" s="109"/>
@@ -15867,7 +15867,7 @@
     </row>
     <row r="202" spans="1:29" ht="15.75" customHeight="1">
       <c r="A202" s="83"/>
-      <c r="B202" s="404"/>
+      <c r="B202" s="384"/>
       <c r="C202" s="112"/>
       <c r="D202" s="117"/>
       <c r="E202" s="109"/>
@@ -15898,7 +15898,7 @@
     </row>
     <row r="203" spans="1:29" ht="15.75" customHeight="1">
       <c r="A203" s="83"/>
-      <c r="B203" s="404"/>
+      <c r="B203" s="384"/>
       <c r="C203" s="112"/>
       <c r="D203" s="117"/>
       <c r="E203" s="109"/>
@@ -15929,7 +15929,7 @@
     </row>
     <row r="204" spans="1:29" ht="15.75" customHeight="1">
       <c r="A204" s="123"/>
-      <c r="B204" s="404"/>
+      <c r="B204" s="384"/>
       <c r="C204" s="112"/>
       <c r="D204" s="124"/>
       <c r="E204" s="125"/>
@@ -15960,7 +15960,7 @@
     </row>
     <row r="205" spans="1:29" ht="15.75" customHeight="1">
       <c r="A205" s="123"/>
-      <c r="B205" s="404"/>
+      <c r="B205" s="384"/>
       <c r="C205" s="112"/>
       <c r="D205" s="126"/>
       <c r="E205" s="109"/>
@@ -15991,7 +15991,7 @@
     </row>
     <row r="206" spans="1:29" ht="15.75" customHeight="1">
       <c r="A206" s="123"/>
-      <c r="B206" s="404"/>
+      <c r="B206" s="384"/>
       <c r="C206" s="112"/>
       <c r="D206" s="126"/>
       <c r="E206" s="109"/>
@@ -16022,7 +16022,7 @@
     </row>
     <row r="207" spans="1:29" ht="15.75" customHeight="1">
       <c r="A207" s="123"/>
-      <c r="B207" s="404"/>
+      <c r="B207" s="384"/>
       <c r="C207" s="112"/>
       <c r="D207" s="126"/>
       <c r="E207" s="127"/>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="208" spans="1:29" ht="15.75" customHeight="1">
       <c r="A208" s="123"/>
-      <c r="B208" s="404"/>
+      <c r="B208" s="384"/>
       <c r="C208" s="112"/>
       <c r="D208" s="126"/>
       <c r="E208" s="128"/>
@@ -16084,7 +16084,7 @@
     </row>
     <row r="209" spans="1:29" ht="15.75" customHeight="1">
       <c r="A209" s="123"/>
-      <c r="B209" s="404"/>
+      <c r="B209" s="384"/>
       <c r="C209" s="112"/>
       <c r="D209" s="126"/>
       <c r="E209" s="128"/>
@@ -16115,7 +16115,7 @@
     </row>
     <row r="210" spans="1:29" ht="15.75" customHeight="1">
       <c r="A210" s="123"/>
-      <c r="B210" s="404"/>
+      <c r="B210" s="384"/>
       <c r="C210" s="112"/>
       <c r="D210" s="126"/>
       <c r="E210" s="128"/>
@@ -16146,7 +16146,7 @@
     </row>
     <row r="211" spans="1:29" ht="15.75" customHeight="1">
       <c r="A211" s="123"/>
-      <c r="B211" s="404"/>
+      <c r="B211" s="384"/>
       <c r="C211" s="112"/>
       <c r="D211" s="126"/>
       <c r="E211" s="128"/>
@@ -16177,7 +16177,7 @@
     </row>
     <row r="212" spans="1:29" ht="15.75" customHeight="1">
       <c r="A212" s="123"/>
-      <c r="B212" s="404"/>
+      <c r="B212" s="384"/>
       <c r="C212" s="112"/>
       <c r="D212" s="126"/>
       <c r="E212" s="109"/>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="213" spans="1:29" ht="15.75" customHeight="1">
       <c r="A213" s="123"/>
-      <c r="B213" s="404"/>
+      <c r="B213" s="384"/>
       <c r="C213" s="112"/>
       <c r="D213" s="126"/>
       <c r="E213" s="109"/>
@@ -16239,7 +16239,7 @@
     </row>
     <row r="214" spans="1:29" ht="15.75" customHeight="1">
       <c r="A214" s="123"/>
-      <c r="B214" s="404"/>
+      <c r="B214" s="384"/>
       <c r="C214" s="112"/>
       <c r="D214" s="126"/>
       <c r="E214" s="109"/>
@@ -16270,7 +16270,7 @@
     </row>
     <row r="215" spans="1:29" ht="15.75" customHeight="1">
       <c r="A215" s="123"/>
-      <c r="B215" s="404"/>
+      <c r="B215" s="384"/>
       <c r="C215" s="112"/>
       <c r="D215" s="126"/>
       <c r="E215" s="109"/>
@@ -16301,7 +16301,7 @@
     </row>
     <row r="216" spans="1:29" ht="15.75" customHeight="1">
       <c r="A216" s="123"/>
-      <c r="B216" s="404"/>
+      <c r="B216" s="384"/>
       <c r="C216" s="112"/>
       <c r="D216" s="126"/>
       <c r="E216" s="125"/>
@@ -16332,7 +16332,7 @@
     </row>
     <row r="217" spans="1:29" ht="15.75" customHeight="1">
       <c r="A217" s="123"/>
-      <c r="B217" s="404"/>
+      <c r="B217" s="384"/>
       <c r="C217" s="112"/>
       <c r="D217" s="129"/>
       <c r="E217" s="130"/>
@@ -16363,7 +16363,7 @@
     </row>
     <row r="218" spans="1:29" ht="15.75" customHeight="1">
       <c r="A218" s="123"/>
-      <c r="B218" s="404"/>
+      <c r="B218" s="384"/>
       <c r="C218" s="112"/>
       <c r="D218" s="131"/>
       <c r="E218" s="125"/>
@@ -16394,9 +16394,9 @@
     </row>
     <row r="219" spans="1:29" ht="15.75" customHeight="1">
       <c r="A219" s="123"/>
-      <c r="B219" s="404"/>
+      <c r="B219" s="384"/>
       <c r="C219" s="112"/>
-      <c r="D219" s="406"/>
+      <c r="D219" s="464"/>
       <c r="E219" s="109"/>
       <c r="F219" s="98"/>
       <c r="G219" s="98"/>
@@ -16405,7 +16405,7 @@
       <c r="J219" s="98"/>
       <c r="K219" s="98"/>
       <c r="L219" s="89"/>
-      <c r="M219" s="409"/>
+      <c r="M219" s="456"/>
       <c r="N219" s="82"/>
       <c r="O219" s="82"/>
       <c r="P219" s="82"/>
@@ -16425,9 +16425,9 @@
     </row>
     <row r="220" spans="1:29" ht="15.75" customHeight="1">
       <c r="A220" s="83"/>
-      <c r="B220" s="404"/>
+      <c r="B220" s="384"/>
       <c r="C220" s="112"/>
-      <c r="D220" s="407"/>
+      <c r="D220" s="431"/>
       <c r="E220" s="109"/>
       <c r="F220" s="98"/>
       <c r="G220" s="98"/>
@@ -16436,7 +16436,7 @@
       <c r="J220" s="98"/>
       <c r="K220" s="98"/>
       <c r="L220" s="89"/>
-      <c r="M220" s="407"/>
+      <c r="M220" s="431"/>
       <c r="N220" s="82"/>
       <c r="O220" s="82"/>
       <c r="P220" s="82"/>
@@ -16456,9 +16456,9 @@
     </row>
     <row r="221" spans="1:29" ht="15.75" customHeight="1">
       <c r="A221" s="83"/>
-      <c r="B221" s="404"/>
+      <c r="B221" s="384"/>
       <c r="C221" s="112"/>
-      <c r="D221" s="407"/>
+      <c r="D221" s="431"/>
       <c r="E221" s="127"/>
       <c r="F221" s="98"/>
       <c r="G221" s="98"/>
@@ -16467,7 +16467,7 @@
       <c r="J221" s="98"/>
       <c r="K221" s="98"/>
       <c r="L221" s="89"/>
-      <c r="M221" s="407"/>
+      <c r="M221" s="431"/>
       <c r="N221" s="82"/>
       <c r="O221" s="82"/>
       <c r="P221" s="82"/>
@@ -16487,9 +16487,9 @@
     </row>
     <row r="222" spans="1:29" ht="15.75" customHeight="1">
       <c r="A222" s="83"/>
-      <c r="B222" s="404"/>
+      <c r="B222" s="384"/>
       <c r="C222" s="112"/>
-      <c r="D222" s="407"/>
+      <c r="D222" s="431"/>
       <c r="E222" s="128"/>
       <c r="F222" s="98"/>
       <c r="G222" s="98"/>
@@ -16498,7 +16498,7 @@
       <c r="J222" s="98"/>
       <c r="K222" s="98"/>
       <c r="L222" s="89"/>
-      <c r="M222" s="407"/>
+      <c r="M222" s="431"/>
       <c r="N222" s="82"/>
       <c r="O222" s="82"/>
       <c r="P222" s="82"/>
@@ -16518,9 +16518,9 @@
     </row>
     <row r="223" spans="1:29" ht="15.75" customHeight="1">
       <c r="A223" s="83"/>
-      <c r="B223" s="404"/>
+      <c r="B223" s="384"/>
       <c r="C223" s="112"/>
-      <c r="D223" s="407"/>
+      <c r="D223" s="431"/>
       <c r="E223" s="128"/>
       <c r="F223" s="98"/>
       <c r="G223" s="98"/>
@@ -16529,7 +16529,7 @@
       <c r="J223" s="98"/>
       <c r="K223" s="98"/>
       <c r="L223" s="89"/>
-      <c r="M223" s="407"/>
+      <c r="M223" s="431"/>
       <c r="N223" s="82"/>
       <c r="O223" s="82"/>
       <c r="P223" s="82"/>
@@ -16549,9 +16549,9 @@
     </row>
     <row r="224" spans="1:29" ht="15.75" customHeight="1">
       <c r="A224" s="83"/>
-      <c r="B224" s="404"/>
+      <c r="B224" s="384"/>
       <c r="C224" s="112"/>
-      <c r="D224" s="407"/>
+      <c r="D224" s="431"/>
       <c r="E224" s="128"/>
       <c r="F224" s="98"/>
       <c r="G224" s="98"/>
@@ -16560,7 +16560,7 @@
       <c r="J224" s="98"/>
       <c r="K224" s="98"/>
       <c r="L224" s="89"/>
-      <c r="M224" s="407"/>
+      <c r="M224" s="431"/>
       <c r="N224" s="82"/>
       <c r="O224" s="82"/>
       <c r="P224" s="82"/>
@@ -16580,9 +16580,9 @@
     </row>
     <row r="225" spans="1:29" ht="15.75" customHeight="1">
       <c r="A225" s="83"/>
-      <c r="B225" s="404"/>
+      <c r="B225" s="384"/>
       <c r="C225" s="112"/>
-      <c r="D225" s="407"/>
+      <c r="D225" s="431"/>
       <c r="E225" s="128"/>
       <c r="F225" s="98"/>
       <c r="G225" s="98"/>
@@ -16591,7 +16591,7 @@
       <c r="J225" s="98"/>
       <c r="K225" s="98"/>
       <c r="L225" s="89"/>
-      <c r="M225" s="407"/>
+      <c r="M225" s="431"/>
       <c r="N225" s="82"/>
       <c r="O225" s="82"/>
       <c r="P225" s="82"/>
@@ -16611,9 +16611,9 @@
     </row>
     <row r="226" spans="1:29" ht="15.75" customHeight="1">
       <c r="A226" s="83"/>
-      <c r="B226" s="404"/>
+      <c r="B226" s="384"/>
       <c r="C226" s="112"/>
-      <c r="D226" s="407"/>
+      <c r="D226" s="431"/>
       <c r="E226" s="109"/>
       <c r="F226" s="98"/>
       <c r="G226" s="98"/>
@@ -16622,7 +16622,7 @@
       <c r="J226" s="98"/>
       <c r="K226" s="98"/>
       <c r="L226" s="89"/>
-      <c r="M226" s="410"/>
+      <c r="M226" s="433"/>
       <c r="N226" s="82"/>
       <c r="O226" s="82"/>
       <c r="P226" s="82"/>
@@ -16642,9 +16642,9 @@
     </row>
     <row r="227" spans="1:29" ht="15.75" customHeight="1">
       <c r="A227" s="83"/>
-      <c r="B227" s="404"/>
+      <c r="B227" s="384"/>
       <c r="C227" s="112"/>
-      <c r="D227" s="407"/>
+      <c r="D227" s="431"/>
       <c r="E227" s="109"/>
       <c r="F227" s="98"/>
       <c r="G227" s="98"/>
@@ -16673,9 +16673,9 @@
     </row>
     <row r="228" spans="1:29" ht="15.75" customHeight="1">
       <c r="A228" s="83"/>
-      <c r="B228" s="404"/>
+      <c r="B228" s="384"/>
       <c r="C228" s="112"/>
-      <c r="D228" s="407"/>
+      <c r="D228" s="431"/>
       <c r="E228" s="109"/>
       <c r="F228" s="98"/>
       <c r="G228" s="98"/>
@@ -16704,9 +16704,9 @@
     </row>
     <row r="229" spans="1:29" ht="15.75" customHeight="1">
       <c r="A229" s="83"/>
-      <c r="B229" s="405"/>
+      <c r="B229" s="385"/>
       <c r="C229" s="112"/>
-      <c r="D229" s="408"/>
+      <c r="D229" s="465"/>
       <c r="E229" s="109"/>
       <c r="F229" s="98"/>
       <c r="G229" s="98"/>
@@ -16770,7 +16770,7 @@
       <c r="C231" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="D231" s="433"/>
+      <c r="D231" s="455"/>
       <c r="E231" s="109"/>
       <c r="F231" s="98"/>
       <c r="G231" s="122"/>
@@ -16801,7 +16801,7 @@
       <c r="A232" s="133"/>
       <c r="B232" s="131"/>
       <c r="C232" s="138"/>
-      <c r="D232" s="407"/>
+      <c r="D232" s="431"/>
       <c r="E232" s="109"/>
       <c r="F232" s="98"/>
       <c r="G232" s="122"/>
@@ -16832,7 +16832,7 @@
       <c r="A233" s="133"/>
       <c r="B233" s="131"/>
       <c r="C233" s="138"/>
-      <c r="D233" s="407"/>
+      <c r="D233" s="431"/>
       <c r="E233" s="109"/>
       <c r="F233" s="98"/>
       <c r="G233" s="122"/>
@@ -16863,7 +16863,7 @@
       <c r="A234" s="133"/>
       <c r="B234" s="131"/>
       <c r="C234" s="131"/>
-      <c r="D234" s="407"/>
+      <c r="D234" s="431"/>
       <c r="E234" s="118"/>
       <c r="F234" s="98"/>
       <c r="G234" s="122"/>
@@ -16894,7 +16894,7 @@
       <c r="A235" s="133"/>
       <c r="B235" s="136"/>
       <c r="C235" s="131"/>
-      <c r="D235" s="407"/>
+      <c r="D235" s="431"/>
       <c r="E235" s="118"/>
       <c r="F235" s="98"/>
       <c r="G235" s="122"/>
@@ -16925,7 +16925,7 @@
       <c r="A236" s="133"/>
       <c r="B236" s="136"/>
       <c r="C236" s="131"/>
-      <c r="D236" s="407"/>
+      <c r="D236" s="431"/>
       <c r="E236" s="118"/>
       <c r="F236" s="98"/>
       <c r="G236" s="122"/>
@@ -16956,7 +16956,7 @@
       <c r="A237" s="133"/>
       <c r="B237" s="136"/>
       <c r="C237" s="131"/>
-      <c r="D237" s="407"/>
+      <c r="D237" s="431"/>
       <c r="E237" s="109"/>
       <c r="F237" s="98"/>
       <c r="G237" s="122"/>
@@ -16987,7 +16987,7 @@
       <c r="A238" s="133"/>
       <c r="B238" s="136"/>
       <c r="C238" s="131"/>
-      <c r="D238" s="407"/>
+      <c r="D238" s="431"/>
       <c r="E238" s="109"/>
       <c r="F238" s="98"/>
       <c r="G238" s="122"/>
@@ -17018,7 +17018,7 @@
       <c r="A239" s="133"/>
       <c r="B239" s="136"/>
       <c r="C239" s="136"/>
-      <c r="D239" s="410"/>
+      <c r="D239" s="433"/>
       <c r="E239" s="109"/>
       <c r="F239" s="98"/>
       <c r="G239" s="122"/>
@@ -18358,8 +18358,8 @@
       <c r="H282" s="157"/>
       <c r="I282" s="157"/>
       <c r="J282" s="157"/>
-      <c r="K282" s="434"/>
-      <c r="L282" s="409"/>
+      <c r="K282" s="451"/>
+      <c r="L282" s="456"/>
       <c r="M282" s="152"/>
       <c r="N282" s="82"/>
       <c r="O282" s="82"/>
@@ -18389,8 +18389,8 @@
       <c r="H283" s="159"/>
       <c r="I283" s="159"/>
       <c r="J283" s="159"/>
-      <c r="K283" s="407"/>
-      <c r="L283" s="407"/>
+      <c r="K283" s="431"/>
+      <c r="L283" s="431"/>
       <c r="M283" s="152"/>
       <c r="N283" s="82"/>
       <c r="O283" s="82"/>
@@ -18420,8 +18420,8 @@
       <c r="H284" s="80"/>
       <c r="I284" s="80"/>
       <c r="J284" s="80"/>
-      <c r="K284" s="410"/>
-      <c r="L284" s="410"/>
+      <c r="K284" s="433"/>
+      <c r="L284" s="433"/>
       <c r="M284" s="152"/>
       <c r="N284" s="82"/>
       <c r="O284" s="82"/>
@@ -18629,9 +18629,9 @@
     <row r="291" spans="1:29" ht="15.75" customHeight="1">
       <c r="A291" s="133"/>
       <c r="B291" s="145"/>
-      <c r="C291" s="435"/>
+      <c r="C291" s="452"/>
       <c r="D291" s="131"/>
-      <c r="E291" s="436"/>
+      <c r="E291" s="430"/>
       <c r="F291" s="91"/>
       <c r="G291" s="91"/>
       <c r="H291" s="91"/>
@@ -18660,9 +18660,9 @@
     <row r="292" spans="1:29" ht="15.75" customHeight="1">
       <c r="A292" s="133"/>
       <c r="B292" s="145"/>
-      <c r="C292" s="407"/>
+      <c r="C292" s="431"/>
       <c r="D292" s="131"/>
-      <c r="E292" s="407"/>
+      <c r="E292" s="431"/>
       <c r="F292" s="91"/>
       <c r="G292" s="91"/>
       <c r="H292" s="91"/>
@@ -18691,9 +18691,9 @@
     <row r="293" spans="1:29" ht="15.75" customHeight="1">
       <c r="A293" s="133"/>
       <c r="B293" s="145"/>
-      <c r="C293" s="407"/>
+      <c r="C293" s="431"/>
       <c r="D293" s="131"/>
-      <c r="E293" s="410"/>
+      <c r="E293" s="433"/>
       <c r="F293" s="91"/>
       <c r="G293" s="91"/>
       <c r="H293" s="91"/>
@@ -18722,7 +18722,7 @@
     <row r="294" spans="1:29" ht="15.75" customHeight="1">
       <c r="A294" s="133"/>
       <c r="B294" s="145"/>
-      <c r="C294" s="407"/>
+      <c r="C294" s="431"/>
       <c r="D294" s="131"/>
       <c r="E294" s="99"/>
       <c r="F294" s="91"/>
@@ -18753,7 +18753,7 @@
     <row r="295" spans="1:29" ht="15.75" customHeight="1">
       <c r="A295" s="133"/>
       <c r="B295" s="145"/>
-      <c r="C295" s="407"/>
+      <c r="C295" s="431"/>
       <c r="D295" s="131"/>
       <c r="E295" s="99"/>
       <c r="F295" s="91"/>
@@ -18784,7 +18784,7 @@
     <row r="296" spans="1:29" ht="15.75" customHeight="1">
       <c r="A296" s="133"/>
       <c r="B296" s="145"/>
-      <c r="C296" s="407"/>
+      <c r="C296" s="431"/>
       <c r="D296" s="131"/>
       <c r="E296" s="99"/>
       <c r="F296" s="155"/>
@@ -18815,7 +18815,7 @@
     <row r="297" spans="1:29" ht="15.75" customHeight="1">
       <c r="A297" s="133"/>
       <c r="B297" s="145"/>
-      <c r="C297" s="410"/>
+      <c r="C297" s="433"/>
       <c r="D297" s="131"/>
       <c r="E297" s="99"/>
       <c r="F297" s="91"/>
@@ -18846,7 +18846,7 @@
     <row r="298" spans="1:29" ht="15.75" customHeight="1">
       <c r="A298" s="133"/>
       <c r="B298" s="145"/>
-      <c r="C298" s="437"/>
+      <c r="C298" s="450"/>
       <c r="D298" s="143"/>
       <c r="E298" s="99"/>
       <c r="F298" s="155"/>
@@ -18877,7 +18877,7 @@
     <row r="299" spans="1:29" ht="15.75" customHeight="1">
       <c r="A299" s="133"/>
       <c r="B299" s="145"/>
-      <c r="C299" s="410"/>
+      <c r="C299" s="433"/>
       <c r="D299" s="163"/>
       <c r="E299" s="99"/>
       <c r="F299" s="155"/>
@@ -18939,7 +18939,7 @@
     <row r="301" spans="1:29" ht="30" customHeight="1">
       <c r="A301" s="133"/>
       <c r="B301" s="145"/>
-      <c r="C301" s="437"/>
+      <c r="C301" s="450"/>
       <c r="D301" s="143"/>
       <c r="E301" s="99"/>
       <c r="F301" s="91"/>
@@ -18970,7 +18970,7 @@
     <row r="302" spans="1:29" ht="15.75" customHeight="1">
       <c r="A302" s="133"/>
       <c r="B302" s="145"/>
-      <c r="C302" s="407"/>
+      <c r="C302" s="431"/>
       <c r="D302" s="144"/>
       <c r="E302" s="99"/>
       <c r="F302" s="91"/>
@@ -19001,7 +19001,7 @@
     <row r="303" spans="1:29" ht="15.75" customHeight="1">
       <c r="A303" s="133"/>
       <c r="B303" s="145"/>
-      <c r="C303" s="407"/>
+      <c r="C303" s="431"/>
       <c r="D303" s="144"/>
       <c r="E303" s="99"/>
       <c r="F303" s="91"/>
@@ -19032,7 +19032,7 @@
     <row r="304" spans="1:29" ht="15.75" customHeight="1">
       <c r="A304" s="133"/>
       <c r="B304" s="145"/>
-      <c r="C304" s="407"/>
+      <c r="C304" s="431"/>
       <c r="D304" s="144"/>
       <c r="E304" s="99"/>
       <c r="F304" s="155"/>
@@ -19063,7 +19063,7 @@
     <row r="305" spans="1:29" ht="15.75" customHeight="1">
       <c r="A305" s="133"/>
       <c r="B305" s="145"/>
-      <c r="C305" s="410"/>
+      <c r="C305" s="433"/>
       <c r="D305" s="144"/>
       <c r="E305" s="165"/>
       <c r="F305" s="91"/>
@@ -19443,7 +19443,7 @@
       <c r="H317" s="155"/>
       <c r="I317" s="155"/>
       <c r="J317" s="155"/>
-      <c r="K317" s="438"/>
+      <c r="K317" s="449"/>
       <c r="L317" s="89"/>
       <c r="M317" s="120"/>
       <c r="N317" s="82"/>
@@ -19474,7 +19474,7 @@
       <c r="H318" s="155"/>
       <c r="I318" s="155"/>
       <c r="J318" s="155"/>
-      <c r="K318" s="410"/>
+      <c r="K318" s="433"/>
       <c r="L318" s="89"/>
       <c r="M318" s="120"/>
       <c r="N318" s="82"/>
@@ -19559,7 +19559,7 @@
     <row r="321" spans="1:29" ht="15.75" customHeight="1">
       <c r="A321" s="133"/>
       <c r="B321" s="145"/>
-      <c r="C321" s="437"/>
+      <c r="C321" s="450"/>
       <c r="D321" s="143"/>
       <c r="E321" s="99"/>
       <c r="F321" s="155"/>
@@ -19567,7 +19567,7 @@
       <c r="H321" s="155"/>
       <c r="I321" s="155"/>
       <c r="J321" s="155"/>
-      <c r="K321" s="434"/>
+      <c r="K321" s="451"/>
       <c r="L321" s="89"/>
       <c r="M321" s="120"/>
       <c r="N321" s="82"/>
@@ -19590,7 +19590,7 @@
     <row r="322" spans="1:29" ht="15.75" customHeight="1">
       <c r="A322" s="133"/>
       <c r="B322" s="145"/>
-      <c r="C322" s="410"/>
+      <c r="C322" s="433"/>
       <c r="D322" s="163"/>
       <c r="E322" s="99"/>
       <c r="F322" s="155"/>
@@ -19598,7 +19598,7 @@
       <c r="H322" s="155"/>
       <c r="I322" s="155"/>
       <c r="J322" s="155"/>
-      <c r="K322" s="410"/>
+      <c r="K322" s="433"/>
       <c r="L322" s="89"/>
       <c r="M322" s="120"/>
       <c r="N322" s="82"/>
@@ -19621,7 +19621,7 @@
     <row r="323" spans="1:29" ht="15.75" customHeight="1">
       <c r="A323" s="133"/>
       <c r="B323" s="145"/>
-      <c r="C323" s="435"/>
+      <c r="C323" s="452"/>
       <c r="D323" s="156"/>
       <c r="E323" s="118"/>
       <c r="F323" s="98"/>
@@ -19652,7 +19652,7 @@
     <row r="324" spans="1:29" ht="15.75" customHeight="1">
       <c r="A324" s="133"/>
       <c r="B324" s="145"/>
-      <c r="C324" s="410"/>
+      <c r="C324" s="433"/>
       <c r="D324" s="116"/>
       <c r="E324" s="118"/>
       <c r="F324" s="98"/>
@@ -19714,7 +19714,7 @@
     <row r="326" spans="1:29" ht="15.75" customHeight="1">
       <c r="A326" s="133"/>
       <c r="B326" s="145"/>
-      <c r="C326" s="437"/>
+      <c r="C326" s="450"/>
       <c r="D326" s="143"/>
       <c r="E326" s="118"/>
       <c r="F326" s="98"/>
@@ -19745,7 +19745,7 @@
     <row r="327" spans="1:29" ht="15.75" customHeight="1">
       <c r="A327" s="133"/>
       <c r="B327" s="145"/>
-      <c r="C327" s="407"/>
+      <c r="C327" s="431"/>
       <c r="D327" s="144"/>
       <c r="E327" s="118"/>
       <c r="F327" s="98"/>
@@ -19776,7 +19776,7 @@
     <row r="328" spans="1:29" ht="15.75" customHeight="1">
       <c r="A328" s="133"/>
       <c r="B328" s="145"/>
-      <c r="C328" s="410"/>
+      <c r="C328" s="433"/>
       <c r="D328" s="163"/>
       <c r="E328" s="118"/>
       <c r="F328" s="98"/>
@@ -19961,10 +19961,10 @@
     </row>
     <row r="334" spans="1:29" ht="15.75" customHeight="1">
       <c r="A334" s="140"/>
-      <c r="B334" s="439"/>
-      <c r="C334" s="435"/>
+      <c r="B334" s="453"/>
+      <c r="C334" s="452"/>
       <c r="D334" s="131"/>
-      <c r="E334" s="435"/>
+      <c r="E334" s="452"/>
       <c r="F334" s="91"/>
       <c r="G334" s="91"/>
       <c r="H334" s="91"/>
@@ -19992,10 +19992,10 @@
     </row>
     <row r="335" spans="1:29" ht="15.75" customHeight="1">
       <c r="A335" s="140"/>
-      <c r="B335" s="407"/>
-      <c r="C335" s="407"/>
+      <c r="B335" s="431"/>
+      <c r="C335" s="431"/>
       <c r="D335" s="131"/>
-      <c r="E335" s="407"/>
+      <c r="E335" s="431"/>
       <c r="F335" s="91"/>
       <c r="G335" s="91"/>
       <c r="H335" s="91"/>
@@ -20023,10 +20023,10 @@
     </row>
     <row r="336" spans="1:29" ht="15.75" customHeight="1">
       <c r="A336" s="140"/>
-      <c r="B336" s="407"/>
-      <c r="C336" s="407"/>
+      <c r="B336" s="431"/>
+      <c r="C336" s="431"/>
       <c r="D336" s="131"/>
-      <c r="E336" s="407"/>
+      <c r="E336" s="431"/>
       <c r="F336" s="91"/>
       <c r="G336" s="91"/>
       <c r="H336" s="91"/>
@@ -20054,10 +20054,10 @@
     </row>
     <row r="337" spans="1:29" ht="15.75" customHeight="1">
       <c r="A337" s="140"/>
-      <c r="B337" s="407"/>
-      <c r="C337" s="407"/>
+      <c r="B337" s="431"/>
+      <c r="C337" s="431"/>
       <c r="D337" s="131"/>
-      <c r="E337" s="407"/>
+      <c r="E337" s="431"/>
       <c r="F337" s="91"/>
       <c r="G337" s="91"/>
       <c r="H337" s="91"/>
@@ -20085,10 +20085,10 @@
     </row>
     <row r="338" spans="1:29" ht="15.75" customHeight="1">
       <c r="A338" s="140"/>
-      <c r="B338" s="407"/>
-      <c r="C338" s="407"/>
+      <c r="B338" s="431"/>
+      <c r="C338" s="431"/>
       <c r="D338" s="131"/>
-      <c r="E338" s="407"/>
+      <c r="E338" s="431"/>
       <c r="F338" s="91"/>
       <c r="G338" s="91"/>
       <c r="H338" s="91"/>
@@ -20116,10 +20116,10 @@
     </row>
     <row r="339" spans="1:29" ht="15.75" customHeight="1">
       <c r="A339" s="140"/>
-      <c r="B339" s="407"/>
-      <c r="C339" s="407"/>
+      <c r="B339" s="431"/>
+      <c r="C339" s="431"/>
       <c r="D339" s="131"/>
-      <c r="E339" s="407"/>
+      <c r="E339" s="431"/>
       <c r="F339" s="155"/>
       <c r="G339" s="155"/>
       <c r="H339" s="155"/>
@@ -20147,10 +20147,10 @@
     </row>
     <row r="340" spans="1:29" ht="15.75" customHeight="1">
       <c r="A340" s="140"/>
-      <c r="B340" s="407"/>
-      <c r="C340" s="407"/>
+      <c r="B340" s="431"/>
+      <c r="C340" s="431"/>
       <c r="D340" s="131"/>
-      <c r="E340" s="407"/>
+      <c r="E340" s="431"/>
       <c r="F340" s="91"/>
       <c r="G340" s="91"/>
       <c r="H340" s="91"/>
@@ -20178,10 +20178,10 @@
     </row>
     <row r="341" spans="1:29" ht="15.75" customHeight="1">
       <c r="A341" s="140"/>
-      <c r="B341" s="407"/>
-      <c r="C341" s="407"/>
+      <c r="B341" s="431"/>
+      <c r="C341" s="431"/>
       <c r="D341" s="131"/>
-      <c r="E341" s="410"/>
+      <c r="E341" s="433"/>
       <c r="F341" s="91"/>
       <c r="G341" s="91"/>
       <c r="H341" s="91"/>
@@ -20209,8 +20209,8 @@
     </row>
     <row r="342" spans="1:29" ht="15.75" customHeight="1">
       <c r="A342" s="140"/>
-      <c r="B342" s="407"/>
-      <c r="C342" s="407"/>
+      <c r="B342" s="431"/>
+      <c r="C342" s="431"/>
       <c r="D342" s="131"/>
       <c r="E342" s="136"/>
       <c r="F342" s="88"/>
@@ -20240,8 +20240,8 @@
     </row>
     <row r="343" spans="1:29" ht="15.75" customHeight="1">
       <c r="A343" s="140"/>
-      <c r="B343" s="407"/>
-      <c r="C343" s="407"/>
+      <c r="B343" s="431"/>
+      <c r="C343" s="431"/>
       <c r="D343" s="131"/>
       <c r="E343" s="136"/>
       <c r="F343" s="89"/>
@@ -20271,10 +20271,10 @@
     </row>
     <row r="344" spans="1:29" ht="15.75" customHeight="1">
       <c r="A344" s="140"/>
-      <c r="B344" s="407"/>
-      <c r="C344" s="407"/>
+      <c r="B344" s="431"/>
+      <c r="C344" s="431"/>
       <c r="D344" s="156"/>
-      <c r="E344" s="435"/>
+      <c r="E344" s="452"/>
       <c r="F344" s="98"/>
       <c r="G344" s="98"/>
       <c r="H344" s="98"/>
@@ -20302,10 +20302,10 @@
     </row>
     <row r="345" spans="1:29" ht="15.75" customHeight="1">
       <c r="A345" s="140"/>
-      <c r="B345" s="407"/>
-      <c r="C345" s="407"/>
+      <c r="B345" s="431"/>
+      <c r="C345" s="431"/>
       <c r="D345" s="137"/>
-      <c r="E345" s="407"/>
+      <c r="E345" s="431"/>
       <c r="F345" s="89"/>
       <c r="G345" s="89"/>
       <c r="H345" s="89"/>
@@ -20333,10 +20333,10 @@
     </row>
     <row r="346" spans="1:29" ht="15.75" customHeight="1">
       <c r="A346" s="140"/>
-      <c r="B346" s="407"/>
-      <c r="C346" s="407"/>
+      <c r="B346" s="431"/>
+      <c r="C346" s="431"/>
       <c r="D346" s="137"/>
-      <c r="E346" s="407"/>
+      <c r="E346" s="431"/>
       <c r="F346" s="89"/>
       <c r="G346" s="89"/>
       <c r="H346" s="89"/>
@@ -20364,10 +20364,10 @@
     </row>
     <row r="347" spans="1:29" ht="15.75" customHeight="1">
       <c r="A347" s="140"/>
-      <c r="B347" s="407"/>
-      <c r="C347" s="410"/>
+      <c r="B347" s="431"/>
+      <c r="C347" s="433"/>
       <c r="D347" s="116"/>
-      <c r="E347" s="410"/>
+      <c r="E347" s="433"/>
       <c r="F347" s="89"/>
       <c r="G347" s="89"/>
       <c r="H347" s="89"/>
@@ -20395,7 +20395,7 @@
     </row>
     <row r="348" spans="1:29" ht="15.75" customHeight="1">
       <c r="A348" s="140"/>
-      <c r="B348" s="407"/>
+      <c r="B348" s="431"/>
       <c r="C348" s="131"/>
       <c r="D348" s="137"/>
       <c r="E348" s="137"/>
@@ -20426,10 +20426,10 @@
     </row>
     <row r="349" spans="1:29" ht="15.75" customHeight="1">
       <c r="A349" s="140"/>
-      <c r="B349" s="407"/>
-      <c r="C349" s="435"/>
+      <c r="B349" s="431"/>
+      <c r="C349" s="452"/>
       <c r="D349" s="156"/>
-      <c r="E349" s="440"/>
+      <c r="E349" s="454"/>
       <c r="F349" s="98"/>
       <c r="G349" s="98"/>
       <c r="H349" s="98"/>
@@ -20457,10 +20457,10 @@
     </row>
     <row r="350" spans="1:29" ht="15.75" customHeight="1">
       <c r="A350" s="140"/>
-      <c r="B350" s="407"/>
-      <c r="C350" s="407"/>
+      <c r="B350" s="431"/>
+      <c r="C350" s="431"/>
       <c r="D350" s="116"/>
-      <c r="E350" s="410"/>
+      <c r="E350" s="433"/>
       <c r="F350" s="98"/>
       <c r="G350" s="98"/>
       <c r="H350" s="98"/>
@@ -20488,10 +20488,10 @@
     </row>
     <row r="351" spans="1:29" ht="15.75" customHeight="1">
       <c r="A351" s="140"/>
-      <c r="B351" s="407"/>
-      <c r="C351" s="407"/>
+      <c r="B351" s="431"/>
+      <c r="C351" s="431"/>
       <c r="D351" s="131"/>
-      <c r="E351" s="440"/>
+      <c r="E351" s="454"/>
       <c r="F351" s="98"/>
       <c r="G351" s="98"/>
       <c r="H351" s="98"/>
@@ -20519,10 +20519,10 @@
     </row>
     <row r="352" spans="1:29" ht="15.75" customHeight="1">
       <c r="A352" s="140"/>
-      <c r="B352" s="407"/>
-      <c r="C352" s="410"/>
+      <c r="B352" s="431"/>
+      <c r="C352" s="433"/>
       <c r="D352" s="131"/>
-      <c r="E352" s="410"/>
+      <c r="E352" s="433"/>
       <c r="F352" s="98"/>
       <c r="G352" s="98"/>
       <c r="H352" s="98"/>
@@ -20550,7 +20550,7 @@
     </row>
     <row r="353" spans="1:29" ht="15.75" customHeight="1">
       <c r="A353" s="140"/>
-      <c r="B353" s="407"/>
+      <c r="B353" s="431"/>
       <c r="C353" s="136"/>
       <c r="D353" s="136"/>
       <c r="E353" s="140"/>
@@ -20581,10 +20581,10 @@
     </row>
     <row r="354" spans="1:29" ht="15.75" customHeight="1">
       <c r="A354" s="140"/>
-      <c r="B354" s="407"/>
-      <c r="C354" s="435"/>
+      <c r="B354" s="431"/>
+      <c r="C354" s="452"/>
       <c r="D354" s="156"/>
-      <c r="E354" s="435"/>
+      <c r="E354" s="452"/>
       <c r="F354" s="98"/>
       <c r="G354" s="98"/>
       <c r="H354" s="98"/>
@@ -20612,10 +20612,10 @@
     </row>
     <row r="355" spans="1:29" ht="15.75" customHeight="1">
       <c r="A355" s="140"/>
-      <c r="B355" s="407"/>
-      <c r="C355" s="407"/>
+      <c r="B355" s="431"/>
+      <c r="C355" s="431"/>
       <c r="D355" s="137"/>
-      <c r="E355" s="407"/>
+      <c r="E355" s="431"/>
       <c r="F355" s="98"/>
       <c r="G355" s="98"/>
       <c r="H355" s="98"/>
@@ -20643,10 +20643,10 @@
     </row>
     <row r="356" spans="1:29" ht="15.75" customHeight="1">
       <c r="A356" s="140"/>
-      <c r="B356" s="407"/>
-      <c r="C356" s="407"/>
+      <c r="B356" s="431"/>
+      <c r="C356" s="431"/>
       <c r="D356" s="137"/>
-      <c r="E356" s="407"/>
+      <c r="E356" s="431"/>
       <c r="F356" s="98"/>
       <c r="G356" s="98"/>
       <c r="H356" s="98"/>
@@ -20674,10 +20674,10 @@
     </row>
     <row r="357" spans="1:29" ht="15.75" customHeight="1">
       <c r="A357" s="140"/>
-      <c r="B357" s="407"/>
-      <c r="C357" s="407"/>
+      <c r="B357" s="431"/>
+      <c r="C357" s="431"/>
       <c r="D357" s="137"/>
-      <c r="E357" s="407"/>
+      <c r="E357" s="431"/>
       <c r="F357" s="98"/>
       <c r="G357" s="98"/>
       <c r="H357" s="98"/>
@@ -20705,10 +20705,10 @@
     </row>
     <row r="358" spans="1:29" ht="15.75" customHeight="1">
       <c r="A358" s="140"/>
-      <c r="B358" s="407"/>
-      <c r="C358" s="407"/>
+      <c r="B358" s="431"/>
+      <c r="C358" s="431"/>
       <c r="D358" s="137"/>
-      <c r="E358" s="407"/>
+      <c r="E358" s="431"/>
       <c r="F358" s="91"/>
       <c r="G358" s="91"/>
       <c r="H358" s="91"/>
@@ -20736,10 +20736,10 @@
     </row>
     <row r="359" spans="1:29" ht="15.75" customHeight="1">
       <c r="A359" s="140"/>
-      <c r="B359" s="407"/>
-      <c r="C359" s="407"/>
+      <c r="B359" s="431"/>
+      <c r="C359" s="431"/>
       <c r="D359" s="116"/>
-      <c r="E359" s="410"/>
+      <c r="E359" s="433"/>
       <c r="F359" s="91"/>
       <c r="G359" s="91"/>
       <c r="H359" s="91"/>
@@ -20767,10 +20767,10 @@
     </row>
     <row r="360" spans="1:29" ht="15.75" customHeight="1">
       <c r="A360" s="140"/>
-      <c r="B360" s="407"/>
-      <c r="C360" s="407"/>
+      <c r="B360" s="431"/>
+      <c r="C360" s="431"/>
       <c r="D360" s="156"/>
-      <c r="E360" s="435"/>
+      <c r="E360" s="452"/>
       <c r="F360" s="98"/>
       <c r="G360" s="98"/>
       <c r="H360" s="98"/>
@@ -20798,10 +20798,10 @@
     </row>
     <row r="361" spans="1:29" ht="15.75" customHeight="1">
       <c r="A361" s="140"/>
-      <c r="B361" s="407"/>
-      <c r="C361" s="407"/>
+      <c r="B361" s="431"/>
+      <c r="C361" s="431"/>
       <c r="D361" s="137"/>
-      <c r="E361" s="407"/>
+      <c r="E361" s="431"/>
       <c r="F361" s="89"/>
       <c r="G361" s="89"/>
       <c r="H361" s="89"/>
@@ -20829,10 +20829,10 @@
     </row>
     <row r="362" spans="1:29" ht="15.75" customHeight="1">
       <c r="A362" s="140"/>
-      <c r="B362" s="407"/>
-      <c r="C362" s="407"/>
+      <c r="B362" s="431"/>
+      <c r="C362" s="431"/>
       <c r="D362" s="137"/>
-      <c r="E362" s="407"/>
+      <c r="E362" s="431"/>
       <c r="F362" s="89"/>
       <c r="G362" s="89"/>
       <c r="H362" s="89"/>
@@ -20860,10 +20860,10 @@
     </row>
     <row r="363" spans="1:29" ht="15.75" customHeight="1">
       <c r="A363" s="140"/>
-      <c r="B363" s="410"/>
-      <c r="C363" s="410"/>
+      <c r="B363" s="433"/>
+      <c r="C363" s="433"/>
       <c r="D363" s="116"/>
-      <c r="E363" s="410"/>
+      <c r="E363" s="433"/>
       <c r="F363" s="89"/>
       <c r="G363" s="89"/>
       <c r="H363" s="89"/>
@@ -23613,41 +23613,6 @@
     <row r="1045" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D163:D164"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D66"/>
-    <mergeCell ref="D68:D79"/>
-    <mergeCell ref="D81:D87"/>
-    <mergeCell ref="D89:D99"/>
-    <mergeCell ref="D101:D105"/>
-    <mergeCell ref="K317:K318"/>
-    <mergeCell ref="C321:C322"/>
-    <mergeCell ref="K321:K322"/>
-    <mergeCell ref="C323:C324"/>
-    <mergeCell ref="B334:B363"/>
-    <mergeCell ref="C354:C363"/>
-    <mergeCell ref="E354:E359"/>
-    <mergeCell ref="E360:E363"/>
-    <mergeCell ref="C349:C352"/>
-    <mergeCell ref="E349:E350"/>
-    <mergeCell ref="E351:E352"/>
-    <mergeCell ref="C298:C299"/>
-    <mergeCell ref="C301:C305"/>
-    <mergeCell ref="C326:C328"/>
-    <mergeCell ref="C334:C347"/>
-    <mergeCell ref="E334:E341"/>
-    <mergeCell ref="E344:E347"/>
-    <mergeCell ref="D231:D239"/>
-    <mergeCell ref="K282:K284"/>
-    <mergeCell ref="L282:L284"/>
-    <mergeCell ref="C291:C297"/>
-    <mergeCell ref="E291:E293"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="B10:B229"/>
     <mergeCell ref="D219:D229"/>
@@ -23664,6 +23629,41 @@
     <mergeCell ref="D140:D150"/>
     <mergeCell ref="C10:C119"/>
     <mergeCell ref="D152:D161"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D231:D239"/>
+    <mergeCell ref="K282:K284"/>
+    <mergeCell ref="L282:L284"/>
+    <mergeCell ref="C291:C297"/>
+    <mergeCell ref="E291:E293"/>
+    <mergeCell ref="C298:C299"/>
+    <mergeCell ref="C301:C305"/>
+    <mergeCell ref="C326:C328"/>
+    <mergeCell ref="C334:C347"/>
+    <mergeCell ref="E334:E341"/>
+    <mergeCell ref="E344:E347"/>
+    <mergeCell ref="K317:K318"/>
+    <mergeCell ref="C321:C322"/>
+    <mergeCell ref="K321:K322"/>
+    <mergeCell ref="C323:C324"/>
+    <mergeCell ref="B334:B363"/>
+    <mergeCell ref="C354:C363"/>
+    <mergeCell ref="E354:E359"/>
+    <mergeCell ref="E360:E363"/>
+    <mergeCell ref="C349:C352"/>
+    <mergeCell ref="E349:E350"/>
+    <mergeCell ref="E351:E352"/>
+    <mergeCell ref="D163:D164"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D66"/>
+    <mergeCell ref="D68:D79"/>
+    <mergeCell ref="D81:D87"/>
+    <mergeCell ref="D89:D99"/>
+    <mergeCell ref="D101:D105"/>
   </mergeCells>
   <conditionalFormatting sqref="L8">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
@@ -23757,39 +23757,39 @@
     <row r="2" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="3" spans="1:26" ht="8.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="25.5" customHeight="1" thickBot="1">
-      <c r="B4" s="458" t="s">
+      <c r="B4" s="411" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="459"/>
-      <c r="D4" s="459"/>
-      <c r="E4" s="459"/>
-      <c r="F4" s="459"/>
-      <c r="G4" s="460"/>
+      <c r="C4" s="412"/>
+      <c r="D4" s="412"/>
+      <c r="E4" s="412"/>
+      <c r="F4" s="412"/>
+      <c r="G4" s="413"/>
       <c r="K4" s="183"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
       <c r="B5" s="250" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="461" t="s">
+      <c r="C5" s="414" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="462"/>
-      <c r="E5" s="462"/>
-      <c r="F5" s="462"/>
-      <c r="G5" s="463"/>
+      <c r="D5" s="398"/>
+      <c r="E5" s="398"/>
+      <c r="F5" s="398"/>
+      <c r="G5" s="399"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
       <c r="B6" s="251" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="461" t="s">
+      <c r="C6" s="414" t="s">
         <v>664</v>
       </c>
-      <c r="D6" s="462"/>
-      <c r="E6" s="462"/>
-      <c r="F6" s="462"/>
-      <c r="G6" s="463"/>
+      <c r="D6" s="398"/>
+      <c r="E6" s="398"/>
+      <c r="F6" s="398"/>
+      <c r="G6" s="399"/>
       <c r="I6" s="184" t="s">
         <v>49</v>
       </c>
@@ -23805,13 +23805,13 @@
       <c r="B7" s="250" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="464">
+      <c r="C7" s="397">
         <v>1</v>
       </c>
-      <c r="D7" s="462"/>
-      <c r="E7" s="462"/>
-      <c r="F7" s="462"/>
-      <c r="G7" s="463"/>
+      <c r="D7" s="398"/>
+      <c r="E7" s="398"/>
+      <c r="F7" s="398"/>
+      <c r="G7" s="399"/>
       <c r="I7" s="187">
         <f>C15</f>
         <v>86</v>
@@ -23826,13 +23826,13 @@
       <c r="B8" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="464" t="s">
+      <c r="C8" s="397" t="s">
         <v>665</v>
       </c>
-      <c r="D8" s="462"/>
-      <c r="E8" s="462"/>
-      <c r="F8" s="462"/>
-      <c r="G8" s="463"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
+      <c r="G8" s="399"/>
       <c r="I8" s="187">
         <f>D15</f>
         <v>12</v>
@@ -23847,13 +23847,13 @@
       <c r="B9" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="464" t="s">
+      <c r="C9" s="397" t="s">
         <v>665</v>
       </c>
-      <c r="D9" s="462"/>
-      <c r="E9" s="462"/>
-      <c r="F9" s="462"/>
-      <c r="G9" s="463"/>
+      <c r="D9" s="398"/>
+      <c r="E9" s="398"/>
+      <c r="F9" s="398"/>
+      <c r="G9" s="399"/>
       <c r="I9" s="187">
         <f>E15</f>
         <v>0</v>
@@ -23880,13 +23880,13 @@
       <c r="B10" s="250" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="464" t="s">
+      <c r="C10" s="397" t="s">
         <v>502</v>
       </c>
-      <c r="D10" s="462"/>
-      <c r="E10" s="462"/>
-      <c r="F10" s="462"/>
-      <c r="G10" s="463"/>
+      <c r="D10" s="398"/>
+      <c r="E10" s="398"/>
+      <c r="F10" s="398"/>
+      <c r="G10" s="399"/>
       <c r="I10" s="187">
         <f>F15</f>
         <v>0</v>
@@ -23902,22 +23902,22 @@
       <c r="P10" s="100"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B11" s="473" t="s">
+      <c r="B11" s="400" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="403"/>
-      <c r="D11" s="403"/>
-      <c r="E11" s="403"/>
-      <c r="F11" s="403"/>
-      <c r="G11" s="474"/>
+      <c r="C11" s="401"/>
+      <c r="D11" s="401"/>
+      <c r="E11" s="401"/>
+      <c r="F11" s="401"/>
+      <c r="G11" s="402"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B12" s="470"/>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-      <c r="G12" s="472"/>
+      <c r="B12" s="394"/>
+      <c r="C12" s="395"/>
+      <c r="D12" s="395"/>
+      <c r="E12" s="395"/>
+      <c r="F12" s="395"/>
+      <c r="G12" s="396"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="B13" s="192" t="s">
@@ -24052,21 +24052,21 @@
       <c r="R17" s="195"/>
     </row>
     <row r="18" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B18" s="475" t="s">
+      <c r="B18" s="403" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="399"/>
-      <c r="D18" s="399"/>
-      <c r="E18" s="399"/>
-      <c r="F18" s="399"/>
-      <c r="G18" s="400"/>
+      <c r="C18" s="404"/>
+      <c r="D18" s="404"/>
+      <c r="E18" s="404"/>
+      <c r="F18" s="404"/>
+      <c r="G18" s="405"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B19" s="476" t="s">
+      <c r="B19" s="406" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="399"/>
-      <c r="D19" s="400"/>
+      <c r="C19" s="404"/>
+      <c r="D19" s="405"/>
       <c r="E19" s="208"/>
       <c r="F19" s="208" t="s">
         <v>67</v>
@@ -24076,11 +24076,11 @@
       </c>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="407" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="399"/>
-      <c r="D20" s="400"/>
+      <c r="C20" s="404"/>
+      <c r="D20" s="405"/>
       <c r="E20" s="209"/>
       <c r="F20" s="209" t="s">
         <v>70</v>
@@ -24090,11 +24090,11 @@
       </c>
     </row>
     <row r="21" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B21" s="477" t="s">
+      <c r="B21" s="407" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="399"/>
-      <c r="D21" s="400"/>
+      <c r="C21" s="404"/>
+      <c r="D21" s="405"/>
       <c r="E21" s="209"/>
       <c r="F21" s="209" t="s">
         <v>70</v>
@@ -24105,306 +24105,306 @@
     </row>
     <row r="22" spans="2:18" ht="15.75" customHeight="1"/>
     <row r="23" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B23" s="480"/>
-      <c r="C23" s="478" t="s">
+      <c r="B23" s="410"/>
+      <c r="C23" s="408" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="479" t="s">
+      <c r="D23" s="409" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="466"/>
-      <c r="F23" s="466"/>
-      <c r="G23" s="467"/>
+      <c r="E23" s="389"/>
+      <c r="F23" s="389"/>
+      <c r="G23" s="390"/>
     </row>
     <row r="24" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B24" s="404"/>
-      <c r="C24" s="404"/>
-      <c r="D24" s="468"/>
-      <c r="E24" s="419"/>
-      <c r="F24" s="419"/>
-      <c r="G24" s="469"/>
+      <c r="B24" s="384"/>
+      <c r="C24" s="384"/>
+      <c r="D24" s="391"/>
+      <c r="E24" s="392"/>
+      <c r="F24" s="392"/>
+      <c r="G24" s="393"/>
     </row>
     <row r="25" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B25" s="404"/>
-      <c r="C25" s="404"/>
-      <c r="D25" s="468"/>
-      <c r="E25" s="419"/>
-      <c r="F25" s="419"/>
-      <c r="G25" s="469"/>
+      <c r="B25" s="384"/>
+      <c r="C25" s="384"/>
+      <c r="D25" s="391"/>
+      <c r="E25" s="392"/>
+      <c r="F25" s="392"/>
+      <c r="G25" s="393"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B26" s="405"/>
-      <c r="C26" s="405"/>
-      <c r="D26" s="470"/>
-      <c r="E26" s="471"/>
-      <c r="F26" s="471"/>
-      <c r="G26" s="472"/>
+      <c r="B26" s="385"/>
+      <c r="C26" s="385"/>
+      <c r="D26" s="394"/>
+      <c r="E26" s="395"/>
+      <c r="F26" s="395"/>
+      <c r="G26" s="396"/>
     </row>
     <row r="27" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B27" s="481" t="s">
+      <c r="B27" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="482" t="s">
+      <c r="C27" s="383" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="465" t="s">
+      <c r="D27" s="388" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="466"/>
-      <c r="F27" s="466"/>
-      <c r="G27" s="467"/>
+      <c r="E27" s="389"/>
+      <c r="F27" s="389"/>
+      <c r="G27" s="390"/>
     </row>
     <row r="28" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B28" s="404"/>
-      <c r="C28" s="404"/>
-      <c r="D28" s="468"/>
-      <c r="E28" s="419"/>
-      <c r="F28" s="419"/>
-      <c r="G28" s="469"/>
+      <c r="B28" s="384"/>
+      <c r="C28" s="384"/>
+      <c r="D28" s="391"/>
+      <c r="E28" s="392"/>
+      <c r="F28" s="392"/>
+      <c r="G28" s="393"/>
     </row>
     <row r="29" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B29" s="404"/>
-      <c r="C29" s="404"/>
-      <c r="D29" s="468"/>
-      <c r="E29" s="419"/>
-      <c r="F29" s="419"/>
-      <c r="G29" s="469"/>
+      <c r="B29" s="384"/>
+      <c r="C29" s="384"/>
+      <c r="D29" s="391"/>
+      <c r="E29" s="392"/>
+      <c r="F29" s="392"/>
+      <c r="G29" s="393"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B30" s="405"/>
-      <c r="C30" s="405"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
-      <c r="G30" s="472"/>
+      <c r="B30" s="385"/>
+      <c r="C30" s="385"/>
+      <c r="D30" s="394"/>
+      <c r="E30" s="395"/>
+      <c r="F30" s="395"/>
+      <c r="G30" s="396"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B31" s="481" t="s">
+      <c r="B31" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="482" t="s">
+      <c r="C31" s="383" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="465" t="s">
+      <c r="D31" s="388" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="466"/>
-      <c r="F31" s="466"/>
-      <c r="G31" s="467"/>
+      <c r="E31" s="389"/>
+      <c r="F31" s="389"/>
+      <c r="G31" s="390"/>
     </row>
     <row r="32" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B32" s="404"/>
-      <c r="C32" s="404"/>
-      <c r="D32" s="468"/>
-      <c r="E32" s="419"/>
-      <c r="F32" s="419"/>
-      <c r="G32" s="469"/>
+      <c r="B32" s="384"/>
+      <c r="C32" s="384"/>
+      <c r="D32" s="391"/>
+      <c r="E32" s="392"/>
+      <c r="F32" s="392"/>
+      <c r="G32" s="393"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="404"/>
-      <c r="C33" s="404"/>
-      <c r="D33" s="468"/>
-      <c r="E33" s="419"/>
-      <c r="F33" s="419"/>
-      <c r="G33" s="469"/>
+      <c r="B33" s="384"/>
+      <c r="C33" s="384"/>
+      <c r="D33" s="391"/>
+      <c r="E33" s="392"/>
+      <c r="F33" s="392"/>
+      <c r="G33" s="393"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="405"/>
-      <c r="C34" s="405"/>
-      <c r="D34" s="470"/>
-      <c r="E34" s="471"/>
-      <c r="F34" s="471"/>
-      <c r="G34" s="472"/>
+      <c r="B34" s="385"/>
+      <c r="C34" s="385"/>
+      <c r="D34" s="394"/>
+      <c r="E34" s="395"/>
+      <c r="F34" s="395"/>
+      <c r="G34" s="396"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B35" s="481" t="s">
+      <c r="B35" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="482" t="s">
+      <c r="C35" s="383" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="465" t="s">
+      <c r="D35" s="388" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="466"/>
-      <c r="F35" s="466"/>
-      <c r="G35" s="467"/>
+      <c r="E35" s="389"/>
+      <c r="F35" s="389"/>
+      <c r="G35" s="390"/>
     </row>
     <row r="36" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B36" s="404"/>
-      <c r="C36" s="404"/>
-      <c r="D36" s="468"/>
-      <c r="E36" s="419"/>
-      <c r="F36" s="419"/>
-      <c r="G36" s="469"/>
+      <c r="B36" s="384"/>
+      <c r="C36" s="384"/>
+      <c r="D36" s="391"/>
+      <c r="E36" s="392"/>
+      <c r="F36" s="392"/>
+      <c r="G36" s="393"/>
     </row>
     <row r="37" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B37" s="404"/>
-      <c r="C37" s="404"/>
-      <c r="D37" s="468"/>
-      <c r="E37" s="419"/>
-      <c r="F37" s="419"/>
-      <c r="G37" s="469"/>
+      <c r="B37" s="384"/>
+      <c r="C37" s="384"/>
+      <c r="D37" s="391"/>
+      <c r="E37" s="392"/>
+      <c r="F37" s="392"/>
+      <c r="G37" s="393"/>
     </row>
     <row r="38" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B38" s="405"/>
-      <c r="C38" s="405"/>
-      <c r="D38" s="470"/>
-      <c r="E38" s="471"/>
-      <c r="F38" s="471"/>
-      <c r="G38" s="472"/>
+      <c r="B38" s="385"/>
+      <c r="C38" s="385"/>
+      <c r="D38" s="394"/>
+      <c r="E38" s="395"/>
+      <c r="F38" s="395"/>
+      <c r="G38" s="396"/>
     </row>
     <row r="39" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B39" s="481" t="s">
+      <c r="B39" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="482" t="s">
+      <c r="C39" s="383" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="465" t="s">
+      <c r="D39" s="388" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="466"/>
-      <c r="F39" s="466"/>
-      <c r="G39" s="467"/>
+      <c r="E39" s="389"/>
+      <c r="F39" s="389"/>
+      <c r="G39" s="390"/>
     </row>
     <row r="40" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B40" s="404"/>
-      <c r="C40" s="404"/>
-      <c r="D40" s="468"/>
-      <c r="E40" s="419"/>
-      <c r="F40" s="419"/>
-      <c r="G40" s="469"/>
+      <c r="B40" s="384"/>
+      <c r="C40" s="384"/>
+      <c r="D40" s="391"/>
+      <c r="E40" s="392"/>
+      <c r="F40" s="392"/>
+      <c r="G40" s="393"/>
     </row>
     <row r="41" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B41" s="404"/>
-      <c r="C41" s="404"/>
-      <c r="D41" s="468"/>
-      <c r="E41" s="419"/>
-      <c r="F41" s="419"/>
-      <c r="G41" s="469"/>
+      <c r="B41" s="384"/>
+      <c r="C41" s="384"/>
+      <c r="D41" s="391"/>
+      <c r="E41" s="392"/>
+      <c r="F41" s="392"/>
+      <c r="G41" s="393"/>
     </row>
     <row r="42" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B42" s="405"/>
-      <c r="C42" s="405"/>
-      <c r="D42" s="470"/>
-      <c r="E42" s="471"/>
-      <c r="F42" s="471"/>
-      <c r="G42" s="472"/>
+      <c r="B42" s="385"/>
+      <c r="C42" s="385"/>
+      <c r="D42" s="394"/>
+      <c r="E42" s="395"/>
+      <c r="F42" s="395"/>
+      <c r="G42" s="396"/>
     </row>
     <row r="43" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B43" s="481" t="s">
+      <c r="B43" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="483" t="s">
+      <c r="C43" s="387" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="465" t="s">
+      <c r="D43" s="388" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="466"/>
-      <c r="F43" s="466"/>
-      <c r="G43" s="467"/>
+      <c r="E43" s="389"/>
+      <c r="F43" s="389"/>
+      <c r="G43" s="390"/>
     </row>
     <row r="44" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B44" s="404"/>
-      <c r="C44" s="404"/>
-      <c r="D44" s="468"/>
-      <c r="E44" s="419"/>
-      <c r="F44" s="419"/>
-      <c r="G44" s="469"/>
+      <c r="B44" s="384"/>
+      <c r="C44" s="384"/>
+      <c r="D44" s="391"/>
+      <c r="E44" s="392"/>
+      <c r="F44" s="392"/>
+      <c r="G44" s="393"/>
     </row>
     <row r="45" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B45" s="404"/>
-      <c r="C45" s="404"/>
-      <c r="D45" s="468"/>
-      <c r="E45" s="419"/>
-      <c r="F45" s="419"/>
-      <c r="G45" s="469"/>
+      <c r="B45" s="384"/>
+      <c r="C45" s="384"/>
+      <c r="D45" s="391"/>
+      <c r="E45" s="392"/>
+      <c r="F45" s="392"/>
+      <c r="G45" s="393"/>
     </row>
     <row r="46" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B46" s="405"/>
-      <c r="C46" s="405"/>
-      <c r="D46" s="470"/>
-      <c r="E46" s="471"/>
-      <c r="F46" s="471"/>
-      <c r="G46" s="472"/>
+      <c r="B46" s="385"/>
+      <c r="C46" s="385"/>
+      <c r="D46" s="394"/>
+      <c r="E46" s="395"/>
+      <c r="F46" s="395"/>
+      <c r="G46" s="396"/>
     </row>
     <row r="47" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B47" s="481" t="s">
+      <c r="B47" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="483" t="s">
+      <c r="C47" s="387" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="465" t="s">
+      <c r="D47" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="466"/>
-      <c r="F47" s="466"/>
-      <c r="G47" s="467"/>
+      <c r="E47" s="389"/>
+      <c r="F47" s="389"/>
+      <c r="G47" s="390"/>
     </row>
     <row r="48" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B48" s="404"/>
-      <c r="C48" s="404"/>
-      <c r="D48" s="468"/>
-      <c r="E48" s="419"/>
-      <c r="F48" s="419"/>
-      <c r="G48" s="469"/>
+      <c r="B48" s="384"/>
+      <c r="C48" s="384"/>
+      <c r="D48" s="391"/>
+      <c r="E48" s="392"/>
+      <c r="F48" s="392"/>
+      <c r="G48" s="393"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B49" s="404"/>
-      <c r="C49" s="404"/>
-      <c r="D49" s="468"/>
-      <c r="E49" s="419"/>
-      <c r="F49" s="419"/>
-      <c r="G49" s="469"/>
+      <c r="B49" s="384"/>
+      <c r="C49" s="384"/>
+      <c r="D49" s="391"/>
+      <c r="E49" s="392"/>
+      <c r="F49" s="392"/>
+      <c r="G49" s="393"/>
     </row>
     <row r="50" spans="2:7" ht="33.75" customHeight="1">
-      <c r="B50" s="405"/>
-      <c r="C50" s="405"/>
-      <c r="D50" s="470"/>
-      <c r="E50" s="471"/>
-      <c r="F50" s="471"/>
-      <c r="G50" s="472"/>
+      <c r="B50" s="385"/>
+      <c r="C50" s="385"/>
+      <c r="D50" s="394"/>
+      <c r="E50" s="395"/>
+      <c r="F50" s="395"/>
+      <c r="G50" s="396"/>
     </row>
     <row r="51" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B51" s="481" t="s">
+      <c r="B51" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="483" t="s">
+      <c r="C51" s="387" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="465" t="s">
+      <c r="D51" s="388" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="466"/>
-      <c r="F51" s="466"/>
-      <c r="G51" s="467"/>
+      <c r="E51" s="389"/>
+      <c r="F51" s="389"/>
+      <c r="G51" s="390"/>
     </row>
     <row r="52" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B52" s="404"/>
-      <c r="C52" s="404"/>
-      <c r="D52" s="468"/>
-      <c r="E52" s="419"/>
-      <c r="F52" s="419"/>
-      <c r="G52" s="469"/>
+      <c r="B52" s="384"/>
+      <c r="C52" s="384"/>
+      <c r="D52" s="391"/>
+      <c r="E52" s="392"/>
+      <c r="F52" s="392"/>
+      <c r="G52" s="393"/>
     </row>
     <row r="53" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B53" s="404"/>
-      <c r="C53" s="404"/>
-      <c r="D53" s="468"/>
-      <c r="E53" s="419"/>
-      <c r="F53" s="419"/>
-      <c r="G53" s="469"/>
+      <c r="B53" s="384"/>
+      <c r="C53" s="384"/>
+      <c r="D53" s="391"/>
+      <c r="E53" s="392"/>
+      <c r="F53" s="392"/>
+      <c r="G53" s="393"/>
     </row>
     <row r="54" spans="2:7" ht="39" customHeight="1">
-      <c r="B54" s="405"/>
-      <c r="C54" s="405"/>
-      <c r="D54" s="470"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
-      <c r="G54" s="472"/>
+      <c r="B54" s="385"/>
+      <c r="C54" s="385"/>
+      <c r="D54" s="394"/>
+      <c r="E54" s="395"/>
+      <c r="F54" s="395"/>
+      <c r="G54" s="396"/>
     </row>
     <row r="55" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="56" spans="2:7" ht="15.75" customHeight="1"/>
@@ -25354,21 +25354,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="D47:G50"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D51:G54"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:G42"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:G46"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="D27:G30"/>
@@ -25385,11 +25375,21 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="D47:G50"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D51:G54"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:G42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:G46"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C47:C50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -25470,18 +25470,18 @@
       <c r="B3" s="484" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="466"/>
-      <c r="D3" s="466"/>
-      <c r="E3" s="467"/>
+      <c r="C3" s="389"/>
+      <c r="D3" s="389"/>
+      <c r="E3" s="390"/>
       <c r="F3" s="211"/>
       <c r="G3" s="211"/>
       <c r="H3" s="211"/>
     </row>
     <row r="4" spans="1:26" ht="45.75" customHeight="1">
-      <c r="B4" s="470"/>
-      <c r="C4" s="471"/>
-      <c r="D4" s="471"/>
-      <c r="E4" s="472"/>
+      <c r="B4" s="394"/>
+      <c r="C4" s="395"/>
+      <c r="D4" s="395"/>
+      <c r="E4" s="396"/>
       <c r="F4" s="211"/>
       <c r="G4" s="211"/>
       <c r="H4" s="211"/>
@@ -29861,127 +29861,127 @@
     <row r="1" spans="4:14" ht="13.5" customHeight="1"/>
     <row r="2" spans="4:14" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D3" s="500" t="s">
+      <c r="D3" s="509" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="467"/>
-      <c r="G3" s="485" t="s">
+      <c r="E3" s="390"/>
+      <c r="G3" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="507"/>
-      <c r="J3" s="485" t="s">
+      <c r="H3" s="495"/>
+      <c r="J3" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="507"/>
-      <c r="M3" s="485" t="s">
+      <c r="K3" s="495"/>
+      <c r="M3" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="N3" s="507"/>
+      <c r="N3" s="495"/>
     </row>
     <row r="4" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D4" s="468"/>
-      <c r="E4" s="469"/>
-      <c r="G4" s="508"/>
-      <c r="H4" s="509"/>
-      <c r="J4" s="508"/>
-      <c r="K4" s="509"/>
-      <c r="M4" s="508"/>
-      <c r="N4" s="509"/>
+      <c r="D4" s="391"/>
+      <c r="E4" s="393"/>
+      <c r="G4" s="496"/>
+      <c r="H4" s="497"/>
+      <c r="J4" s="496"/>
+      <c r="K4" s="497"/>
+      <c r="M4" s="496"/>
+      <c r="N4" s="497"/>
     </row>
     <row r="5" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D5" s="468"/>
-      <c r="E5" s="469"/>
-      <c r="G5" s="508"/>
-      <c r="H5" s="509"/>
-      <c r="J5" s="508"/>
-      <c r="K5" s="509"/>
-      <c r="M5" s="508"/>
-      <c r="N5" s="509"/>
+      <c r="D5" s="391"/>
+      <c r="E5" s="393"/>
+      <c r="G5" s="496"/>
+      <c r="H5" s="497"/>
+      <c r="J5" s="496"/>
+      <c r="K5" s="497"/>
+      <c r="M5" s="496"/>
+      <c r="N5" s="497"/>
     </row>
     <row r="6" spans="4:14" ht="13.5" customHeight="1" thickBot="1">
-      <c r="D6" s="470"/>
-      <c r="E6" s="472"/>
-      <c r="G6" s="510"/>
-      <c r="H6" s="511"/>
-      <c r="J6" s="510"/>
-      <c r="K6" s="511"/>
-      <c r="M6" s="510"/>
-      <c r="N6" s="511"/>
+      <c r="D6" s="394"/>
+      <c r="E6" s="396"/>
+      <c r="G6" s="498"/>
+      <c r="H6" s="499"/>
+      <c r="J6" s="498"/>
+      <c r="K6" s="499"/>
+      <c r="M6" s="498"/>
+      <c r="N6" s="499"/>
     </row>
     <row r="7" spans="4:14" ht="15" customHeight="1">
-      <c r="D7" s="501" t="s">
+      <c r="D7" s="510" t="s">
         <v>354</v>
       </c>
-      <c r="E7" s="474"/>
-      <c r="G7" s="512" t="s">
+      <c r="E7" s="402"/>
+      <c r="G7" s="500" t="s">
         <v>359</v>
       </c>
-      <c r="H7" s="509"/>
-      <c r="J7" s="512" t="s">
+      <c r="H7" s="497"/>
+      <c r="J7" s="500" t="s">
         <v>363</v>
       </c>
-      <c r="K7" s="509"/>
-      <c r="M7" s="512" t="s">
+      <c r="K7" s="497"/>
+      <c r="M7" s="500" t="s">
         <v>366</v>
       </c>
-      <c r="N7" s="509"/>
+      <c r="N7" s="497"/>
     </row>
     <row r="8" spans="4:14" ht="18.75" customHeight="1">
-      <c r="D8" s="502"/>
-      <c r="E8" s="503"/>
-      <c r="G8" s="508"/>
-      <c r="H8" s="509"/>
-      <c r="J8" s="508"/>
-      <c r="K8" s="509"/>
-      <c r="M8" s="508"/>
-      <c r="N8" s="509"/>
+      <c r="D8" s="511"/>
+      <c r="E8" s="512"/>
+      <c r="G8" s="496"/>
+      <c r="H8" s="497"/>
+      <c r="J8" s="496"/>
+      <c r="K8" s="497"/>
+      <c r="M8" s="496"/>
+      <c r="N8" s="497"/>
     </row>
     <row r="9" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D9" s="504" t="s">
+      <c r="D9" s="513" t="s">
         <v>355</v>
       </c>
-      <c r="E9" s="474"/>
-      <c r="G9" s="515" t="s">
+      <c r="E9" s="402"/>
+      <c r="G9" s="508" t="s">
         <v>360</v>
       </c>
-      <c r="H9" s="509"/>
-      <c r="J9" s="495" t="s">
+      <c r="H9" s="497"/>
+      <c r="J9" s="491" t="s">
         <v>364</v>
       </c>
-      <c r="K9" s="513"/>
-      <c r="M9" s="495" t="s">
+      <c r="K9" s="501"/>
+      <c r="M9" s="491" t="s">
         <v>367</v>
       </c>
-      <c r="N9" s="513"/>
+      <c r="N9" s="501"/>
     </row>
     <row r="10" spans="4:14" ht="21" customHeight="1">
-      <c r="D10" s="502"/>
-      <c r="E10" s="503"/>
+      <c r="D10" s="511"/>
+      <c r="E10" s="512"/>
       <c r="F10" s="283"/>
-      <c r="G10" s="508"/>
-      <c r="H10" s="509"/>
-      <c r="J10" s="514"/>
-      <c r="K10" s="513"/>
-      <c r="M10" s="514"/>
-      <c r="N10" s="513"/>
+      <c r="G10" s="496"/>
+      <c r="H10" s="497"/>
+      <c r="J10" s="502"/>
+      <c r="K10" s="501"/>
+      <c r="M10" s="502"/>
+      <c r="N10" s="501"/>
     </row>
     <row r="11" spans="4:14" ht="21" customHeight="1">
-      <c r="D11" s="505" t="s">
+      <c r="D11" s="514" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="506"/>
-      <c r="G11" s="498" t="s">
+      <c r="E11" s="515"/>
+      <c r="G11" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="H11" s="509"/>
-      <c r="J11" s="498" t="s">
+      <c r="H11" s="497"/>
+      <c r="J11" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="K11" s="509"/>
-      <c r="M11" s="498" t="s">
+      <c r="K11" s="497"/>
+      <c r="M11" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="N11" s="509"/>
+      <c r="N11" s="497"/>
     </row>
     <row r="12" spans="4:14" ht="126.6" customHeight="1">
       <c r="D12" s="270" t="s">
@@ -30129,126 +30129,126 @@
     <row r="20" spans="1:24" ht="13.5" customHeight="1"/>
     <row r="21" spans="1:24" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="22" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D22" s="485" t="s">
+      <c r="D22" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="486"/>
-      <c r="G22" s="485" t="s">
+      <c r="E22" s="503"/>
+      <c r="G22" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="486"/>
-      <c r="J22" s="485" t="s">
+      <c r="H22" s="503"/>
+      <c r="J22" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="K22" s="486"/>
-      <c r="M22" s="485" t="s">
+      <c r="K22" s="503"/>
+      <c r="M22" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="N22" s="486"/>
+      <c r="N22" s="503"/>
     </row>
     <row r="23" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D23" s="487"/>
-      <c r="E23" s="488"/>
-      <c r="G23" s="487"/>
-      <c r="H23" s="488"/>
-      <c r="J23" s="487"/>
-      <c r="K23" s="488"/>
-      <c r="M23" s="487"/>
-      <c r="N23" s="488"/>
+      <c r="D23" s="504"/>
+      <c r="E23" s="505"/>
+      <c r="G23" s="504"/>
+      <c r="H23" s="505"/>
+      <c r="J23" s="504"/>
+      <c r="K23" s="505"/>
+      <c r="M23" s="504"/>
+      <c r="N23" s="505"/>
     </row>
     <row r="24" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D24" s="487"/>
-      <c r="E24" s="488"/>
-      <c r="G24" s="487"/>
-      <c r="H24" s="488"/>
-      <c r="J24" s="487"/>
-      <c r="K24" s="488"/>
-      <c r="M24" s="487"/>
-      <c r="N24" s="488"/>
+      <c r="D24" s="504"/>
+      <c r="E24" s="505"/>
+      <c r="G24" s="504"/>
+      <c r="H24" s="505"/>
+      <c r="J24" s="504"/>
+      <c r="K24" s="505"/>
+      <c r="M24" s="504"/>
+      <c r="N24" s="505"/>
     </row>
     <row r="25" spans="1:24" ht="13.2" customHeight="1" thickBot="1">
-      <c r="D25" s="489"/>
-      <c r="E25" s="490"/>
-      <c r="G25" s="489"/>
-      <c r="H25" s="490"/>
-      <c r="J25" s="489"/>
-      <c r="K25" s="490"/>
-      <c r="M25" s="489"/>
-      <c r="N25" s="490"/>
+      <c r="D25" s="506"/>
+      <c r="E25" s="507"/>
+      <c r="G25" s="506"/>
+      <c r="H25" s="507"/>
+      <c r="J25" s="506"/>
+      <c r="K25" s="507"/>
+      <c r="M25" s="506"/>
+      <c r="N25" s="507"/>
     </row>
     <row r="26" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D26" s="491" t="s">
+      <c r="D26" s="487" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="492"/>
-      <c r="G26" s="491" t="s">
+      <c r="E26" s="488"/>
+      <c r="G26" s="487" t="s">
         <v>376</v>
       </c>
-      <c r="H26" s="492"/>
-      <c r="J26" s="491" t="s">
+      <c r="H26" s="488"/>
+      <c r="J26" s="487" t="s">
         <v>385</v>
       </c>
-      <c r="K26" s="492"/>
-      <c r="M26" s="491" t="s">
+      <c r="K26" s="488"/>
+      <c r="M26" s="487" t="s">
         <v>386</v>
       </c>
-      <c r="N26" s="492"/>
+      <c r="N26" s="488"/>
     </row>
     <row r="27" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D27" s="493"/>
-      <c r="E27" s="494"/>
-      <c r="G27" s="493"/>
-      <c r="H27" s="494"/>
-      <c r="J27" s="493"/>
-      <c r="K27" s="494"/>
-      <c r="M27" s="493"/>
-      <c r="N27" s="494"/>
+      <c r="D27" s="489"/>
+      <c r="E27" s="490"/>
+      <c r="G27" s="489"/>
+      <c r="H27" s="490"/>
+      <c r="J27" s="489"/>
+      <c r="K27" s="490"/>
+      <c r="M27" s="489"/>
+      <c r="N27" s="490"/>
     </row>
     <row r="28" spans="1:24" ht="30" customHeight="1">
-      <c r="D28" s="495" t="s">
+      <c r="D28" s="491" t="s">
         <v>369</v>
       </c>
-      <c r="E28" s="496"/>
-      <c r="G28" s="495" t="s">
+      <c r="E28" s="492"/>
+      <c r="G28" s="491" t="s">
         <v>371</v>
       </c>
-      <c r="H28" s="496"/>
-      <c r="J28" s="495" t="s">
+      <c r="H28" s="492"/>
+      <c r="J28" s="491" t="s">
         <v>374</v>
       </c>
-      <c r="K28" s="496"/>
-      <c r="M28" s="495" t="s">
+      <c r="K28" s="492"/>
+      <c r="M28" s="491" t="s">
         <v>377</v>
       </c>
-      <c r="N28" s="496"/>
+      <c r="N28" s="492"/>
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1">
-      <c r="D29" s="497"/>
-      <c r="E29" s="496"/>
-      <c r="G29" s="497"/>
-      <c r="H29" s="496"/>
-      <c r="J29" s="497"/>
-      <c r="K29" s="496"/>
-      <c r="M29" s="497"/>
-      <c r="N29" s="496"/>
+      <c r="D29" s="493"/>
+      <c r="E29" s="492"/>
+      <c r="G29" s="493"/>
+      <c r="H29" s="492"/>
+      <c r="J29" s="493"/>
+      <c r="K29" s="492"/>
+      <c r="M29" s="493"/>
+      <c r="N29" s="492"/>
     </row>
     <row r="30" spans="1:24" ht="19.8" customHeight="1">
-      <c r="D30" s="498" t="s">
+      <c r="D30" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="499"/>
-      <c r="G30" s="498" t="s">
+      <c r="E30" s="486"/>
+      <c r="G30" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="499"/>
-      <c r="J30" s="498" t="s">
+      <c r="H30" s="486"/>
+      <c r="J30" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="K30" s="499"/>
-      <c r="M30" s="498" t="s">
+      <c r="K30" s="486"/>
+      <c r="M30" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="N30" s="499"/>
+      <c r="N30" s="486"/>
     </row>
     <row r="31" spans="1:24" ht="177" customHeight="1">
       <c r="D31" s="273" t="s">
@@ -30382,126 +30382,126 @@
     <row r="38" spans="4:14" ht="13.5" customHeight="1"/>
     <row r="39" spans="4:14" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="40" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D40" s="485" t="s">
+      <c r="D40" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="E40" s="486"/>
-      <c r="G40" s="485" t="s">
+      <c r="E40" s="503"/>
+      <c r="G40" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="H40" s="486"/>
-      <c r="J40" s="485" t="s">
+      <c r="H40" s="503"/>
+      <c r="J40" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="K40" s="486"/>
-      <c r="M40" s="485" t="s">
+      <c r="K40" s="503"/>
+      <c r="M40" s="494" t="s">
         <v>112</v>
       </c>
-      <c r="N40" s="486"/>
+      <c r="N40" s="503"/>
     </row>
     <row r="41" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D41" s="487"/>
-      <c r="E41" s="488"/>
-      <c r="G41" s="487"/>
-      <c r="H41" s="488"/>
-      <c r="J41" s="487"/>
-      <c r="K41" s="488"/>
-      <c r="M41" s="487"/>
-      <c r="N41" s="488"/>
+      <c r="D41" s="504"/>
+      <c r="E41" s="505"/>
+      <c r="G41" s="504"/>
+      <c r="H41" s="505"/>
+      <c r="J41" s="504"/>
+      <c r="K41" s="505"/>
+      <c r="M41" s="504"/>
+      <c r="N41" s="505"/>
     </row>
     <row r="42" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D42" s="487"/>
-      <c r="E42" s="488"/>
-      <c r="G42" s="487"/>
-      <c r="H42" s="488"/>
-      <c r="J42" s="487"/>
-      <c r="K42" s="488"/>
-      <c r="M42" s="487"/>
-      <c r="N42" s="488"/>
+      <c r="D42" s="504"/>
+      <c r="E42" s="505"/>
+      <c r="G42" s="504"/>
+      <c r="H42" s="505"/>
+      <c r="J42" s="504"/>
+      <c r="K42" s="505"/>
+      <c r="M42" s="504"/>
+      <c r="N42" s="505"/>
     </row>
     <row r="43" spans="4:14" ht="13.5" customHeight="1" thickBot="1">
-      <c r="D43" s="489"/>
-      <c r="E43" s="490"/>
-      <c r="G43" s="489"/>
-      <c r="H43" s="490"/>
-      <c r="J43" s="489"/>
-      <c r="K43" s="490"/>
-      <c r="M43" s="489"/>
-      <c r="N43" s="490"/>
+      <c r="D43" s="506"/>
+      <c r="E43" s="507"/>
+      <c r="G43" s="506"/>
+      <c r="H43" s="507"/>
+      <c r="J43" s="506"/>
+      <c r="K43" s="507"/>
+      <c r="M43" s="506"/>
+      <c r="N43" s="507"/>
     </row>
     <row r="44" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D44" s="491" t="s">
+      <c r="D44" s="487" t="s">
         <v>499</v>
       </c>
-      <c r="E44" s="492"/>
-      <c r="G44" s="491" t="s">
+      <c r="E44" s="488"/>
+      <c r="G44" s="487" t="s">
         <v>500</v>
       </c>
-      <c r="H44" s="492"/>
-      <c r="J44" s="491" t="s">
+      <c r="H44" s="488"/>
+      <c r="J44" s="487" t="s">
         <v>501</v>
       </c>
-      <c r="K44" s="492"/>
-      <c r="M44" s="491" t="s">
+      <c r="K44" s="488"/>
+      <c r="M44" s="487" t="s">
         <v>661</v>
       </c>
-      <c r="N44" s="492"/>
+      <c r="N44" s="488"/>
     </row>
     <row r="45" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D45" s="493"/>
-      <c r="E45" s="494"/>
-      <c r="G45" s="493"/>
-      <c r="H45" s="494"/>
-      <c r="J45" s="493"/>
-      <c r="K45" s="494"/>
-      <c r="M45" s="493"/>
-      <c r="N45" s="494"/>
+      <c r="D45" s="489"/>
+      <c r="E45" s="490"/>
+      <c r="G45" s="489"/>
+      <c r="H45" s="490"/>
+      <c r="J45" s="489"/>
+      <c r="K45" s="490"/>
+      <c r="M45" s="489"/>
+      <c r="N45" s="490"/>
     </row>
     <row r="46" spans="4:14" ht="18.600000000000001" customHeight="1">
-      <c r="D46" s="497" t="s">
+      <c r="D46" s="493" t="s">
         <v>389</v>
       </c>
-      <c r="E46" s="496"/>
-      <c r="G46" s="497" t="s">
+      <c r="E46" s="492"/>
+      <c r="G46" s="493" t="s">
         <v>387</v>
       </c>
-      <c r="H46" s="496"/>
-      <c r="J46" s="497" t="s">
+      <c r="H46" s="492"/>
+      <c r="J46" s="493" t="s">
         <v>391</v>
       </c>
-      <c r="K46" s="496"/>
-      <c r="M46" s="495" t="s">
+      <c r="K46" s="492"/>
+      <c r="M46" s="491" t="s">
         <v>662</v>
       </c>
-      <c r="N46" s="496"/>
+      <c r="N46" s="492"/>
     </row>
     <row r="47" spans="4:14" ht="13.5" customHeight="1">
-      <c r="D47" s="497"/>
-      <c r="E47" s="496"/>
-      <c r="G47" s="497"/>
-      <c r="H47" s="496"/>
-      <c r="J47" s="497"/>
-      <c r="K47" s="496"/>
-      <c r="M47" s="497"/>
-      <c r="N47" s="496"/>
+      <c r="D47" s="493"/>
+      <c r="E47" s="492"/>
+      <c r="G47" s="493"/>
+      <c r="H47" s="492"/>
+      <c r="J47" s="493"/>
+      <c r="K47" s="492"/>
+      <c r="M47" s="493"/>
+      <c r="N47" s="492"/>
     </row>
     <row r="48" spans="4:14" ht="19.2" customHeight="1">
-      <c r="D48" s="498" t="s">
+      <c r="D48" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="499"/>
-      <c r="G48" s="498" t="s">
+      <c r="E48" s="486"/>
+      <c r="G48" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="H48" s="499"/>
-      <c r="J48" s="498" t="s">
+      <c r="H48" s="486"/>
+      <c r="J48" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="K48" s="499"/>
-      <c r="M48" s="498" t="s">
+      <c r="K48" s="486"/>
+      <c r="M48" s="485" t="s">
         <v>113</v>
       </c>
-      <c r="N48" s="499"/>
+      <c r="N48" s="486"/>
     </row>
     <row r="49" spans="4:14" ht="187.8" customHeight="1">
       <c r="D49" s="273" t="s">
@@ -31581,15 +31581,29 @@
     <row r="1003" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="J26:K27"/>
-    <mergeCell ref="M26:N27"/>
-    <mergeCell ref="G28:H29"/>
-    <mergeCell ref="J28:K29"/>
-    <mergeCell ref="M28:N29"/>
-    <mergeCell ref="G26:H27"/>
+    <mergeCell ref="M40:N43"/>
+    <mergeCell ref="M44:N45"/>
+    <mergeCell ref="M46:N47"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="J46:K47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="G40:H43"/>
+    <mergeCell ref="J40:K43"/>
+    <mergeCell ref="D44:E45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="J44:K45"/>
+    <mergeCell ref="D3:E6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D40:E43"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="D26:E27"/>
     <mergeCell ref="M3:N6"/>
     <mergeCell ref="M7:N8"/>
     <mergeCell ref="M9:N10"/>
@@ -31606,29 +31620,15 @@
     <mergeCell ref="G7:H8"/>
     <mergeCell ref="G9:H10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D3:E6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D40:E43"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D28:E29"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="M40:N43"/>
-    <mergeCell ref="M44:N45"/>
-    <mergeCell ref="M46:N47"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="J46:K47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="G40:H43"/>
-    <mergeCell ref="J40:K43"/>
-    <mergeCell ref="D44:E45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="J44:K45"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="J26:K27"/>
+    <mergeCell ref="M26:N27"/>
+    <mergeCell ref="G28:H29"/>
+    <mergeCell ref="J28:K29"/>
+    <mergeCell ref="M28:N29"/>
+    <mergeCell ref="G26:H27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D17" r:id="rId1" display="Take spaces in mobile number field" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
